--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC008B44-8D5E-4349-9AEA-DC1579F18CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93ECEF60-CDCB-4538-86F2-A7F2127B1623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="2554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="2557">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -17086,18 +17086,6 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>计算武器射程时考虑悬崖影响</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
       <t>粘贴地形时默认显示描边</t>
     </r>
   </si>
@@ -22137,6 +22125,20 @@
   </si>
   <si>
     <t>Set FA2 as the default program for %s files</t>
+  </si>
+  <si>
+    <t>计算武器射程时考虑高度影响</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.RangeBound.DrawEllipse</t>
+  </si>
+  <si>
+    <t>使用椭圆绘制除了受高度影响的武器外的所有范围</t>
+  </si>
+  <si>
+    <t>Draw all ranges except for weapons subject to elevation using ellipses</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -22581,7 +22583,7 @@
         <v>1139</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -22592,7 +22594,7 @@
         <v>1140</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -22603,7 +22605,7 @@
         <v>1141</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -22614,7 +22616,7 @@
         <v>1142</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -22625,7 +22627,7 @@
         <v>1143</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="38" x14ac:dyDescent="0.4">
@@ -22636,7 +22638,7 @@
         <v>1144</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="39" x14ac:dyDescent="0.4">
@@ -22669,7 +22671,7 @@
         <v>1147</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
@@ -22680,18 +22682,18 @@
         <v>1148</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>1149</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
@@ -22702,7 +22704,7 @@
         <v>1150</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
@@ -22713,7 +22715,7 @@
         <v>1151</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
@@ -22757,7 +22759,7 @@
         <v>1155</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
@@ -22768,7 +22770,7 @@
         <v>1156</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
@@ -22779,7 +22781,7 @@
         <v>1157</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
@@ -22790,7 +22792,7 @@
         <v>1158</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
@@ -22801,7 +22803,7 @@
         <v>1159</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="39" x14ac:dyDescent="0.4">
@@ -22812,7 +22814,7 @@
         <v>1160</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
@@ -22823,7 +22825,7 @@
         <v>1161</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
@@ -22834,7 +22836,7 @@
         <v>1162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
@@ -22845,7 +22847,7 @@
         <v>1163</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
@@ -22911,7 +22913,7 @@
         <v>1169</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
@@ -22922,7 +22924,7 @@
         <v>1170</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
@@ -22933,7 +22935,7 @@
         <v>1171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
@@ -22944,7 +22946,7 @@
         <v>1172</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
@@ -22955,7 +22957,7 @@
         <v>1173</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
@@ -22966,7 +22968,7 @@
         <v>1142</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
@@ -22977,7 +22979,7 @@
         <v>1174</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
@@ -22988,7 +22990,7 @@
         <v>1175</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
@@ -22999,7 +23001,7 @@
         <v>1176</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
@@ -23010,7 +23012,7 @@
         <v>1177</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
@@ -23021,7 +23023,7 @@
         <v>1154</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
@@ -23032,7 +23034,7 @@
         <v>1178</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
@@ -23043,7 +23045,7 @@
         <v>1179</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
@@ -23054,7 +23056,7 @@
         <v>1180</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
@@ -23065,7 +23067,7 @@
         <v>1181</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.4">
@@ -23076,7 +23078,7 @@
         <v>1182</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
@@ -23087,7 +23089,7 @@
         <v>1183</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.4">
@@ -23098,7 +23100,7 @@
         <v>1184</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.4">
@@ -23109,7 +23111,7 @@
         <v>1173</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.4">
@@ -23120,7 +23122,7 @@
         <v>1142</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.4">
@@ -23131,7 +23133,7 @@
         <v>1185</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.4">
@@ -23142,7 +23144,7 @@
         <v>1186</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.4">
@@ -23153,7 +23155,7 @@
         <v>1187</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
@@ -23164,7 +23166,7 @@
         <v>1188</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
@@ -23215,7 +23217,7 @@
         <v>1189</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
@@ -23391,7 +23393,7 @@
         <v>1205</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="57" x14ac:dyDescent="0.4">
@@ -23402,7 +23404,7 @@
         <v>1206</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.4">
@@ -23424,7 +23426,7 @@
         <v>1208</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.4">
@@ -23435,7 +23437,7 @@
         <v>1172</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.4">
@@ -23446,7 +23448,7 @@
         <v>1173</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.4">
@@ -23457,7 +23459,7 @@
         <v>1142</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.4">
@@ -23468,7 +23470,7 @@
         <v>1176</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.4">
@@ -23479,7 +23481,7 @@
         <v>1209</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.4">
@@ -23490,7 +23492,7 @@
         <v>1177</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.4">
@@ -23501,7 +23503,7 @@
         <v>1210</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.4">
@@ -23512,7 +23514,7 @@
         <v>1211</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.4">
@@ -23523,7 +23525,7 @@
         <v>1212</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.4">
@@ -23534,7 +23536,7 @@
         <v>1213</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.4">
@@ -23545,7 +23547,7 @@
         <v>1214</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.4">
@@ -23567,7 +23569,7 @@
         <v>1216</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.4">
@@ -23578,7 +23580,7 @@
         <v>1217</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.4">
@@ -23589,7 +23591,7 @@
         <v>1218</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.4">
@@ -23600,7 +23602,7 @@
         <v>1219</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.4">
@@ -23611,7 +23613,7 @@
         <v>1220</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.4">
@@ -23622,7 +23624,7 @@
         <v>1221</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.4">
@@ -23633,7 +23635,7 @@
         <v>1222</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.4">
@@ -23644,7 +23646,7 @@
         <v>1179</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.4">
@@ -23655,7 +23657,7 @@
         <v>1180</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.4">
@@ -23666,7 +23668,7 @@
         <v>1181</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.4">
@@ -23677,7 +23679,7 @@
         <v>1223</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.4">
@@ -23688,7 +23690,7 @@
         <v>1224</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.4">
@@ -23930,7 +23932,7 @@
         <v>1245</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.4">
@@ -23941,7 +23943,7 @@
         <v>1246</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.4">
@@ -23952,7 +23954,7 @@
         <v>1247</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.4">
@@ -23963,7 +23965,7 @@
         <v>1248</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.4">
@@ -23974,7 +23976,7 @@
         <v>1184</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.4">
@@ -23985,7 +23987,7 @@
         <v>1173</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.4">
@@ -23996,7 +23998,7 @@
         <v>1142</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.4">
@@ -24007,7 +24009,7 @@
         <v>1249</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.4">
@@ -24018,7 +24020,7 @@
         <v>1250</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="57" x14ac:dyDescent="0.4">
@@ -24029,7 +24031,7 @@
         <v>1251</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="58.5" x14ac:dyDescent="0.4">
@@ -24040,7 +24042,7 @@
         <v>1252</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.4">
@@ -24051,7 +24053,7 @@
         <v>1253</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.4">
@@ -24062,7 +24064,7 @@
         <v>1254</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.4">
@@ -24117,7 +24119,7 @@
         <v>1259</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.4">
@@ -24128,7 +24130,7 @@
         <v>1260</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.4">
@@ -24139,7 +24141,7 @@
         <v>1261</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.4">
@@ -24150,7 +24152,7 @@
         <v>1262</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.4">
@@ -24172,7 +24174,7 @@
         <v>1264</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.4">
@@ -24183,7 +24185,7 @@
         <v>1265</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.4">
@@ -24194,7 +24196,7 @@
         <v>1266</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.4">
@@ -24205,7 +24207,7 @@
         <v>1267</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.4">
@@ -24216,7 +24218,7 @@
         <v>1268</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.4">
@@ -24227,7 +24229,7 @@
         <v>1269</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.4">
@@ -24238,7 +24240,7 @@
         <v>1270</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.4">
@@ -24249,7 +24251,7 @@
         <v>1271</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.4">
@@ -24260,7 +24262,7 @@
         <v>1272</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.4">
@@ -24271,7 +24273,7 @@
         <v>1273</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.4">
@@ -24282,7 +24284,7 @@
         <v>1274</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.4">
@@ -24293,7 +24295,7 @@
         <v>1275</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.4">
@@ -24304,7 +24306,7 @@
         <v>1276</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.4">
@@ -24315,7 +24317,7 @@
         <v>1277</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.4">
@@ -24326,7 +24328,7 @@
         <v>1278</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.4">
@@ -24337,7 +24339,7 @@
         <v>1279</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.4">
@@ -24348,7 +24350,7 @@
         <v>1280</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.4">
@@ -24359,7 +24361,7 @@
         <v>1281</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.4">
@@ -24370,7 +24372,7 @@
         <v>1282</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.4">
@@ -24381,7 +24383,7 @@
         <v>1283</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.4">
@@ -24392,7 +24394,7 @@
         <v>1284</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.4">
@@ -24403,7 +24405,7 @@
         <v>1285</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.4">
@@ -24414,7 +24416,7 @@
         <v>1286</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.4">
@@ -24425,7 +24427,7 @@
         <v>1287</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.4">
@@ -24436,7 +24438,7 @@
         <v>1288</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.4">
@@ -24447,7 +24449,7 @@
         <v>1289</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.4">
@@ -24458,7 +24460,7 @@
         <v>1290</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.4">
@@ -24469,7 +24471,7 @@
         <v>1291</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.4">
@@ -24480,7 +24482,7 @@
         <v>1292</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.4">
@@ -24491,7 +24493,7 @@
         <v>1293</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.4">
@@ -24502,7 +24504,7 @@
         <v>1294</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.4">
@@ -24513,7 +24515,7 @@
         <v>1295</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.4">
@@ -24524,7 +24526,7 @@
         <v>1296</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.4">
@@ -24535,7 +24537,7 @@
         <v>1297</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.4">
@@ -24546,7 +24548,7 @@
         <v>1298</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.4">
@@ -24557,7 +24559,7 @@
         <v>1299</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.4">
@@ -24568,7 +24570,7 @@
         <v>1300</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.4">
@@ -24579,7 +24581,7 @@
         <v>1301</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.4">
@@ -24590,7 +24592,7 @@
         <v>1302</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.4">
@@ -24601,7 +24603,7 @@
         <v>1303</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.4">
@@ -24612,7 +24614,7 @@
         <v>1304</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.4">
@@ -24623,7 +24625,7 @@
         <v>1305</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.4">
@@ -24634,7 +24636,7 @@
         <v>1306</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.4">
@@ -24645,7 +24647,7 @@
         <v>1307</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.4">
@@ -24656,7 +24658,7 @@
         <v>1308</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.4">
@@ -24667,7 +24669,7 @@
         <v>1309</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.4">
@@ -24678,7 +24680,7 @@
         <v>1310</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.4">
@@ -24689,7 +24691,7 @@
         <v>1311</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.4">
@@ -24700,7 +24702,7 @@
         <v>1312</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.4">
@@ -24711,7 +24713,7 @@
         <v>1313</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.4">
@@ -24722,7 +24724,7 @@
         <v>1314</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.4">
@@ -24733,7 +24735,7 @@
         <v>1315</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.4">
@@ -24744,7 +24746,7 @@
         <v>1316</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.4">
@@ -24755,7 +24757,7 @@
         <v>1317</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.4">
@@ -24766,7 +24768,7 @@
         <v>1318</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.4">
@@ -24777,7 +24779,7 @@
         <v>1319</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.4">
@@ -24788,7 +24790,7 @@
         <v>1320</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.4">
@@ -24799,7 +24801,7 @@
         <v>1321</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.4">
@@ -24810,7 +24812,7 @@
         <v>1322</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.4">
@@ -24821,7 +24823,7 @@
         <v>1323</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.4">
@@ -24832,7 +24834,7 @@
         <v>1324</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.4">
@@ -24843,7 +24845,7 @@
         <v>1325</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.4">
@@ -24854,7 +24856,7 @@
         <v>1326</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.4">
@@ -24865,7 +24867,7 @@
         <v>1327</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.4">
@@ -24876,7 +24878,7 @@
         <v>1328</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.4">
@@ -24887,7 +24889,7 @@
         <v>1329</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.4">
@@ -24898,7 +24900,7 @@
         <v>1330</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.4">
@@ -24909,7 +24911,7 @@
         <v>1331</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.4">
@@ -24920,7 +24922,7 @@
         <v>1332</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.4">
@@ -24931,18 +24933,18 @@
         <v>1333</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A218" s="2" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>1334</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.4">
@@ -24953,7 +24955,7 @@
         <v>1335</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.4">
@@ -24964,7 +24966,7 @@
         <v>1336</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.4">
@@ -24975,7 +24977,7 @@
         <v>1337</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.4">
@@ -24986,7 +24988,7 @@
         <v>1338</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.4">
@@ -24997,7 +24999,7 @@
         <v>1339</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.4">
@@ -25008,7 +25010,7 @@
         <v>1340</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.4">
@@ -25019,7 +25021,7 @@
         <v>1341</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.4">
@@ -25030,7 +25032,7 @@
         <v>1342</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.4">
@@ -25041,7 +25043,7 @@
         <v>1343</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.4">
@@ -25052,7 +25054,7 @@
         <v>1344</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.4">
@@ -25063,7 +25065,7 @@
         <v>1345</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.4">
@@ -25074,7 +25076,7 @@
         <v>1346</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.4">
@@ -25085,7 +25087,7 @@
         <v>1347</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.4">
@@ -25096,7 +25098,7 @@
         <v>1348</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.4">
@@ -25107,7 +25109,7 @@
         <v>1349</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.4">
@@ -25118,7 +25120,7 @@
         <v>1350</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.4">
@@ -25129,7 +25131,7 @@
         <v>1351</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.4">
@@ -25140,7 +25142,7 @@
         <v>1352</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.4">
@@ -25151,7 +25153,7 @@
         <v>1353</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.4">
@@ -25162,7 +25164,7 @@
         <v>1354</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.4">
@@ -25173,7 +25175,7 @@
         <v>1355</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.4">
@@ -25184,7 +25186,7 @@
         <v>1356</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.4">
@@ -25195,7 +25197,7 @@
         <v>1357</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.4">
@@ -25206,7 +25208,7 @@
         <v>1358</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.4">
@@ -25217,7 +25219,7 @@
         <v>1359</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.4">
@@ -25228,7 +25230,7 @@
         <v>1360</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.4">
@@ -25239,7 +25241,7 @@
         <v>1361</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.4">
@@ -25250,7 +25252,7 @@
         <v>1362</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.4">
@@ -25261,7 +25263,7 @@
         <v>1363</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.4">
@@ -25272,7 +25274,7 @@
         <v>1364</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.4">
@@ -25283,7 +25285,7 @@
         <v>1365</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.4">
@@ -25294,7 +25296,7 @@
         <v>1366</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.4">
@@ -25305,7 +25307,7 @@
         <v>1367</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.4">
@@ -25316,7 +25318,7 @@
         <v>1368</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.4">
@@ -25327,7 +25329,7 @@
         <v>1369</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.4">
@@ -25338,7 +25340,7 @@
         <v>1370</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.4">
@@ -25349,7 +25351,7 @@
         <v>1371</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.4">
@@ -25360,7 +25362,7 @@
         <v>1372</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.4">
@@ -25371,7 +25373,7 @@
         <v>1373</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.4">
@@ -25382,7 +25384,7 @@
         <v>1374</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.4">
@@ -25393,7 +25395,7 @@
         <v>1375</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.4">
@@ -25404,7 +25406,7 @@
         <v>1376</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.4">
@@ -25415,7 +25417,7 @@
         <v>1377</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.4">
@@ -25426,7 +25428,7 @@
         <v>1378</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.4">
@@ -25437,7 +25439,7 @@
         <v>1379</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.4">
@@ -25448,7 +25450,7 @@
         <v>1380</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.4">
@@ -25459,7 +25461,7 @@
         <v>1381</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.4">
@@ -25470,7 +25472,7 @@
         <v>1382</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.4">
@@ -25481,7 +25483,7 @@
         <v>1383</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.4">
@@ -25492,7 +25494,7 @@
         <v>1384</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.4">
@@ -25503,7 +25505,7 @@
         <v>1385</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.4">
@@ -25514,7 +25516,7 @@
         <v>1386</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.4">
@@ -25525,7 +25527,7 @@
         <v>1387</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.4">
@@ -25536,7 +25538,7 @@
         <v>1388</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.4">
@@ -25547,7 +25549,7 @@
         <v>1389</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.4">
@@ -25558,7 +25560,7 @@
         <v>1390</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.4">
@@ -25569,7 +25571,7 @@
         <v>1391</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.4">
@@ -25580,7 +25582,7 @@
         <v>1392</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.4">
@@ -25591,7 +25593,7 @@
         <v>1393</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.4">
@@ -25602,7 +25604,7 @@
         <v>1394</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.4">
@@ -25613,7 +25615,7 @@
         <v>1395</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.4">
@@ -25624,7 +25626,7 @@
         <v>1396</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.4">
@@ -25635,7 +25637,7 @@
         <v>1397</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.4">
@@ -25646,7 +25648,7 @@
         <v>1398</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.4">
@@ -25657,7 +25659,7 @@
         <v>1399</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.4">
@@ -25668,7 +25670,7 @@
         <v>1395</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.4">
@@ -25679,7 +25681,7 @@
         <v>1398</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.4">
@@ -25690,7 +25692,7 @@
         <v>1400</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.4">
@@ -25712,7 +25714,7 @@
         <v>1401</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.4">
@@ -25723,7 +25725,7 @@
         <v>1402</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.4">
@@ -25734,18 +25736,18 @@
         <v>1403</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A291" s="2" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>1404</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.4">
@@ -25756,7 +25758,7 @@
         <v>1405</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.4">
@@ -25767,7 +25769,7 @@
         <v>1261</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.4">
@@ -25778,7 +25780,7 @@
         <v>1406</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.4">
@@ -25789,7 +25791,7 @@
         <v>1189</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.4">
@@ -25800,7 +25802,7 @@
         <v>1407</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.4">
@@ -25811,7 +25813,7 @@
         <v>1408</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.4">
@@ -25822,7 +25824,7 @@
         <v>1409</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.4">
@@ -25833,7 +25835,7 @@
         <v>1410</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.4">
@@ -25844,7 +25846,7 @@
         <v>1154</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.4">
@@ -25855,7 +25857,7 @@
         <v>1411</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.4">
@@ -25866,7 +25868,7 @@
         <v>1412</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.4">
@@ -25877,7 +25879,7 @@
         <v>1413</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.4">
@@ -25899,7 +25901,7 @@
         <v>1414</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.4">
@@ -25910,7 +25912,7 @@
         <v>1415</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.4">
@@ -25921,7 +25923,7 @@
         <v>1255</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.4">
@@ -25932,7 +25934,7 @@
         <v>1399</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.4">
@@ -25943,7 +25945,7 @@
         <v>1261</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.4">
@@ -25998,7 +26000,7 @@
         <v>1420</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.4">
@@ -26009,7 +26011,7 @@
         <v>1421</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.4">
@@ -26020,7 +26022,7 @@
         <v>1422</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.4">
@@ -26031,7 +26033,7 @@
         <v>1423</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.4">
@@ -26042,7 +26044,7 @@
         <v>1424</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.4">
@@ -26053,7 +26055,7 @@
         <v>1425</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.4">
@@ -26064,7 +26066,7 @@
         <v>1426</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.4">
@@ -26075,7 +26077,7 @@
         <v>1427</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.4">
@@ -26086,7 +26088,7 @@
         <v>1428</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.4">
@@ -26097,7 +26099,7 @@
         <v>1429</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.4">
@@ -26108,7 +26110,7 @@
         <v>1430</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.4">
@@ -26119,7 +26121,7 @@
         <v>1431</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.4">
@@ -26130,7 +26132,7 @@
         <v>1432</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.4">
@@ -26141,7 +26143,7 @@
         <v>1433</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.4">
@@ -26152,7 +26154,7 @@
         <v>1434</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.4">
@@ -26163,7 +26165,7 @@
         <v>1435</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.4">
@@ -26174,7 +26176,7 @@
         <v>1436</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.4">
@@ -26185,7 +26187,7 @@
         <v>1437</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.4">
@@ -26196,7 +26198,7 @@
         <v>1438</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.4">
@@ -26207,7 +26209,7 @@
         <v>1439</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.4">
@@ -26218,7 +26220,7 @@
         <v>1440</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.4">
@@ -26229,7 +26231,7 @@
         <v>1441</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.4">
@@ -26240,7 +26242,7 @@
         <v>1442</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.4">
@@ -26251,7 +26253,7 @@
         <v>1172</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.4">
@@ -26262,7 +26264,7 @@
         <v>1173</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.4">
@@ -26273,7 +26275,7 @@
         <v>1443</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.4">
@@ -26284,7 +26286,7 @@
         <v>1444</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.4">
@@ -26295,7 +26297,7 @@
         <v>1142</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.4">
@@ -26306,7 +26308,7 @@
         <v>1445</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.4">
@@ -26317,7 +26319,7 @@
         <v>1250</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.4">
@@ -26328,7 +26330,7 @@
         <v>1446</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.4">
@@ -26339,7 +26341,7 @@
         <v>1447</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.4">
@@ -26350,7 +26352,7 @@
         <v>1448</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.4">
@@ -26383,7 +26385,7 @@
         <v>1451</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.4">
@@ -26394,7 +26396,7 @@
         <v>1452</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.4">
@@ -26405,7 +26407,7 @@
         <v>1453</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.4">
@@ -26416,7 +26418,7 @@
         <v>1454</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.4">
@@ -26427,7 +26429,7 @@
         <v>1455</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.4">
@@ -26438,7 +26440,7 @@
         <v>1456</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.4">
@@ -26449,7 +26451,7 @@
         <v>1457</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.4">
@@ -26460,7 +26462,7 @@
         <v>1394</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.4">
@@ -26493,7 +26495,7 @@
         <v>1310</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.4">
@@ -26625,7 +26627,7 @@
         <v>1471</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.4">
@@ -26636,7 +26638,7 @@
         <v>1472</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.4">
@@ -26647,7 +26649,7 @@
         <v>1473</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.4">
@@ -26658,7 +26660,7 @@
         <v>1474</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.4">
@@ -26702,7 +26704,7 @@
         <v>1478</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.4">
@@ -27139,10 +27141,10 @@
         <v>409</v>
       </c>
       <c r="B418" s="5" t="s">
+        <v>2348</v>
+      </c>
+      <c r="C418" s="3" t="s">
         <v>2349</v>
-      </c>
-      <c r="C418" s="3" t="s">
-        <v>2350</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.4">
@@ -27681,7 +27683,7 @@
         <v>1407</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.4">
@@ -27758,7 +27760,7 @@
         <v>1545</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.4">
@@ -27769,7 +27771,7 @@
         <v>1546</v>
       </c>
       <c r="C475" s="3" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="38" x14ac:dyDescent="0.4">
@@ -27791,7 +27793,7 @@
         <v>1548</v>
       </c>
       <c r="C477" s="3" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.4">
@@ -27802,7 +27804,7 @@
         <v>1549</v>
       </c>
       <c r="C478" s="3" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.4">
@@ -27813,7 +27815,7 @@
         <v>1550</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.4">
@@ -27824,7 +27826,7 @@
         <v>1551</v>
       </c>
       <c r="C480" s="3" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="38" x14ac:dyDescent="0.4">
@@ -27835,7 +27837,7 @@
         <v>1552</v>
       </c>
       <c r="C481" s="3" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.4">
@@ -27846,7 +27848,7 @@
         <v>1553</v>
       </c>
       <c r="C482" s="3" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="39" x14ac:dyDescent="0.4">
@@ -27857,7 +27859,7 @@
         <v>1554</v>
       </c>
       <c r="C483" s="3" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.4">
@@ -27868,7 +27870,7 @@
         <v>1555</v>
       </c>
       <c r="C484" s="3" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.4">
@@ -27879,7 +27881,7 @@
         <v>1556</v>
       </c>
       <c r="C485" s="3" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.4">
@@ -27890,7 +27892,7 @@
         <v>1557</v>
       </c>
       <c r="C486" s="3" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.4">
@@ -27901,7 +27903,7 @@
         <v>1312</v>
       </c>
       <c r="C487" s="3" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="57" x14ac:dyDescent="0.4">
@@ -27923,7 +27925,7 @@
         <v>1311</v>
       </c>
       <c r="C489" s="3" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="57" x14ac:dyDescent="0.4">
@@ -27945,7 +27947,7 @@
         <v>1560</v>
       </c>
       <c r="C491" s="6" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.4">
@@ -27956,7 +27958,7 @@
         <v>500</v>
       </c>
       <c r="C492" s="3" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="38" x14ac:dyDescent="0.4">
@@ -27967,7 +27969,7 @@
         <v>502</v>
       </c>
       <c r="C493" s="3" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="39" x14ac:dyDescent="0.4">
@@ -28011,7 +28013,7 @@
         <v>1564</v>
       </c>
       <c r="C497" s="3" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.4">
@@ -28022,7 +28024,7 @@
         <v>1565</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.4">
@@ -28033,7 +28035,7 @@
         <v>1566</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.4">
@@ -28044,7 +28046,7 @@
         <v>1567</v>
       </c>
       <c r="C500" s="3" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.4">
@@ -28055,7 +28057,7 @@
         <v>1568</v>
       </c>
       <c r="C501" s="3" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.4">
@@ -28066,7 +28068,7 @@
         <v>1569</v>
       </c>
       <c r="C502" s="3" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.4">
@@ -28077,7 +28079,7 @@
         <v>1570</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.4">
@@ -28088,7 +28090,7 @@
         <v>1571</v>
       </c>
       <c r="C504" s="3" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.4">
@@ -28099,7 +28101,7 @@
         <v>1572</v>
       </c>
       <c r="C505" s="3" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.4">
@@ -28110,7 +28112,7 @@
         <v>1573</v>
       </c>
       <c r="C506" s="3" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.4">
@@ -28121,7 +28123,7 @@
         <v>1574</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.4">
@@ -28132,7 +28134,7 @@
         <v>1575</v>
       </c>
       <c r="C508" s="3" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.4">
@@ -28143,7 +28145,7 @@
         <v>1576</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.4">
@@ -28154,7 +28156,7 @@
         <v>1577</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.4">
@@ -28165,7 +28167,7 @@
         <v>1578</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.4">
@@ -28176,7 +28178,7 @@
         <v>1579</v>
       </c>
       <c r="C512" s="3" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.4">
@@ -28187,7 +28189,7 @@
         <v>1580</v>
       </c>
       <c r="C513" s="3" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.4">
@@ -28198,7 +28200,7 @@
         <v>1581</v>
       </c>
       <c r="C514" s="3" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.4">
@@ -28209,7 +28211,7 @@
         <v>1582</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.4">
@@ -28319,7 +28321,7 @@
         <v>1592</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.4">
@@ -28352,7 +28354,7 @@
         <v>1595</v>
       </c>
       <c r="C528" s="3" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.4">
@@ -28363,7 +28365,7 @@
         <v>1596</v>
       </c>
       <c r="C529" s="3" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.4">
@@ -28374,7 +28376,7 @@
         <v>1597</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.4">
@@ -28385,7 +28387,7 @@
         <v>1598</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.4">
@@ -28396,7 +28398,7 @@
         <v>1599</v>
       </c>
       <c r="C532" s="3" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.4">
@@ -28407,7 +28409,7 @@
         <v>1600</v>
       </c>
       <c r="C533" s="3" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.4">
@@ -28418,7 +28420,7 @@
         <v>1601</v>
       </c>
       <c r="C534" s="3" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.4">
@@ -28429,7 +28431,7 @@
         <v>1602</v>
       </c>
       <c r="C535" s="3" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.4">
@@ -28440,7 +28442,7 @@
         <v>1603</v>
       </c>
       <c r="C536" s="3" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.4">
@@ -28451,7 +28453,7 @@
         <v>1602</v>
       </c>
       <c r="C537" s="3" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.4">
@@ -28462,7 +28464,7 @@
         <v>1604</v>
       </c>
       <c r="C538" s="3" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.4">
@@ -28473,7 +28475,7 @@
         <v>1605</v>
       </c>
       <c r="C539" s="3" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.4">
@@ -28484,7 +28486,7 @@
         <v>1606</v>
       </c>
       <c r="C540" s="3" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.4">
@@ -28495,7 +28497,7 @@
         <v>1607</v>
       </c>
       <c r="C541" s="3" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.4">
@@ -28506,7 +28508,7 @@
         <v>1608</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.4">
@@ -28517,7 +28519,7 @@
         <v>1609</v>
       </c>
       <c r="C543" s="3" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.4">
@@ -28528,7 +28530,7 @@
         <v>1610</v>
       </c>
       <c r="C544" s="3" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.4">
@@ -28539,7 +28541,7 @@
         <v>1611</v>
       </c>
       <c r="C545" s="3" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.4">
@@ -28550,7 +28552,7 @@
         <v>1612</v>
       </c>
       <c r="C546" s="3" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.4">
@@ -28594,7 +28596,7 @@
         <v>1163</v>
       </c>
       <c r="C550" s="3" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.4">
@@ -28605,7 +28607,7 @@
         <v>1616</v>
       </c>
       <c r="C551" s="3" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.4">
@@ -28616,7 +28618,7 @@
         <v>1617</v>
       </c>
       <c r="C552" s="3" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.4">
@@ -28668,7 +28670,7 @@
         <v>1621</v>
       </c>
       <c r="C557" s="3" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.4">
@@ -28679,7 +28681,7 @@
         <v>1622</v>
       </c>
       <c r="C558" s="3" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.4">
@@ -28690,7 +28692,7 @@
         <v>1623</v>
       </c>
       <c r="C559" s="3" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.4">
@@ -28701,7 +28703,7 @@
         <v>1624</v>
       </c>
       <c r="C560" s="3" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.4">
@@ -28712,7 +28714,7 @@
         <v>1625</v>
       </c>
       <c r="C561" s="3" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.4">
@@ -28723,7 +28725,7 @@
         <v>1626</v>
       </c>
       <c r="C562" s="3" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="95" x14ac:dyDescent="0.4">
@@ -28731,10 +28733,10 @@
         <v>572</v>
       </c>
       <c r="B563" s="5" t="s">
+        <v>2350</v>
+      </c>
+      <c r="C563" s="3" t="s">
         <v>2351</v>
-      </c>
-      <c r="C563" s="3" t="s">
-        <v>2352</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.4">
@@ -28742,10 +28744,10 @@
         <v>573</v>
       </c>
       <c r="B564" s="5" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C564" s="3" t="s">
         <v>2269</v>
-      </c>
-      <c r="C564" s="3" t="s">
-        <v>2270</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.4">
@@ -28756,7 +28758,7 @@
         <v>1627</v>
       </c>
       <c r="C565" s="3" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.4">
@@ -28767,7 +28769,7 @@
         <v>1628</v>
       </c>
       <c r="C566" s="3" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.4">
@@ -28778,7 +28780,7 @@
         <v>1629</v>
       </c>
       <c r="C567" s="3" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.4">
@@ -28789,7 +28791,7 @@
         <v>1630</v>
       </c>
       <c r="C568" s="3" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.4">
@@ -28833,7 +28835,7 @@
         <v>1634</v>
       </c>
       <c r="C572" s="3" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.4">
@@ -28844,7 +28846,7 @@
         <v>1635</v>
       </c>
       <c r="C573" s="3" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.4">
@@ -28855,7 +28857,7 @@
         <v>1636</v>
       </c>
       <c r="C574" s="3" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.4">
@@ -28866,7 +28868,7 @@
         <v>1637</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.4">
@@ -28877,7 +28879,7 @@
         <v>1638</v>
       </c>
       <c r="C576" s="3" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.4">
@@ -28888,7 +28890,7 @@
         <v>1639</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.4">
@@ -28899,7 +28901,7 @@
         <v>1640</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.4">
@@ -28910,7 +28912,7 @@
         <v>1641</v>
       </c>
       <c r="C579" s="3" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.4">
@@ -28921,7 +28923,7 @@
         <v>1642</v>
       </c>
       <c r="C580" s="3" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.4">
@@ -28987,7 +28989,7 @@
         <v>1648</v>
       </c>
       <c r="C586" s="3" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.4">
@@ -28998,7 +29000,7 @@
         <v>1649</v>
       </c>
       <c r="C587" s="3" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.4">
@@ -29009,7 +29011,7 @@
         <v>1650</v>
       </c>
       <c r="C588" s="3" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.4">
@@ -29020,7 +29022,7 @@
         <v>1651</v>
       </c>
       <c r="C589" s="3" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.4">
@@ -29031,7 +29033,7 @@
         <v>1652</v>
       </c>
       <c r="C590" s="3" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.4">
@@ -29053,7 +29055,7 @@
         <v>1654</v>
       </c>
       <c r="C592" s="3" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.4">
@@ -29064,7 +29066,7 @@
         <v>1655</v>
       </c>
       <c r="C593" s="3" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.4">
@@ -29075,7 +29077,7 @@
         <v>1656</v>
       </c>
       <c r="C594" s="3" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.4">
@@ -29086,7 +29088,7 @@
         <v>1657</v>
       </c>
       <c r="C595" s="3" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.4">
@@ -29097,7 +29099,7 @@
         <v>1658</v>
       </c>
       <c r="C596" s="3" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.4">
@@ -29108,7 +29110,7 @@
         <v>1659</v>
       </c>
       <c r="C597" s="3" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.4">
@@ -29119,7 +29121,7 @@
         <v>1660</v>
       </c>
       <c r="C598" s="3" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.4">
@@ -29130,7 +29132,7 @@
         <v>1661</v>
       </c>
       <c r="C599" s="3" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.4">
@@ -29141,7 +29143,7 @@
         <v>1662</v>
       </c>
       <c r="C600" s="3" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.4">
@@ -29152,7 +29154,7 @@
         <v>1663</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.4">
@@ -29163,7 +29165,7 @@
         <v>1664</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.4">
@@ -29174,7 +29176,7 @@
         <v>1665</v>
       </c>
       <c r="C603" s="3" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.4">
@@ -29185,7 +29187,7 @@
         <v>1666</v>
       </c>
       <c r="C604" s="3" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.4">
@@ -29196,7 +29198,7 @@
         <v>1667</v>
       </c>
       <c r="C605" s="3" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.4">
@@ -29207,7 +29209,7 @@
         <v>1668</v>
       </c>
       <c r="C606" s="3" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="607" spans="1:3" ht="114" x14ac:dyDescent="0.4">
@@ -29218,7 +29220,7 @@
         <v>1669</v>
       </c>
       <c r="C607" s="3" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.4">
@@ -29229,7 +29231,7 @@
         <v>1670</v>
       </c>
       <c r="C608" s="3" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.4">
@@ -29240,7 +29242,7 @@
         <v>1671</v>
       </c>
       <c r="C609" s="3" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.4">
@@ -29251,7 +29253,7 @@
         <v>1672</v>
       </c>
       <c r="C610" s="3" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.4">
@@ -29262,7 +29264,7 @@
         <v>1673</v>
       </c>
       <c r="C611" s="3" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.4">
@@ -29273,7 +29275,7 @@
         <v>1172</v>
       </c>
       <c r="C612" s="3" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.4">
@@ -29372,7 +29374,7 @@
         <v>1682</v>
       </c>
       <c r="C621" s="3" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.4">
@@ -30161,7 +30163,7 @@
         <v>702</v>
       </c>
       <c r="B693" s="5" t="s">
-        <v>1754</v>
+        <v>2553</v>
       </c>
       <c r="C693" s="3" t="s">
         <v>1102</v>
@@ -30172,7 +30174,7 @@
         <v>703</v>
       </c>
       <c r="B694" s="5" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="C694" s="3" t="s">
         <v>1072</v>
@@ -30183,7 +30185,7 @@
         <v>704</v>
       </c>
       <c r="B695" s="5" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="C695" s="3" t="s">
         <v>1026</v>
@@ -30194,7 +30196,7 @@
         <v>705</v>
       </c>
       <c r="B696" s="5" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="C696" s="3" t="s">
         <v>1027</v>
@@ -30205,7 +30207,7 @@
         <v>706</v>
       </c>
       <c r="B697" s="5" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="C697" s="3" t="s">
         <v>1028</v>
@@ -30216,7 +30218,7 @@
         <v>707</v>
       </c>
       <c r="B698" s="5" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="C698" s="3" t="s">
         <v>1029</v>
@@ -30227,7 +30229,7 @@
         <v>708</v>
       </c>
       <c r="B699" s="5" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="C699" s="3" t="s">
         <v>1025</v>
@@ -30238,10 +30240,10 @@
         <v>709</v>
       </c>
       <c r="B700" s="5" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="C700" s="3" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.4">
@@ -30249,7 +30251,7 @@
         <v>710</v>
       </c>
       <c r="B701" s="5" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="C701" s="3" t="s">
         <v>1128</v>
@@ -30260,7 +30262,7 @@
         <v>711</v>
       </c>
       <c r="B702" s="5" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C702" s="3" t="s">
         <v>1085</v>
@@ -30271,7 +30273,7 @@
         <v>712</v>
       </c>
       <c r="B703" s="5" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="C703" s="3" t="s">
         <v>1126</v>
@@ -30282,7 +30284,7 @@
         <v>713</v>
       </c>
       <c r="B704" s="5" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="C704" s="3" t="s">
         <v>1127</v>
@@ -30293,7 +30295,7 @@
         <v>714</v>
       </c>
       <c r="B705" s="5" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="C705" s="3" t="s">
         <v>1089</v>
@@ -30304,7 +30306,7 @@
         <v>715</v>
       </c>
       <c r="B706" s="5" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="C706" s="3" t="s">
         <v>1125</v>
@@ -30315,7 +30317,7 @@
         <v>716</v>
       </c>
       <c r="B707" s="5" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="C707" s="3" t="s">
         <v>1058</v>
@@ -30326,10 +30328,10 @@
         <v>717</v>
       </c>
       <c r="B708" s="5" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="C708" s="3" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.4">
@@ -30337,7 +30339,7 @@
         <v>722</v>
       </c>
       <c r="B709" s="5" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C709" s="3" t="s">
         <v>990</v>
@@ -30370,7 +30372,7 @@
         <v>723</v>
       </c>
       <c r="B712" s="5" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C712" s="3" t="s">
         <v>934</v>
@@ -30381,7 +30383,7 @@
         <v>724</v>
       </c>
       <c r="B713" s="5" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="C713" s="3" t="s">
         <v>955</v>
@@ -30392,7 +30394,7 @@
         <v>725</v>
       </c>
       <c r="B714" s="5" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C714" s="3" t="s">
         <v>956</v>
@@ -30403,7 +30405,7 @@
         <v>727</v>
       </c>
       <c r="B715" s="5" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="C715" s="3" t="s">
         <v>1090</v>
@@ -30414,7 +30416,7 @@
         <v>726</v>
       </c>
       <c r="B716" s="5" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C716" s="3" t="s">
         <v>1091</v>
@@ -30425,7 +30427,7 @@
         <v>728</v>
       </c>
       <c r="B717" s="5" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="C717" s="3" t="s">
         <v>1067</v>
@@ -30436,10 +30438,10 @@
         <v>729</v>
       </c>
       <c r="B718" s="5" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="C718" s="3" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.4">
@@ -30447,7 +30449,7 @@
         <v>730</v>
       </c>
       <c r="B719" s="5" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C719" s="3" t="s">
         <v>1079</v>
@@ -30458,7 +30460,7 @@
         <v>731</v>
       </c>
       <c r="B720" s="5" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C720" s="3" t="s">
         <v>1093</v>
@@ -30469,7 +30471,7 @@
         <v>732</v>
       </c>
       <c r="B721" s="5" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C721" s="3" t="s">
         <v>1114</v>
@@ -30480,7 +30482,7 @@
         <v>733</v>
       </c>
       <c r="B722" s="5" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="C722" s="3" t="s">
         <v>935</v>
@@ -30491,7 +30493,7 @@
         <v>734</v>
       </c>
       <c r="B723" s="5" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="C723" s="3" t="s">
         <v>1092</v>
@@ -30516,7 +30518,7 @@
         <v>1410</v>
       </c>
       <c r="C725" s="3" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.4">
@@ -30527,7 +30529,7 @@
         <v>1415</v>
       </c>
       <c r="C726" s="3" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.4">
@@ -30535,7 +30537,7 @@
         <v>735</v>
       </c>
       <c r="B727" s="5" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="C727" s="3" t="s">
         <v>893</v>
@@ -30546,10 +30548,10 @@
         <v>739</v>
       </c>
       <c r="B728" s="5" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="C728" s="3" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.4">
@@ -30557,7 +30559,7 @@
         <v>740</v>
       </c>
       <c r="B729" s="5" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="C729" s="3" t="s">
         <v>843</v>
@@ -30568,7 +30570,7 @@
         <v>741</v>
       </c>
       <c r="B730" s="5" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="C730" s="3" t="s">
         <v>844</v>
@@ -30579,7 +30581,7 @@
         <v>742</v>
       </c>
       <c r="B731" s="5" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="C731" s="3" t="s">
         <v>845</v>
@@ -30590,7 +30592,7 @@
         <v>743</v>
       </c>
       <c r="B732" s="5" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="C732" s="3" t="s">
         <v>846</v>
@@ -30601,7 +30603,7 @@
         <v>744</v>
       </c>
       <c r="B733" s="5" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="C733" s="3" t="s">
         <v>848</v>
@@ -30612,7 +30614,7 @@
         <v>745</v>
       </c>
       <c r="B734" s="5" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="C734" s="3" t="s">
         <v>851</v>
@@ -30623,7 +30625,7 @@
         <v>746</v>
       </c>
       <c r="B735" s="5" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="C735" s="3" t="s">
         <v>852</v>
@@ -30634,7 +30636,7 @@
         <v>760</v>
       </c>
       <c r="B736" s="5" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="C736" s="3" t="s">
         <v>853</v>
@@ -30645,7 +30647,7 @@
         <v>747</v>
       </c>
       <c r="B737" s="5" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="C737" s="3" t="s">
         <v>854</v>
@@ -30656,7 +30658,7 @@
         <v>748</v>
       </c>
       <c r="B738" s="5" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="C738" s="3" t="s">
         <v>855</v>
@@ -30667,7 +30669,7 @@
         <v>749</v>
       </c>
       <c r="B739" s="5" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="C739" s="3" t="s">
         <v>856</v>
@@ -30678,7 +30680,7 @@
         <v>750</v>
       </c>
       <c r="B740" s="5" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="C740" s="3" t="s">
         <v>849</v>
@@ -30689,7 +30691,7 @@
         <v>751</v>
       </c>
       <c r="B741" s="5" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="C741" s="3" t="s">
         <v>850</v>
@@ -30700,7 +30702,7 @@
         <v>752</v>
       </c>
       <c r="B742" s="5" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="C742" s="3" t="s">
         <v>965</v>
@@ -30711,7 +30713,7 @@
         <v>757</v>
       </c>
       <c r="B743" s="5" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="C743" s="3" t="s">
         <v>909</v>
@@ -30722,7 +30724,7 @@
         <v>756</v>
       </c>
       <c r="B744" s="5" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="C744" s="3" t="s">
         <v>911</v>
@@ -30733,7 +30735,7 @@
         <v>755</v>
       </c>
       <c r="B745" s="5" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="C745" s="3" t="s">
         <v>910</v>
@@ -30744,7 +30746,7 @@
         <v>754</v>
       </c>
       <c r="B746" s="5" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="C746" s="3" t="s">
         <v>912</v>
@@ -30755,7 +30757,7 @@
         <v>753</v>
       </c>
       <c r="B747" s="5" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="C747" s="3" t="s">
         <v>913</v>
@@ -30766,7 +30768,7 @@
         <v>758</v>
       </c>
       <c r="B748" s="5" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="C748" s="3" t="s">
         <v>1033</v>
@@ -30777,7 +30779,7 @@
         <v>759</v>
       </c>
       <c r="B749" s="5" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="C749" s="3" t="s">
         <v>1035</v>
@@ -30788,7 +30790,7 @@
         <v>761</v>
       </c>
       <c r="B750" s="5" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="C750" s="3" t="s">
         <v>857</v>
@@ -30799,7 +30801,7 @@
         <v>762</v>
       </c>
       <c r="B751" s="5" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="C751" s="3" t="s">
         <v>847</v>
@@ -30810,7 +30812,7 @@
         <v>763</v>
       </c>
       <c r="B752" s="5" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="C752" s="3" t="s">
         <v>1059</v>
@@ -30821,7 +30823,7 @@
         <v>764</v>
       </c>
       <c r="B753" s="5" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="C753" s="3" t="s">
         <v>1049</v>
@@ -30832,7 +30834,7 @@
         <v>765</v>
       </c>
       <c r="B754" s="5" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="C754" s="3" t="s">
         <v>1098</v>
@@ -30843,7 +30845,7 @@
         <v>766</v>
       </c>
       <c r="B755" s="5" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="C755" s="3" t="s">
         <v>928</v>
@@ -30854,10 +30856,10 @@
         <v>771</v>
       </c>
       <c r="B756" s="5" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C756" s="3" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.4">
@@ -30865,10 +30867,10 @@
         <v>770</v>
       </c>
       <c r="B757" s="5" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="C757" s="3" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.4">
@@ -30876,10 +30878,10 @@
         <v>769</v>
       </c>
       <c r="B758" s="5" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="C758" s="3" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.4">
@@ -30887,10 +30889,10 @@
         <v>768</v>
       </c>
       <c r="B759" s="5" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="C759" s="3" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.4">
@@ -30898,10 +30900,10 @@
         <v>767</v>
       </c>
       <c r="B760" s="5" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="C760" s="3" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.4">
@@ -30909,7 +30911,7 @@
         <v>772</v>
       </c>
       <c r="B761" s="5" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="C761" s="3" t="s">
         <v>1034</v>
@@ -30920,7 +30922,7 @@
         <v>773</v>
       </c>
       <c r="B762" s="5" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="C762" s="3" t="s">
         <v>989</v>
@@ -30931,10 +30933,10 @@
         <v>775</v>
       </c>
       <c r="B763" s="5" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="C763" s="3" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.4">
@@ -30942,7 +30944,7 @@
         <v>774</v>
       </c>
       <c r="B764" s="5" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="C764" s="3" t="s">
         <v>894</v>
@@ -30953,10 +30955,10 @@
         <v>778</v>
       </c>
       <c r="B765" s="5" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="C765" s="6" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.4">
@@ -30964,7 +30966,7 @@
         <v>777</v>
       </c>
       <c r="B766" s="5" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="C766" s="3" t="s">
         <v>1061</v>
@@ -30975,7 +30977,7 @@
         <v>776</v>
       </c>
       <c r="B767" s="5" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="C767" s="3" t="s">
         <v>1062</v>
@@ -30986,10 +30988,10 @@
         <v>779</v>
       </c>
       <c r="B768" s="5" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="C768" s="3" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.4">
@@ -30997,10 +30999,10 @@
         <v>780</v>
       </c>
       <c r="B769" s="5" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="C769" s="3" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.4">
@@ -31008,7 +31010,7 @@
         <v>781</v>
       </c>
       <c r="B770" s="5" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="C770" s="3" t="s">
         <v>919</v>
@@ -31019,10 +31021,10 @@
         <v>788</v>
       </c>
       <c r="B771" s="5" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="C771" s="3" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.4">
@@ -31030,10 +31032,10 @@
         <v>787</v>
       </c>
       <c r="B772" s="5" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="C772" s="3" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.4">
@@ -31041,10 +31043,10 @@
         <v>786</v>
       </c>
       <c r="B773" s="5" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="C773" s="3" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.4">
@@ -31052,10 +31054,10 @@
         <v>785</v>
       </c>
       <c r="B774" s="5" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="C774" s="3" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.4">
@@ -31063,10 +31065,10 @@
         <v>784</v>
       </c>
       <c r="B775" s="5" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="C775" s="3" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.4">
@@ -31074,10 +31076,10 @@
         <v>783</v>
       </c>
       <c r="B776" s="5" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="C776" s="3" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.4">
@@ -31085,10 +31087,10 @@
         <v>782</v>
       </c>
       <c r="B777" s="5" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="C777" s="3" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="778" spans="1:3" ht="38" x14ac:dyDescent="0.4">
@@ -31096,10 +31098,10 @@
         <v>791</v>
       </c>
       <c r="B778" s="5" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="C778" s="3" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.4">
@@ -31107,10 +31109,10 @@
         <v>790</v>
       </c>
       <c r="B779" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="C779" s="3" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.4">
@@ -31118,10 +31120,10 @@
         <v>789</v>
       </c>
       <c r="B780" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C780" s="3" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.4">
@@ -31129,7 +31131,7 @@
         <v>792</v>
       </c>
       <c r="B781" s="5" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="C781" s="3" t="s">
         <v>923</v>
@@ -31140,7 +31142,7 @@
         <v>793</v>
       </c>
       <c r="B782" s="5" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="C782" s="3" t="s">
         <v>921</v>
@@ -31151,7 +31153,7 @@
         <v>794</v>
       </c>
       <c r="B783" s="5" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="C783" s="3" t="s">
         <v>922</v>
@@ -31162,10 +31164,10 @@
         <v>803</v>
       </c>
       <c r="B784" s="5" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="C784" s="3" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.4">
@@ -31173,10 +31175,10 @@
         <v>802</v>
       </c>
       <c r="B785" s="5" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="C785" s="3" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.4">
@@ -31187,7 +31189,7 @@
         <v>1374</v>
       </c>
       <c r="C786" s="3" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.4">
@@ -31198,7 +31200,7 @@
         <v>1375</v>
       </c>
       <c r="C787" s="3" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.4">
@@ -31209,7 +31211,7 @@
         <v>1376</v>
       </c>
       <c r="C788" s="3" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.4">
@@ -31220,7 +31222,7 @@
         <v>1377</v>
       </c>
       <c r="C789" s="3" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="790" spans="1:3" x14ac:dyDescent="0.4">
@@ -31228,10 +31230,10 @@
         <v>797</v>
       </c>
       <c r="B790" s="5" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="C790" s="3" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.4">
@@ -31239,10 +31241,10 @@
         <v>796</v>
       </c>
       <c r="B791" s="5" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="C791" s="3" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.4">
@@ -31250,10 +31252,10 @@
         <v>795</v>
       </c>
       <c r="B792" s="5" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="C792" s="3" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.4">
@@ -31261,7 +31263,7 @@
         <v>804</v>
       </c>
       <c r="B793" s="5" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="C793" s="3" t="s">
         <v>920</v>
@@ -31272,10 +31274,10 @@
         <v>807</v>
       </c>
       <c r="B794" s="5" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="C794" s="3" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.4">
@@ -31283,10 +31285,10 @@
         <v>806</v>
       </c>
       <c r="B795" s="5" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="C795" s="3" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="796" spans="1:3" x14ac:dyDescent="0.4">
@@ -31294,10 +31296,10 @@
         <v>805</v>
       </c>
       <c r="B796" s="5" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="C796" s="3" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.4">
@@ -31305,7 +31307,7 @@
         <v>808</v>
       </c>
       <c r="B797" s="5" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="C797" s="3" t="s">
         <v>1050</v>
@@ -31316,10 +31318,10 @@
         <v>809</v>
       </c>
       <c r="B798" s="5" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="C798" s="3" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.4">
@@ -31327,10 +31329,10 @@
         <v>813</v>
       </c>
       <c r="B799" s="5" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="C799" s="3" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.4">
@@ -31338,10 +31340,10 @@
         <v>812</v>
       </c>
       <c r="B800" s="5" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="C800" s="3" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="801" spans="1:3" ht="38" x14ac:dyDescent="0.4">
@@ -31349,7 +31351,7 @@
         <v>811</v>
       </c>
       <c r="B801" s="5" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="C801" s="3" t="s">
         <v>1040</v>
@@ -31360,7 +31362,7 @@
         <v>810</v>
       </c>
       <c r="B802" s="5" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="C802" s="3" t="s">
         <v>1041</v>
@@ -31371,10 +31373,10 @@
         <v>814</v>
       </c>
       <c r="B803" s="5" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C803" s="3" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.4">
@@ -31382,10 +31384,10 @@
         <v>815</v>
       </c>
       <c r="B804" s="5" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="C804" s="3" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.4">
@@ -31393,10 +31395,10 @@
         <v>816</v>
       </c>
       <c r="B805" s="5" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="C805" s="3" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.4">
@@ -31404,10 +31406,10 @@
         <v>817</v>
       </c>
       <c r="B806" s="5" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="C806" s="3" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="807" spans="1:3" x14ac:dyDescent="0.4">
@@ -31415,10 +31417,10 @@
         <v>818</v>
       </c>
       <c r="B807" s="5" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C807" s="3" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.4">
@@ -31426,7 +31428,7 @@
         <v>819</v>
       </c>
       <c r="B808" s="5" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="C808" s="3" t="s">
         <v>995</v>
@@ -31434,1069 +31436,1080 @@
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A809" s="4" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="B809" s="5" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="C809" s="3" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A810" s="4" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="B810" s="5" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="C810" s="3" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A811" s="4" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B811" s="5" t="s">
+        <v>2272</v>
+      </c>
+      <c r="C811" s="3" t="s">
         <v>2271</v>
-      </c>
-      <c r="B811" s="5" t="s">
-        <v>2273</v>
-      </c>
-      <c r="C811" s="3" t="s">
-        <v>2272</v>
       </c>
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A812" s="4" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B812" s="5" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C812" s="3" t="s">
         <v>2275</v>
-      </c>
-      <c r="B812" s="5" t="s">
-        <v>2274</v>
-      </c>
-      <c r="C812" s="3" t="s">
-        <v>2276</v>
       </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A813" s="4" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B813" s="5" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C813" s="3" t="s">
         <v>2286</v>
-      </c>
-      <c r="B813" s="5" t="s">
-        <v>2285</v>
-      </c>
-      <c r="C813" s="3" t="s">
-        <v>2287</v>
       </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A814" s="4" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B814" s="5" t="s">
         <v>2282</v>
       </c>
-      <c r="B814" s="5" t="s">
+      <c r="C814" s="3" t="s">
         <v>2283</v>
-      </c>
-      <c r="C814" s="3" t="s">
-        <v>2284</v>
       </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A815" s="4" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B815" s="5" t="s">
         <v>2295</v>
       </c>
-      <c r="B815" s="5" t="s">
-        <v>2296</v>
-      </c>
       <c r="C815" s="3" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A816" s="4" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="B816" s="5" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="C816" s="3" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A817" s="4" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="B817" s="5" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="C817" s="3" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A818" s="4" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="B818" s="5" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="C818" s="3" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A819" s="4" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="B819" s="5" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="C819" s="3" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A820" s="4" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="B820" s="5" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="C820" s="3" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A821" s="4" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="B821" s="5" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="C821" s="3" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A822" s="4" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="B822" s="5" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="C822" s="3" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="823" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A823" s="4" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="B823" s="5" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="C823" s="3" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A824" s="4" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="B824" s="5" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="C824" s="3" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A825" s="4" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="B825" s="5" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="C825" s="3" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A826" s="4" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B826" s="5" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C826" s="3" t="s">
         <v>2321</v>
-      </c>
-      <c r="B826" s="5" t="s">
-        <v>2323</v>
-      </c>
-      <c r="C826" s="3" t="s">
-        <v>2322</v>
       </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A827" s="4" t="s">
+        <v>2332</v>
+      </c>
+      <c r="B827" s="5" t="s">
         <v>2333</v>
       </c>
-      <c r="B827" s="5" t="s">
-        <v>2334</v>
-      </c>
       <c r="C827" s="3" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A828" s="4" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="B828" s="5" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="C828" s="3" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A829" s="4" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="B829" s="5" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="C829" s="3" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A830" s="4" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="B830" s="5" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="C830" s="3" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A831" s="4" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="B831" s="5" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="C831" s="3" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="832" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A832" s="4" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B832" s="5" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="C832" s="3" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="833" spans="1:3" ht="95" x14ac:dyDescent="0.4">
       <c r="A833" s="4" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B833" s="5" t="s">
         <v>2342</v>
       </c>
-      <c r="B833" s="5" t="s">
+      <c r="C833" s="3" t="s">
         <v>2343</v>
-      </c>
-      <c r="C833" s="3" t="s">
-        <v>2344</v>
       </c>
     </row>
     <row r="834" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A834" s="4" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B834" s="5" t="s">
         <v>2345</v>
       </c>
-      <c r="B834" s="5" t="s">
+      <c r="C834" s="3" t="s">
         <v>2346</v>
-      </c>
-      <c r="C834" s="3" t="s">
-        <v>2347</v>
       </c>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A835" s="4" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B835" s="5" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C835" s="3" t="s">
         <v>2353</v>
-      </c>
-      <c r="B835" s="5" t="s">
-        <v>2355</v>
-      </c>
-      <c r="C835" s="3" t="s">
-        <v>2354</v>
       </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A836" s="4" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B836" s="5" t="s">
         <v>2356</v>
       </c>
-      <c r="B836" s="5" t="s">
+      <c r="C836" s="3" t="s">
         <v>2357</v>
-      </c>
-      <c r="C836" s="3" t="s">
-        <v>2358</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A837" s="4" t="s">
+        <v>2358</v>
+      </c>
+      <c r="B837" s="5" t="s">
+        <v>2360</v>
+      </c>
+      <c r="C837" s="3" t="s">
         <v>2359</v>
-      </c>
-      <c r="B837" s="5" t="s">
-        <v>2361</v>
-      </c>
-      <c r="C837" s="3" t="s">
-        <v>2360</v>
       </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A838" s="4" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="B838" s="5" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="C838" s="3" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A839" s="4" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B839" s="5" t="s">
         <v>2365</v>
       </c>
-      <c r="B839" s="5" t="s">
+      <c r="C839" s="3" t="s">
         <v>2366</v>
-      </c>
-      <c r="C839" s="3" t="s">
-        <v>2367</v>
       </c>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A840" s="4" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B840" s="5" t="s">
         <v>2368</v>
       </c>
-      <c r="B840" s="5" t="s">
+      <c r="C840" s="3" t="s">
         <v>2369</v>
-      </c>
-      <c r="C840" s="3" t="s">
-        <v>2370</v>
       </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A841" s="4" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B841" s="5" t="s">
         <v>2371</v>
       </c>
-      <c r="B841" s="5" t="s">
+      <c r="C841" s="3" t="s">
         <v>2372</v>
-      </c>
-      <c r="C841" s="3" t="s">
-        <v>2373</v>
       </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A842" s="4" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B842" s="5" t="s">
         <v>2374</v>
       </c>
-      <c r="B842" s="5" t="s">
+      <c r="C842" s="3" t="s">
         <v>2375</v>
-      </c>
-      <c r="C842" s="3" t="s">
-        <v>2376</v>
       </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A843" s="4" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B843" s="5" t="s">
         <v>2377</v>
       </c>
-      <c r="B843" s="5" t="s">
+      <c r="C843" s="3" t="s">
         <v>2378</v>
-      </c>
-      <c r="C843" s="3" t="s">
-        <v>2379</v>
       </c>
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A844" s="4" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B844" s="5" t="s">
         <v>2380</v>
       </c>
-      <c r="B844" s="5" t="s">
-        <v>2381</v>
-      </c>
       <c r="C844" s="3" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A845" s="4" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B845" s="5" t="s">
         <v>2382</v>
       </c>
-      <c r="B845" s="5" t="s">
+      <c r="C845" s="3" t="s">
         <v>2383</v>
-      </c>
-      <c r="C845" s="3" t="s">
-        <v>2384</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A846" s="4" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="B846" s="5" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C846" s="3" t="s">
         <v>2369</v>
-      </c>
-      <c r="C846" s="3" t="s">
-        <v>2370</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A847" s="4" t="s">
+        <v>2385</v>
+      </c>
+      <c r="B847" s="5" t="s">
         <v>2386</v>
       </c>
-      <c r="B847" s="5" t="s">
+      <c r="C847" s="3" t="s">
         <v>2387</v>
-      </c>
-      <c r="C847" s="3" t="s">
-        <v>2388</v>
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A848" s="4" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B848" s="5" t="s">
         <v>2389</v>
       </c>
-      <c r="B848" s="5" t="s">
-        <v>2390</v>
-      </c>
       <c r="C848" s="3" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A849" s="4" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B849" s="5" t="s">
         <v>2391</v>
       </c>
-      <c r="B849" s="5" t="s">
+      <c r="C849" s="3" t="s">
         <v>2392</v>
-      </c>
-      <c r="C849" s="3" t="s">
-        <v>2393</v>
       </c>
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A850" s="4" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B850" s="5" t="s">
+        <v>2393</v>
+      </c>
+      <c r="C850" s="3" t="s">
         <v>2395</v>
-      </c>
-      <c r="B850" s="5" t="s">
-        <v>2394</v>
-      </c>
-      <c r="C850" s="3" t="s">
-        <v>2396</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A851" s="4" t="s">
+        <v>2396</v>
+      </c>
+      <c r="B851" s="5" t="s">
         <v>2397</v>
       </c>
-      <c r="B851" s="5" t="s">
+      <c r="C851" s="3" t="s">
         <v>2398</v>
-      </c>
-      <c r="C851" s="3" t="s">
-        <v>2399</v>
       </c>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A852" s="4" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B852" s="5" t="s">
         <v>2400</v>
       </c>
-      <c r="B852" s="5" t="s">
+      <c r="C852" s="3" t="s">
         <v>2401</v>
-      </c>
-      <c r="C852" s="3" t="s">
-        <v>2402</v>
       </c>
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A853" s="4" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="B853" s="5" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="C853" s="3" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A854" s="4" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B854" s="5" t="s">
+        <v>2444</v>
+      </c>
+      <c r="C854" s="3" t="s">
         <v>2406</v>
-      </c>
-      <c r="B854" s="5" t="s">
-        <v>2445</v>
-      </c>
-      <c r="C854" s="3" t="s">
-        <v>2407</v>
       </c>
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A855" s="4" t="s">
+        <v>2407</v>
+      </c>
+      <c r="B855" s="5" t="s">
+        <v>2445</v>
+      </c>
+      <c r="C855" s="3" t="s">
         <v>2408</v>
-      </c>
-      <c r="B855" s="5" t="s">
-        <v>2446</v>
-      </c>
-      <c r="C855" s="3" t="s">
-        <v>2409</v>
       </c>
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A856" s="4" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B856" s="5" t="s">
+        <v>2446</v>
+      </c>
+      <c r="C856" s="3" t="s">
         <v>2410</v>
-      </c>
-      <c r="B856" s="5" t="s">
-        <v>2447</v>
-      </c>
-      <c r="C856" s="3" t="s">
-        <v>2411</v>
       </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A857" s="4" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B857" s="5" t="s">
+        <v>2447</v>
+      </c>
+      <c r="C857" s="3" t="s">
         <v>2413</v>
-      </c>
-      <c r="B857" s="5" t="s">
-        <v>2448</v>
-      </c>
-      <c r="C857" s="3" t="s">
-        <v>2414</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A858" s="4" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="B858" s="5" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="C858" s="3" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A859" s="4" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B859" s="5" t="s">
+        <v>2449</v>
+      </c>
+      <c r="C859" s="3" t="s">
         <v>2416</v>
-      </c>
-      <c r="B859" s="5" t="s">
-        <v>2450</v>
-      </c>
-      <c r="C859" s="3" t="s">
-        <v>2417</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A860" s="4" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B860" s="5" t="s">
+        <v>2450</v>
+      </c>
+      <c r="C860" s="3" t="s">
         <v>2418</v>
-      </c>
-      <c r="B860" s="5" t="s">
-        <v>2451</v>
-      </c>
-      <c r="C860" s="3" t="s">
-        <v>2419</v>
       </c>
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A861" s="4" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B861" s="5" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C861" s="3" t="s">
         <v>2420</v>
-      </c>
-      <c r="B861" s="5" t="s">
-        <v>2452</v>
-      </c>
-      <c r="C861" s="3" t="s">
-        <v>2421</v>
       </c>
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A862" s="4" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="B862" s="5" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="C862" s="3" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A863" s="4" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="B863" s="5" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="C863" s="3" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A864" s="4" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="B864" s="5" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="C864" s="3" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A865" s="4" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="B865" s="5" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="C865" s="3" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A866" s="4" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="B866" s="5" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="C866" s="3" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A867" s="4" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="B867" s="5" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="C867" s="3" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A868" s="4" t="s">
+        <v>2432</v>
+      </c>
+      <c r="B868" s="5" t="s">
+        <v>2458</v>
+      </c>
+      <c r="C868" s="3" t="s">
         <v>2433</v>
-      </c>
-      <c r="B868" s="5" t="s">
-        <v>2459</v>
-      </c>
-      <c r="C868" s="3" t="s">
-        <v>2434</v>
       </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A869" s="4" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="B869" s="5" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="C869" s="3" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A870" s="4" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B870" s="5" t="s">
+        <v>2460</v>
+      </c>
+      <c r="C870" s="3" t="s">
         <v>2436</v>
-      </c>
-      <c r="B870" s="5" t="s">
-        <v>2461</v>
-      </c>
-      <c r="C870" s="3" t="s">
-        <v>2437</v>
       </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A871" s="4" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B871" s="5" t="s">
+        <v>2461</v>
+      </c>
+      <c r="C871" s="3" t="s">
         <v>2438</v>
-      </c>
-      <c r="B871" s="5" t="s">
-        <v>2462</v>
-      </c>
-      <c r="C871" s="3" t="s">
-        <v>2439</v>
       </c>
     </row>
     <row r="872" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A872" s="4" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B872" s="5" t="s">
+        <v>2462</v>
+      </c>
+      <c r="C872" s="3" t="s">
         <v>2440</v>
-      </c>
-      <c r="B872" s="5" t="s">
-        <v>2463</v>
-      </c>
-      <c r="C872" s="3" t="s">
-        <v>2441</v>
       </c>
     </row>
     <row r="873" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A873" s="4" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B873" s="5" t="s">
+        <v>2463</v>
+      </c>
+      <c r="C873" s="3" t="s">
         <v>2442</v>
-      </c>
-      <c r="B873" s="5" t="s">
-        <v>2464</v>
-      </c>
-      <c r="C873" s="3" t="s">
-        <v>2443</v>
       </c>
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A874" s="4" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B874" s="5" t="s">
+        <v>2466</v>
+      </c>
+      <c r="C874" s="3" t="s">
         <v>2465</v>
-      </c>
-      <c r="B874" s="5" t="s">
-        <v>2467</v>
-      </c>
-      <c r="C874" s="3" t="s">
-        <v>2466</v>
       </c>
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A875" s="4" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B875" s="5" t="s">
         <v>2468</v>
       </c>
-      <c r="B875" s="5" t="s">
+      <c r="C875" s="3" t="s">
         <v>2469</v>
-      </c>
-      <c r="C875" s="3" t="s">
-        <v>2470</v>
       </c>
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A876" s="4" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="B876" s="5" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="C876" s="3" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="877" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A877" s="4" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="B877" s="5" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="C877" s="3" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="878" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A878" s="4" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="B878" s="5" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="C878" s="3" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A879" s="4" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="B879" s="5" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="C879" s="3" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A880" s="4" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="B880" s="5" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="C880" s="3" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A881" s="4" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B881" s="5" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="C881" s="3" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A882" s="4" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="B882" s="5" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="C882" s="3" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="883" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A883" s="4" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="B883" s="5" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="C883" s="3" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="884" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A884" s="4" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="B884" s="5" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="C884" s="3" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="885" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A885" s="4" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="B885" s="5" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="C885" s="3" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="886" spans="1:3" ht="285" x14ac:dyDescent="0.4">
       <c r="A886" s="4" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B886" s="5" t="s">
         <v>2542</v>
       </c>
-      <c r="B886" s="5" t="s">
+      <c r="C886" s="3" t="s">
         <v>2543</v>
-      </c>
-      <c r="C886" s="3" t="s">
-        <v>2544</v>
       </c>
     </row>
     <row r="887" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A887" s="4" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="B887" s="5" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="C887" s="3" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="888" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A888" s="4" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="B888" s="5" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="C888" s="3" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="889" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A889" s="4" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="B889" s="5" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="C889" s="3" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="890" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A890" s="4" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="B890" s="5" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="C890" s="3" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A891" s="4" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="B891" s="5" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="C891" s="3" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A892" s="4" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="B892" s="5" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="C892" s="3" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A893" s="4" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="B893" s="5" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="C893" s="3" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="894" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A894" s="4" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="B894" s="5" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="C894" s="3" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="895" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A895" s="4" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="B895" s="5" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="C895" s="3" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="896" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A896" s="4" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="B896" s="5" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="C896" s="3" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="897" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A897" s="4" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="B897" s="5" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="C897" s="3" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="898" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A898" s="4" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="B898" s="5" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="C898" s="3" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="899" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A899" s="4" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B899" s="5" t="s">
+        <v>2531</v>
+      </c>
+      <c r="C899" s="3" t="s">
         <v>2530</v>
-      </c>
-      <c r="B899" s="5" t="s">
-        <v>2532</v>
-      </c>
-      <c r="C899" s="3" t="s">
-        <v>2531</v>
       </c>
     </row>
     <row r="900" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A900" s="4" t="s">
+        <v>2532</v>
+      </c>
+      <c r="B900" s="5" t="s">
         <v>2533</v>
       </c>
-      <c r="B900" s="5" t="s">
+      <c r="C900" s="3" t="s">
         <v>2534</v>
-      </c>
-      <c r="C900" s="3" t="s">
-        <v>2535</v>
       </c>
     </row>
     <row r="901" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A901" s="4" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B901" s="5" t="s">
         <v>2536</v>
       </c>
-      <c r="B901" s="5" t="s">
+      <c r="C901" s="3" t="s">
         <v>2537</v>
-      </c>
-      <c r="C901" s="3" t="s">
-        <v>2538</v>
       </c>
     </row>
     <row r="902" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A902" s="4" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B902" s="5" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C902" s="3" t="s">
         <v>2540</v>
-      </c>
-      <c r="B902" s="5" t="s">
-        <v>2539</v>
-      </c>
-      <c r="C902" s="3" t="s">
-        <v>2541</v>
       </c>
     </row>
     <row r="903" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A903" s="4" t="s">
+        <v>2544</v>
+      </c>
+      <c r="B903" s="5" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C903" s="3" t="s">
         <v>2545</v>
-      </c>
-      <c r="B903" s="5" t="s">
-        <v>2547</v>
-      </c>
-      <c r="C903" s="3" t="s">
-        <v>2546</v>
       </c>
     </row>
     <row r="904" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A904" s="4" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B904" s="5" t="s">
+        <v>2549</v>
+      </c>
+      <c r="C904" s="3" t="s">
         <v>2548</v>
-      </c>
-      <c r="B904" s="5" t="s">
-        <v>2550</v>
-      </c>
-      <c r="C904" s="3" t="s">
-        <v>2549</v>
       </c>
     </row>
     <row r="905" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A905" s="4" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B905" s="5" t="s">
+        <v>2550</v>
+      </c>
+      <c r="C905" s="3" t="s">
         <v>2552</v>
       </c>
-      <c r="B905" s="5" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C905" s="3" t="s">
-        <v>2553</v>
+    </row>
+    <row r="906" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A906" s="4" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B906" s="5" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C906" s="3" t="s">
+        <v>2556</v>
       </c>
     </row>
     <row r="910" spans="1:3" x14ac:dyDescent="0.4">

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93ECEF60-CDCB-4538-86F2-A7F2127B1623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D00EAD0-2659-4FFF-A44E-0EFE74D84F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="2557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2715" uniqueCount="2560">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -22138,6 +22138,17 @@
   </si>
   <si>
     <t>Draw all ranges except for weapons subject to elevation using ellipses</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TipDialogPrevious</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Previous tip</t>
+  </si>
+  <si>
+    <t>上一提示</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -32512,6 +32523,17 @@
         <v>2556</v>
       </c>
     </row>
+    <row r="907" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A907" s="4" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B907" s="5" t="s">
+        <v>2559</v>
+      </c>
+      <c r="C907" s="3" t="s">
+        <v>2558</v>
+      </c>
+    </row>
     <row r="910" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A910" s="7"/>
     </row>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D437C2-89E4-4CD1-8F9A-0CF7EE114333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E213F9B4-3A27-4782-BB93-B4F7DA5E228B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1900" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="2557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="2566">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -22102,13 +22102,44 @@
   <si>
     <t>上一提示</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lock layout</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hide toolbar</t>
+  </si>
+  <si>
+    <t>Reset toolbar</t>
+  </si>
+  <si>
+    <t>ToolbarMenu.LockLayout</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ToolbarMenu.HideToolbar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ToolbarMenu.ResetToolbar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>锁定布局</t>
+  </si>
+  <si>
+    <t>隐藏工具栏</t>
+  </si>
+  <si>
+    <t>重置工具栏</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -22173,14 +22204,6 @@
       <family val="1"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -22214,7 +22237,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -22233,9 +22256,6 @@
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -22518,7 +22538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C916"/>
+  <dimension ref="A1:C909"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="4" customWidth="1"/>
@@ -32475,29 +32495,38 @@
         <v>2555</v>
       </c>
     </row>
+    <row r="907" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A907" s="4" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B907" s="5" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C907" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A908" s="4" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B908" s="5" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C908" s="3" t="s">
+        <v>2558</v>
+      </c>
+    </row>
     <row r="909" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A909" s="7"/>
-    </row>
-    <row r="910" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A910" s="7"/>
-    </row>
-    <row r="911" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A911" s="7"/>
-    </row>
-    <row r="912" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A912" s="7"/>
-    </row>
-    <row r="913" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A913" s="7"/>
-    </row>
-    <row r="914" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A914" s="7"/>
-    </row>
-    <row r="915" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A915" s="7"/>
-    </row>
-    <row r="916" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A916" s="7"/>
+      <c r="A909" s="4" t="s">
+        <v>2562</v>
+      </c>
+      <c r="B909" s="5" t="s">
+        <v>2565</v>
+      </c>
+      <c r="C909" s="3" t="s">
+        <v>2559</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E213F9B4-3A27-4782-BB93-B4F7DA5E228B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3ACBBD4-98DB-49D6-9496-EE427122F492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1900" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="2566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="2575">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -22133,6 +22133,36 @@
   </si>
   <si>
     <t>重置工具栏</t>
+  </si>
+  <si>
+    <t>0 - No spotlight</t>
+  </si>
+  <si>
+    <t>1 - Rules.ini setting</t>
+  </si>
+  <si>
+    <t>2 - Circle / Direction</t>
+  </si>
+  <si>
+    <t>StructSpotlight.0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StructSpotlight.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StructSpotlight.2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0 - 无聚光灯</t>
+  </si>
+  <si>
+    <t>1 - 使用Rules设置</t>
+  </si>
+  <si>
+    <t>2 - 圆/目标聚光灯</t>
   </si>
 </sst>
 </file>
@@ -22538,7 +22568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C909"/>
+  <dimension ref="A1:C912"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="4" customWidth="1"/>
@@ -32528,6 +32558,39 @@
         <v>2559</v>
       </c>
     </row>
+    <row r="910" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A910" s="4" t="s">
+        <v>2569</v>
+      </c>
+      <c r="B910" s="5" t="s">
+        <v>2572</v>
+      </c>
+      <c r="C910" s="3" t="s">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A911" s="4" t="s">
+        <v>2570</v>
+      </c>
+      <c r="B911" s="5" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C911" s="3" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A912" s="4" t="s">
+        <v>2571</v>
+      </c>
+      <c r="B912" s="5" t="s">
+        <v>2574</v>
+      </c>
+      <c r="C912" s="3" t="s">
+        <v>2568</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3ACBBD4-98DB-49D6-9496-EE427122F492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9B63EB-11C7-48F9-8BF9-817C5EA2DFE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2240" yWindow="2240" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="2575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2736" uniqueCount="2579">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -22163,6 +22163,20 @@
   </si>
   <si>
     <t>2 - 圆/目标聚光灯</t>
+  </si>
+  <si>
+    <t>TechnoOptionsCaption</t>
+  </si>
+  <si>
+    <t>通用格式刷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Techno Property Brush</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropertyBrushTechno</t>
   </si>
 </sst>
 </file>
@@ -22568,7 +22582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C912"/>
+  <dimension ref="A1:C914"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="4" customWidth="1"/>
@@ -32591,6 +32605,28 @@
         <v>2568</v>
       </c>
     </row>
+    <row r="913" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A913" s="4" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B913" s="5" t="s">
+        <v>2576</v>
+      </c>
+      <c r="C913" s="3" t="s">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A914" s="4" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B914" s="5" t="s">
+        <v>2576</v>
+      </c>
+      <c r="C914" s="3" t="s">
+        <v>2577</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9B63EB-11C7-48F9-8BF9-817C5EA2DFE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543A9372-2DA2-478E-8EDA-A61F04A609F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2240" yWindow="2240" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2736" uniqueCount="2579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2739" uniqueCount="2582">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -22177,6 +22177,16 @@
   </si>
   <si>
     <t>PropertyBrushTechno</t>
+  </si>
+  <si>
+    <t>Options.DisplayBridgeOverlay</t>
+  </si>
+  <si>
+    <t>Display invisible bridge overlays in numbers</t>
+  </si>
+  <si>
+    <t>以数字显示不可见的桥梁覆盖物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -22582,7 +22592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C914"/>
+  <dimension ref="A1:C915"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="4" customWidth="1"/>
@@ -32627,6 +32637,17 @@
         <v>2577</v>
       </c>
     </row>
+    <row r="915" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A915" s="4" t="s">
+        <v>2579</v>
+      </c>
+      <c r="B915" s="5" t="s">
+        <v>2581</v>
+      </c>
+      <c r="C915" s="3" t="s">
+        <v>2580</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543A9372-2DA2-478E-8EDA-A61F04A609F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C5F01F-8546-4655-9C79-19BF3263C3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2240" yWindow="2240" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2739" uniqueCount="2582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2742" uniqueCount="2585">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -22186,6 +22186,17 @@
   </si>
   <si>
     <t>以数字显示不可见的桥梁覆盖物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disable Auto Connect Wall</t>
+  </si>
+  <si>
+    <t>Menu.Options.DisableAutoConnectWall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>禁止自动连接围墙</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -22592,7 +22603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C915"/>
+  <dimension ref="A1:C916"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="4" customWidth="1"/>
@@ -32648,6 +32659,17 @@
         <v>2580</v>
       </c>
     </row>
+    <row r="916" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A916" s="4" t="s">
+        <v>2583</v>
+      </c>
+      <c r="B916" s="5" t="s">
+        <v>2584</v>
+      </c>
+      <c r="C916" s="3" t="s">
+        <v>2582</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C5F01F-8546-4655-9C79-19BF3263C3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A69430B-E5AA-469B-9BDF-BE3188D36056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2240" yWindow="2240" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2742" uniqueCount="2585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="2588">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -22198,6 +22198,15 @@
   <si>
     <t>禁止自动连接围墙</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.LoadGameFromMapFolder.OnInit</t>
+  </si>
+  <si>
+    <t>Load game resources from map folder when directly open map</t>
+  </si>
+  <si>
+    <t>双击打开地图文件时，从地图目录加载资源文件</t>
   </si>
 </sst>
 </file>
@@ -22603,7 +22612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C916"/>
+  <dimension ref="A1:C917"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="4" customWidth="1"/>
@@ -32670,6 +32679,17 @@
         <v>2582</v>
       </c>
     </row>
+    <row r="917" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A917" s="4" t="s">
+        <v>2585</v>
+      </c>
+      <c r="B917" s="5" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C917" s="3" t="s">
+        <v>2586</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A69430B-E5AA-469B-9BDF-BE3188D36056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90139EE7-E951-4B92-92C1-BB771D05B9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2240" yWindow="2240" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="2588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="2591">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -22207,6 +22207,16 @@
   </si>
   <si>
     <t>双击打开地图文件时，从地图目录加载资源文件</t>
+  </si>
+  <si>
+    <t>Enable veinhole logic</t>
+  </si>
+  <si>
+    <t>Options.EnableVeinholeLogic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>启用泰伯利亚藤蔓（蔓孔）逻辑</t>
   </si>
 </sst>
 </file>
@@ -22612,7 +22622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C917"/>
+  <dimension ref="A1:C918"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="4" customWidth="1"/>
@@ -32690,6 +32700,17 @@
         <v>2586</v>
       </c>
     </row>
+    <row r="918" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A918" s="4" t="s">
+        <v>2589</v>
+      </c>
+      <c r="B918" s="5" t="s">
+        <v>2590</v>
+      </c>
+      <c r="C918" s="3" t="s">
+        <v>2588</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90139EE7-E951-4B92-92C1-BB771D05B9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80AA0536-FF3B-4C9E-88B6-8E7DE506D008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2240" yWindow="2240" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21378,9 +21378,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Display remapble colors of overlays</t>
-  </si>
-  <si>
     <t>显示围墙覆盖物的所属色</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -22217,6 +22214,10 @@
   </si>
   <si>
     <t>启用泰伯利亚藤蔓（蔓孔）逻辑</t>
+  </si>
+  <si>
+    <t>Display remapable colors of overlays</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -30219,7 +30220,7 @@
         <v>701</v>
       </c>
       <c r="B692" s="5" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C692" s="3" t="s">
         <v>1100</v>
@@ -31803,183 +31804,183 @@
         <v>2355</v>
       </c>
       <c r="B836" s="5" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="C836" s="3" t="s">
-        <v>2356</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A837" s="4" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="B837" s="5" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="C837" s="3" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A838" s="4" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B838" s="5" t="s">
         <v>2361</v>
       </c>
-      <c r="B838" s="5" t="s">
+      <c r="C838" s="3" t="s">
         <v>2362</v>
-      </c>
-      <c r="C838" s="3" t="s">
-        <v>2363</v>
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A839" s="4" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B839" s="5" t="s">
         <v>2364</v>
       </c>
-      <c r="B839" s="5" t="s">
+      <c r="C839" s="3" t="s">
         <v>2365</v>
-      </c>
-      <c r="C839" s="3" t="s">
-        <v>2366</v>
       </c>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A840" s="4" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B840" s="5" t="s">
         <v>2367</v>
       </c>
-      <c r="B840" s="5" t="s">
+      <c r="C840" s="3" t="s">
         <v>2368</v>
-      </c>
-      <c r="C840" s="3" t="s">
-        <v>2369</v>
       </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A841" s="4" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B841" s="5" t="s">
         <v>2370</v>
       </c>
-      <c r="B841" s="5" t="s">
+      <c r="C841" s="3" t="s">
         <v>2371</v>
-      </c>
-      <c r="C841" s="3" t="s">
-        <v>2372</v>
       </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A842" s="4" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B842" s="5" t="s">
         <v>2373</v>
       </c>
-      <c r="B842" s="5" t="s">
+      <c r="C842" s="3" t="s">
         <v>2374</v>
-      </c>
-      <c r="C842" s="3" t="s">
-        <v>2375</v>
       </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A843" s="4" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B843" s="5" t="s">
         <v>2376</v>
       </c>
-      <c r="B843" s="5" t="s">
-        <v>2377</v>
-      </c>
       <c r="C843" s="3" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A844" s="4" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B844" s="5" t="s">
         <v>2378</v>
       </c>
-      <c r="B844" s="5" t="s">
+      <c r="C844" s="3" t="s">
         <v>2379</v>
-      </c>
-      <c r="C844" s="3" t="s">
-        <v>2380</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A845" s="4" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="B845" s="5" t="s">
+        <v>2364</v>
+      </c>
+      <c r="C845" s="3" t="s">
         <v>2365</v>
-      </c>
-      <c r="C845" s="3" t="s">
-        <v>2366</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A846" s="4" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B846" s="5" t="s">
         <v>2382</v>
       </c>
-      <c r="B846" s="5" t="s">
+      <c r="C846" s="3" t="s">
         <v>2383</v>
-      </c>
-      <c r="C846" s="3" t="s">
-        <v>2384</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A847" s="4" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B847" s="5" t="s">
         <v>2385</v>
       </c>
-      <c r="B847" s="5" t="s">
-        <v>2386</v>
-      </c>
       <c r="C847" s="3" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A848" s="4" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B848" s="5" t="s">
         <v>2387</v>
       </c>
-      <c r="B848" s="5" t="s">
+      <c r="C848" s="3" t="s">
         <v>2388</v>
-      </c>
-      <c r="C848" s="3" t="s">
-        <v>2389</v>
       </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A849" s="4" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B849" s="5" t="s">
+        <v>2389</v>
+      </c>
+      <c r="C849" s="3" t="s">
         <v>2391</v>
-      </c>
-      <c r="B849" s="5" t="s">
-        <v>2390</v>
-      </c>
-      <c r="C849" s="3" t="s">
-        <v>2392</v>
       </c>
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A850" s="4" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B850" s="5" t="s">
         <v>2393</v>
       </c>
-      <c r="B850" s="5" t="s">
+      <c r="C850" s="3" t="s">
         <v>2394</v>
-      </c>
-      <c r="C850" s="3" t="s">
-        <v>2395</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A851" s="4" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B851" s="5" t="s">
         <v>2396</v>
       </c>
-      <c r="B851" s="5" t="s">
+      <c r="C851" s="3" t="s">
         <v>2397</v>
-      </c>
-      <c r="C851" s="3" t="s">
-        <v>2398</v>
       </c>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A852" s="4" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="B852" s="5" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="C852" s="3" t="s">
         <v>1898</v>
@@ -31987,728 +31988,728 @@
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A853" s="4" t="s">
+        <v>2401</v>
+      </c>
+      <c r="B853" s="5" t="s">
+        <v>2440</v>
+      </c>
+      <c r="C853" s="3" t="s">
         <v>2402</v>
-      </c>
-      <c r="B853" s="5" t="s">
-        <v>2441</v>
-      </c>
-      <c r="C853" s="3" t="s">
-        <v>2403</v>
       </c>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A854" s="4" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B854" s="5" t="s">
+        <v>2441</v>
+      </c>
+      <c r="C854" s="3" t="s">
         <v>2404</v>
-      </c>
-      <c r="B854" s="5" t="s">
-        <v>2442</v>
-      </c>
-      <c r="C854" s="3" t="s">
-        <v>2405</v>
       </c>
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A855" s="4" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B855" s="5" t="s">
+        <v>2442</v>
+      </c>
+      <c r="C855" s="3" t="s">
         <v>2406</v>
-      </c>
-      <c r="B855" s="5" t="s">
-        <v>2443</v>
-      </c>
-      <c r="C855" s="3" t="s">
-        <v>2407</v>
       </c>
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A856" s="4" t="s">
+        <v>2408</v>
+      </c>
+      <c r="B856" s="5" t="s">
+        <v>2443</v>
+      </c>
+      <c r="C856" s="3" t="s">
         <v>2409</v>
-      </c>
-      <c r="B856" s="5" t="s">
-        <v>2444</v>
-      </c>
-      <c r="C856" s="3" t="s">
-        <v>2410</v>
       </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A857" s="4" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="B857" s="5" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="C857" s="3" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A858" s="4" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B858" s="5" t="s">
+        <v>2445</v>
+      </c>
+      <c r="C858" s="3" t="s">
         <v>2412</v>
-      </c>
-      <c r="B858" s="5" t="s">
-        <v>2446</v>
-      </c>
-      <c r="C858" s="3" t="s">
-        <v>2413</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A859" s="4" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B859" s="5" t="s">
+        <v>2446</v>
+      </c>
+      <c r="C859" s="3" t="s">
         <v>2414</v>
-      </c>
-      <c r="B859" s="5" t="s">
-        <v>2447</v>
-      </c>
-      <c r="C859" s="3" t="s">
-        <v>2415</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A860" s="4" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B860" s="5" t="s">
+        <v>2447</v>
+      </c>
+      <c r="C860" s="3" t="s">
         <v>2416</v>
-      </c>
-      <c r="B860" s="5" t="s">
-        <v>2448</v>
-      </c>
-      <c r="C860" s="3" t="s">
-        <v>2417</v>
       </c>
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A861" s="4" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="B861" s="5" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="C861" s="3" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A862" s="4" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="B862" s="5" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="C862" s="3" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A863" s="4" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="B863" s="5" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C863" s="3" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A864" s="4" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="B864" s="5" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="C864" s="3" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A865" s="4" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="B865" s="5" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="C865" s="3" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A866" s="4" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="B866" s="5" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="C866" s="3" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A867" s="4" t="s">
+        <v>2428</v>
+      </c>
+      <c r="B867" s="5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="C867" s="3" t="s">
         <v>2429</v>
-      </c>
-      <c r="B867" s="5" t="s">
-        <v>2455</v>
-      </c>
-      <c r="C867" s="3" t="s">
-        <v>2430</v>
       </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A868" s="4" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="B868" s="5" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="C868" s="3" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A869" s="4" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B869" s="5" t="s">
+        <v>2456</v>
+      </c>
+      <c r="C869" s="3" t="s">
         <v>2432</v>
-      </c>
-      <c r="B869" s="5" t="s">
-        <v>2457</v>
-      </c>
-      <c r="C869" s="3" t="s">
-        <v>2433</v>
       </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A870" s="4" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B870" s="5" t="s">
+        <v>2457</v>
+      </c>
+      <c r="C870" s="3" t="s">
         <v>2434</v>
-      </c>
-      <c r="B870" s="5" t="s">
-        <v>2458</v>
-      </c>
-      <c r="C870" s="3" t="s">
-        <v>2435</v>
       </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A871" s="4" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B871" s="5" t="s">
+        <v>2458</v>
+      </c>
+      <c r="C871" s="3" t="s">
         <v>2436</v>
-      </c>
-      <c r="B871" s="5" t="s">
-        <v>2459</v>
-      </c>
-      <c r="C871" s="3" t="s">
-        <v>2437</v>
       </c>
     </row>
     <row r="872" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A872" s="4" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B872" s="5" t="s">
+        <v>2459</v>
+      </c>
+      <c r="C872" s="3" t="s">
         <v>2438</v>
-      </c>
-      <c r="B872" s="5" t="s">
-        <v>2460</v>
-      </c>
-      <c r="C872" s="3" t="s">
-        <v>2439</v>
       </c>
     </row>
     <row r="873" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A873" s="4" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B873" s="5" t="s">
+        <v>2462</v>
+      </c>
+      <c r="C873" s="3" t="s">
         <v>2461</v>
-      </c>
-      <c r="B873" s="5" t="s">
-        <v>2463</v>
-      </c>
-      <c r="C873" s="3" t="s">
-        <v>2462</v>
       </c>
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A874" s="4" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B874" s="5" t="s">
         <v>2464</v>
       </c>
-      <c r="B874" s="5" t="s">
+      <c r="C874" s="3" t="s">
         <v>2465</v>
-      </c>
-      <c r="C874" s="3" t="s">
-        <v>2466</v>
       </c>
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A875" s="4" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="B875" s="5" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="C875" s="3" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A876" s="4" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="B876" s="5" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="C876" s="3" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="877" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A877" s="4" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="B877" s="5" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="C877" s="3" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="878" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A878" s="4" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="B878" s="5" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="C878" s="3" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A879" s="4" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="B879" s="5" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="C879" s="3" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A880" s="4" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="B880" s="5" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="C880" s="3" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A881" s="4" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="B881" s="5" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="C881" s="3" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A882" s="4" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="B882" s="5" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="C882" s="3" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="883" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A883" s="4" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="B883" s="5" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="C883" s="3" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="884" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A884" s="4" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B884" s="5" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="C884" s="3" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="885" spans="1:3" ht="285" x14ac:dyDescent="0.4">
       <c r="A885" s="4" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B885" s="5" t="s">
         <v>2538</v>
       </c>
-      <c r="B885" s="5" t="s">
+      <c r="C885" s="3" t="s">
         <v>2539</v>
-      </c>
-      <c r="C885" s="3" t="s">
-        <v>2540</v>
       </c>
     </row>
     <row r="886" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A886" s="4" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="B886" s="5" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="C886" s="3" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="887" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A887" s="4" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="B887" s="5" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="C887" s="3" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="888" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A888" s="4" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="B888" s="5" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="C888" s="3" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="889" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A889" s="4" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="B889" s="5" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="C889" s="3" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="890" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A890" s="4" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="B890" s="5" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="C890" s="3" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A891" s="4" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="B891" s="5" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="C891" s="3" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A892" s="4" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="B892" s="5" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="C892" s="3" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A893" s="4" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="B893" s="5" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="C893" s="3" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="894" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A894" s="4" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="B894" s="5" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="C894" s="3" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="895" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A895" s="4" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="B895" s="5" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="C895" s="3" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="896" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A896" s="4" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="B896" s="5" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="C896" s="3" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="897" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A897" s="4" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="B897" s="5" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="C897" s="3" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="898" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A898" s="4" t="s">
+        <v>2525</v>
+      </c>
+      <c r="B898" s="5" t="s">
+        <v>2527</v>
+      </c>
+      <c r="C898" s="3" t="s">
         <v>2526</v>
-      </c>
-      <c r="B898" s="5" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C898" s="3" t="s">
-        <v>2527</v>
       </c>
     </row>
     <row r="899" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A899" s="4" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B899" s="5" t="s">
         <v>2529</v>
       </c>
-      <c r="B899" s="5" t="s">
+      <c r="C899" s="3" t="s">
         <v>2530</v>
-      </c>
-      <c r="C899" s="3" t="s">
-        <v>2531</v>
       </c>
     </row>
     <row r="900" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A900" s="4" t="s">
+        <v>2531</v>
+      </c>
+      <c r="B900" s="5" t="s">
         <v>2532</v>
       </c>
-      <c r="B900" s="5" t="s">
+      <c r="C900" s="3" t="s">
         <v>2533</v>
-      </c>
-      <c r="C900" s="3" t="s">
-        <v>2534</v>
       </c>
     </row>
     <row r="901" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A901" s="4" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B901" s="5" t="s">
+        <v>2534</v>
+      </c>
+      <c r="C901" s="3" t="s">
         <v>2536</v>
-      </c>
-      <c r="B901" s="5" t="s">
-        <v>2535</v>
-      </c>
-      <c r="C901" s="3" t="s">
-        <v>2537</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A902" s="4" t="s">
+        <v>2540</v>
+      </c>
+      <c r="B902" s="5" t="s">
+        <v>2542</v>
+      </c>
+      <c r="C902" s="3" t="s">
         <v>2541</v>
-      </c>
-      <c r="B902" s="5" t="s">
-        <v>2543</v>
-      </c>
-      <c r="C902" s="3" t="s">
-        <v>2542</v>
       </c>
     </row>
     <row r="903" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A903" s="4" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B903" s="5" t="s">
+        <v>2545</v>
+      </c>
+      <c r="C903" s="3" t="s">
         <v>2544</v>
-      </c>
-      <c r="B903" s="5" t="s">
-        <v>2546</v>
-      </c>
-      <c r="C903" s="3" t="s">
-        <v>2545</v>
       </c>
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A904" s="4" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B904" s="5" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C904" s="3" t="s">
         <v>2548</v>
-      </c>
-      <c r="B904" s="5" t="s">
-        <v>2547</v>
-      </c>
-      <c r="C904" s="3" t="s">
-        <v>2549</v>
       </c>
     </row>
     <row r="905" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A905" s="4" t="s">
+        <v>2550</v>
+      </c>
+      <c r="B905" s="5" t="s">
         <v>2551</v>
       </c>
-      <c r="B905" s="5" t="s">
+      <c r="C905" s="3" t="s">
         <v>2552</v>
-      </c>
-      <c r="C905" s="3" t="s">
-        <v>2553</v>
       </c>
     </row>
     <row r="906" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A906" s="4" t="s">
+        <v>2553</v>
+      </c>
+      <c r="B906" s="5" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C906" s="3" t="s">
         <v>2554</v>
-      </c>
-      <c r="B906" s="5" t="s">
-        <v>2556</v>
-      </c>
-      <c r="C906" s="3" t="s">
-        <v>2555</v>
       </c>
     </row>
     <row r="907" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A907" s="4" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="B907" s="5" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
       <c r="C907" s="3" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="908" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A908" s="4" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="B908" s="5" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="C908" s="3" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="909" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A909" s="4" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
       <c r="B909" s="5" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
       <c r="C909" s="3" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="910" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A910" s="4" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="B910" s="5" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="C910" s="3" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="911" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A911" s="4" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="B911" s="5" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="C911" s="3" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="912" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A912" s="4" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="B912" s="5" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="C912" s="3" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="913" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A913" s="4" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B913" s="5" t="s">
         <v>2575</v>
       </c>
-      <c r="B913" s="5" t="s">
+      <c r="C913" s="3" t="s">
         <v>2576</v>
-      </c>
-      <c r="C913" s="3" t="s">
-        <v>2577</v>
       </c>
     </row>
     <row r="914" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A914" s="4" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
       <c r="B914" s="5" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C914" s="3" t="s">
         <v>2576</v>
-      </c>
-      <c r="C914" s="3" t="s">
-        <v>2577</v>
       </c>
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A915" s="4" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B915" s="5" t="s">
+        <v>2580</v>
+      </c>
+      <c r="C915" s="3" t="s">
         <v>2579</v>
-      </c>
-      <c r="B915" s="5" t="s">
-        <v>2581</v>
-      </c>
-      <c r="C915" s="3" t="s">
-        <v>2580</v>
       </c>
     </row>
     <row r="916" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A916" s="4" t="s">
+        <v>2582</v>
+      </c>
+      <c r="B916" s="5" t="s">
         <v>2583</v>
       </c>
-      <c r="B916" s="5" t="s">
-        <v>2584</v>
-      </c>
       <c r="C916" s="3" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="917" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A917" s="4" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B917" s="5" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C917" s="3" t="s">
         <v>2585</v>
-      </c>
-      <c r="B917" s="5" t="s">
-        <v>2587</v>
-      </c>
-      <c r="C917" s="3" t="s">
-        <v>2586</v>
       </c>
     </row>
     <row r="918" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A918" s="4" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B918" s="5" t="s">
         <v>2589</v>
       </c>
-      <c r="B918" s="5" t="s">
-        <v>2590</v>
-      </c>
       <c r="C918" s="3" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
     </row>
   </sheetData>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80AA0536-FF3B-4C9E-88B6-8E7DE506D008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F58980-1419-450D-B0B1-908E24B00EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2240" yWindow="2240" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="2591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2787" uniqueCount="2630">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -22206,17 +22206,208 @@
     <t>双击打开地图文件时，从地图目录加载资源文件</t>
   </si>
   <si>
+    <t>Options.EnableVeinholeLogic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Display remapable colors of overlays</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>启用泰伯利亚藤蔓（蔓孔）逻辑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Enable veinhole logic</t>
-  </si>
-  <si>
-    <t>Options.EnableVeinholeLogic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>启用泰伯利亚藤蔓（蔓孔）逻辑</t>
-  </si>
-  <si>
-    <t>Display remapable colors of overlays</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridObjectViewer.Group</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridObjectViewer.Search</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Search:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridObjectViewer.AllInfantry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All infantries</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridObjectViewer.AllVehicle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All vehicles</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridObjectViewer.AllAircraft</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All aircrafts</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridObjectViewer.AllBuilding</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All buildings</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridObjectViewer.AllTerrain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All terrain types</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridObjectViewer.AllSmudge</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All smudges</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridObjectViewer.All</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All objects</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对象分组:</t>
+  </si>
+  <si>
+    <t>搜索:</t>
+  </si>
+  <si>
+    <t>所有步兵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有车辆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有飞行器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有建筑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有地形对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有污染</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TabPages.GridObjectViewer</t>
+  </si>
+  <si>
+    <t>Object Viewer</t>
+  </si>
+  <si>
+    <t>对象查看器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.GridObjectViewer.LoadEditorCategory</t>
+  </si>
+  <si>
+    <t>Options.GridObjectViewer.LoadForceSides</t>
+  </si>
+  <si>
+    <r>
+      <t>根据对象的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>EditorCategory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在对象查看器中分类</t>
+    </r>
+  </si>
+  <si>
+    <t>Classify objects in the object viewer based on their EditCategory</t>
+  </si>
+  <si>
+    <r>
+      <t>根据对象的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ForceSides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在对象查看器中分类</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Classify objects in the object viewer based on their ForceSides</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridObjectViewer.CurrentSelect</t>
+  </si>
+  <si>
+    <t>当前选择:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Current:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -22623,7 +22814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C918"/>
+  <dimension ref="A1:C942"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="4" customWidth="1"/>
@@ -31807,7 +31998,7 @@
         <v>2356</v>
       </c>
       <c r="C836" s="3" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.4">
@@ -32701,16 +32892,203 @@
         <v>2585</v>
       </c>
     </row>
-    <row r="918" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="918" spans="1:3" ht="19" x14ac:dyDescent="0.4">
       <c r="A918" s="4" t="s">
-        <v>2588</v>
-      </c>
-      <c r="B918" s="5" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B918" s="4" t="s">
         <v>2589</v>
       </c>
-      <c r="C918" s="3" t="s">
-        <v>2587</v>
-      </c>
+      <c r="C918" s="4" t="s">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A919" s="4" t="s">
+        <v>2591</v>
+      </c>
+      <c r="B919" s="5" t="s">
+        <v>2609</v>
+      </c>
+      <c r="C919" s="4" t="s">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A920" s="4" t="s">
+        <v>2593</v>
+      </c>
+      <c r="B920" s="5" t="s">
+        <v>2610</v>
+      </c>
+      <c r="C920" s="4" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A921" s="4" t="s">
+        <v>2627</v>
+      </c>
+      <c r="B921" s="5" t="s">
+        <v>2628</v>
+      </c>
+      <c r="C921" s="4" t="s">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A922" s="4" t="s">
+        <v>2595</v>
+      </c>
+      <c r="B922" s="5" t="s">
+        <v>2611</v>
+      </c>
+      <c r="C922" s="4" t="s">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A923" s="4" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B923" s="5" t="s">
+        <v>2612</v>
+      </c>
+      <c r="C923" s="4" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A924" s="4" t="s">
+        <v>2599</v>
+      </c>
+      <c r="B924" s="5" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C924" s="4" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A925" s="4" t="s">
+        <v>2601</v>
+      </c>
+      <c r="B925" s="5" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C925" s="4" t="s">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A926" s="4" t="s">
+        <v>2603</v>
+      </c>
+      <c r="B926" s="5" t="s">
+        <v>2615</v>
+      </c>
+      <c r="C926" s="4" t="s">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A927" s="4" t="s">
+        <v>2605</v>
+      </c>
+      <c r="B927" s="5" t="s">
+        <v>2616</v>
+      </c>
+      <c r="C927" s="4" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A928" s="4" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B928" s="5" t="s">
+        <v>2617</v>
+      </c>
+      <c r="C928" s="4" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A929" s="4" t="s">
+        <v>2618</v>
+      </c>
+      <c r="B929" s="5" t="s">
+        <v>2620</v>
+      </c>
+      <c r="C929" s="4" t="s">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A930" s="4" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B930" s="5" t="s">
+        <v>2623</v>
+      </c>
+      <c r="C930" s="4" t="s">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A931" s="4" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B931" s="5" t="s">
+        <v>2625</v>
+      </c>
+      <c r="C931" s="4" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3" ht="19" x14ac:dyDescent="0.4">
+      <c r="B932" s="4"/>
+      <c r="C932" s="4"/>
+    </row>
+    <row r="933" spans="1:3" ht="19" x14ac:dyDescent="0.4">
+      <c r="B933" s="4"/>
+      <c r="C933" s="4"/>
+    </row>
+    <row r="934" spans="1:3" ht="19" x14ac:dyDescent="0.4">
+      <c r="B934" s="4"/>
+      <c r="C934" s="4"/>
+    </row>
+    <row r="935" spans="1:3" ht="19" x14ac:dyDescent="0.4">
+      <c r="B935" s="4"/>
+      <c r="C935" s="4"/>
+    </row>
+    <row r="936" spans="1:3" ht="19" x14ac:dyDescent="0.4">
+      <c r="B936" s="4"/>
+      <c r="C936" s="4"/>
+    </row>
+    <row r="937" spans="1:3" ht="19" x14ac:dyDescent="0.4">
+      <c r="B937" s="4"/>
+      <c r="C937" s="4"/>
+    </row>
+    <row r="938" spans="1:3" ht="19" x14ac:dyDescent="0.4">
+      <c r="B938" s="4"/>
+      <c r="C938" s="4"/>
+    </row>
+    <row r="939" spans="1:3" ht="19" x14ac:dyDescent="0.4">
+      <c r="B939" s="4"/>
+      <c r="C939" s="4"/>
+    </row>
+    <row r="940" spans="1:3" ht="19" x14ac:dyDescent="0.4">
+      <c r="B940" s="4"/>
+      <c r="C940" s="4"/>
+    </row>
+    <row r="941" spans="1:3" ht="19" x14ac:dyDescent="0.4">
+      <c r="B941" s="4"/>
+      <c r="C941" s="4"/>
+    </row>
+    <row r="942" spans="1:3" ht="19" x14ac:dyDescent="0.4">
+      <c r="B942" s="4"/>
+      <c r="C942" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95510E20-EB25-426A-98A9-E1F8BF07D2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B96FDB7-868A-40F5-8C4F-22AE83C530B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2240" yWindow="2240" windowWidth="31590" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2829" uniqueCount="2683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2853" uniqueCount="2707">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23289,6 +23289,86 @@
   </si>
   <si>
     <t>Center</t>
+  </si>
+  <si>
+    <t>地表类型: %#x, 高度 %d /</t>
+  </si>
+  <si>
+    <t>覆盖物: %#x, 覆盖物数据: %#x /</t>
+  </si>
+  <si>
+    <t>建筑: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>车辆: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>飞行器: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>步兵: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>单元标记: %s (%s) /</t>
+  </si>
+  <si>
+    <t>StatusBarText7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusBarText6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusBarText5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusBarText4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusBarText3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusBarText2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusBarText1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Terrain type: %#x, height %d /</t>
+  </si>
+  <si>
+    <t>Overlay: %#x, OverlayData %#x /</t>
+  </si>
+  <si>
+    <t>Structure: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>Vehicle: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>Aircraft: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>Infantry: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>CellTag: %s (%s) /</t>
+  </si>
+  <si>
+    <t>GridObjectViewer.OverlayText</t>
+  </si>
+  <si>
+    <t>索引: %d, 覆盖物数据: %d</t>
+  </si>
+  <si>
+    <t>Index: %d, OverlayData: %d</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -23682,7 +23762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C945"/>
+  <dimension ref="A1:C953"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34068,8 +34148,97 @@
         <v>2682</v>
       </c>
     </row>
+    <row r="946" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A946" s="3" t="s">
+        <v>2696</v>
+      </c>
+      <c r="B946" s="4" t="s">
+        <v>2683</v>
+      </c>
+      <c r="C946" s="3" t="s">
+        <v>2697</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A947" s="3" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B947" s="4" t="s">
+        <v>2684</v>
+      </c>
+      <c r="C947" s="3" t="s">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A948" s="3" t="s">
+        <v>2694</v>
+      </c>
+      <c r="B948" s="4" t="s">
+        <v>2685</v>
+      </c>
+      <c r="C948" s="3" t="s">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="949" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A949" s="3" t="s">
+        <v>2693</v>
+      </c>
+      <c r="B949" s="4" t="s">
+        <v>2686</v>
+      </c>
+      <c r="C949" s="3" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="950" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A950" s="3" t="s">
+        <v>2692</v>
+      </c>
+      <c r="B950" s="4" t="s">
+        <v>2687</v>
+      </c>
+      <c r="C950" s="3" t="s">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="951" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A951" s="3" t="s">
+        <v>2691</v>
+      </c>
+      <c r="B951" s="4" t="s">
+        <v>2688</v>
+      </c>
+      <c r="C951" s="3" t="s">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="952" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A952" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B952" s="4" t="s">
+        <v>2689</v>
+      </c>
+      <c r="C952" s="3" t="s">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="953" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A953" s="3" t="s">
+        <v>2704</v>
+      </c>
+      <c r="B953" s="4" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C953" s="3" t="s">
+        <v>2706</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B96FDB7-868A-40F5-8C4F-22AE83C530B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEC952D-FC7C-4416-9BDF-1DC55DBAAB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2853" uniqueCount="2707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2856" uniqueCount="2710">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23369,6 +23369,16 @@
   <si>
     <t>Index: %d, OverlayData: %d</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NewVersionAvailable</t>
+  </si>
+  <si>
+    <t>发现新版本:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New version available:</t>
   </si>
 </sst>
 </file>
@@ -23762,7 +23772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C953"/>
+  <dimension ref="A1:C954"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34236,6 +34246,17 @@
         <v>2706</v>
       </c>
     </row>
+    <row r="954" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A954" s="3" t="s">
+        <v>2707</v>
+      </c>
+      <c r="B954" s="4" t="s">
+        <v>2708</v>
+      </c>
+      <c r="C954" s="3" t="s">
+        <v>2709</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEC952D-FC7C-4416-9BDF-1DC55DBAAB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FA97EA-A56C-4AC2-B5F4-D9CF7CEC6493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2856" uniqueCount="2710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="2713">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -6674,16 +6674,9 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>在创建触发时始终使用下一个递增索引号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Options.UseSequentialIndexing</t>
   </si>
   <si>
-    <t>Always assign the next incremental index when creating triggers</t>
-  </si>
-  <si>
     <t>GlobalSearch.TreeView</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -23379,6 +23372,23 @@
   </si>
   <si>
     <t>New version available:</t>
+  </si>
+  <si>
+    <t>Assign independent suffixes to different types (triggers, teams...)</t>
+  </si>
+  <si>
+    <t>Options.UseSeparateIndexing</t>
+  </si>
+  <si>
+    <t>为触发、小队等分配带有独立后缀的ID</t>
+  </si>
+  <si>
+    <t>在创建触发、小队时始终使用下一个递增索引号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Always assign the next incremental index when creating triggers and teams</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -23772,7 +23782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C954"/>
+  <dimension ref="A1:C955"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -23797,7 +23807,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1194</v>
@@ -23808,7 +23818,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1195</v>
@@ -23819,7 +23829,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1196</v>
@@ -23830,7 +23840,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1197</v>
@@ -23841,7 +23851,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1198</v>
@@ -23852,7 +23862,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1199</v>
@@ -23863,7 +23873,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1124</v>
@@ -23874,7 +23884,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>854</v>
@@ -23885,7 +23895,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1200</v>
@@ -23896,7 +23906,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1201</v>
@@ -23904,13 +23914,13 @@
     </row>
     <row r="12" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
@@ -23918,7 +23928,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1202</v>
@@ -23929,7 +23939,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1203</v>
@@ -23940,7 +23950,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1002</v>
@@ -23951,7 +23961,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>816</v>
@@ -23962,7 +23972,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>886</v>
@@ -23973,7 +23983,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1204</v>
@@ -23984,7 +23994,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1205</v>
@@ -23995,7 +24005,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1206</v>
@@ -24006,7 +24016,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1207</v>
@@ -24017,7 +24027,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1208</v>
@@ -24028,7 +24038,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1209</v>
@@ -24039,7 +24049,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1210</v>
@@ -24050,7 +24060,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1211</v>
@@ -24061,7 +24071,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1595</v>
@@ -24072,7 +24082,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>857</v>
@@ -24083,7 +24093,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>858</v>
@@ -24094,7 +24104,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>859</v>
@@ -24105,7 +24115,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>860</v>
@@ -24116,7 +24126,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>861</v>
@@ -24127,7 +24137,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1212</v>
@@ -24138,7 +24148,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1213</v>
@@ -24149,7 +24159,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1214</v>
@@ -24160,7 +24170,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1215</v>
@@ -24171,7 +24181,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>1216</v>
@@ -24182,7 +24192,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>1197</v>
@@ -24193,7 +24203,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>1217</v>
@@ -24204,7 +24214,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>1218</v>
@@ -24215,7 +24225,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>1219</v>
@@ -24226,7 +24236,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>1236</v>
@@ -24237,7 +24247,7 @@
         <v>39</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>1220</v>
@@ -24248,7 +24258,7 @@
         <v>1129</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>1221</v>
@@ -24259,7 +24269,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>1222</v>
@@ -24270,7 +24280,7 @@
         <v>41</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>1223</v>
@@ -24281,7 +24291,7 @@
         <v>42</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>1224</v>
@@ -24292,7 +24302,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>1225</v>
@@ -24303,7 +24313,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>1226</v>
@@ -24314,7 +24324,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>1227</v>
@@ -24325,7 +24335,7 @@
         <v>33</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>1216</v>
@@ -24336,7 +24346,7 @@
         <v>34</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>1197</v>
@@ -24347,7 +24357,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>1228</v>
@@ -24358,7 +24368,7 @@
         <v>47</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>1229</v>
@@ -24369,7 +24379,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>1230</v>
@@ -24380,7 +24390,7 @@
         <v>49</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>1231</v>
@@ -24431,10 +24441,10 @@
         <v>55</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
@@ -24442,7 +24452,7 @@
         <v>56</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>871</v>
@@ -24453,7 +24463,7 @@
         <v>57</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>867</v>
@@ -24464,7 +24474,7 @@
         <v>58</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>866</v>
@@ -24475,7 +24485,7 @@
         <v>59</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>869</v>
@@ -24486,7 +24496,7 @@
         <v>60</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>868</v>
@@ -24497,7 +24507,7 @@
         <v>61</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>870</v>
@@ -24508,7 +24518,7 @@
         <v>62</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>862</v>
@@ -24519,7 +24529,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>863</v>
@@ -24530,7 +24540,7 @@
         <v>64</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>864</v>
@@ -24541,7 +24551,7 @@
         <v>65</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>865</v>
@@ -24552,7 +24562,7 @@
         <v>66</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>875</v>
@@ -24563,7 +24573,7 @@
         <v>67</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>876</v>
@@ -24574,7 +24584,7 @@
         <v>68</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>877</v>
@@ -24585,7 +24595,7 @@
         <v>69</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>878</v>
@@ -24596,7 +24606,7 @@
         <v>70</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>879</v>
@@ -24607,7 +24617,7 @@
         <v>71</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>1232</v>
@@ -24618,7 +24628,7 @@
         <v>72</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>1233</v>
@@ -24640,7 +24650,7 @@
         <v>74</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>1234</v>
@@ -24651,7 +24661,7 @@
         <v>75</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>1215</v>
@@ -24662,7 +24672,7 @@
         <v>76</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>1216</v>
@@ -24673,7 +24683,7 @@
         <v>77</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>1197</v>
@@ -24684,7 +24694,7 @@
         <v>78</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>1219</v>
@@ -24695,7 +24705,7 @@
         <v>79</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>1235</v>
@@ -24706,7 +24716,7 @@
         <v>80</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>1236</v>
@@ -24717,7 +24727,7 @@
         <v>81</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>1237</v>
@@ -24728,7 +24738,7 @@
         <v>82</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>1238</v>
@@ -24739,7 +24749,7 @@
         <v>83</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>1239</v>
@@ -24750,7 +24760,7 @@
         <v>84</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>1240</v>
@@ -24761,7 +24771,7 @@
         <v>85</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>1241</v>
@@ -24772,7 +24782,7 @@
         <v>86</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>888</v>
@@ -24783,7 +24793,7 @@
         <v>87</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>1242</v>
@@ -24794,7 +24804,7 @@
         <v>88</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>1243</v>
@@ -24805,7 +24815,7 @@
         <v>89</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>1244</v>
@@ -24816,7 +24826,7 @@
         <v>90</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>1245</v>
@@ -24827,7 +24837,7 @@
         <v>91</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>1246</v>
@@ -24838,7 +24848,7 @@
         <v>92</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>1247</v>
@@ -24849,7 +24859,7 @@
         <v>93</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>1248</v>
@@ -24860,7 +24870,7 @@
         <v>94</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>1222</v>
@@ -24871,7 +24881,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>1223</v>
@@ -24882,7 +24892,7 @@
         <v>96</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>1224</v>
@@ -24893,7 +24903,7 @@
         <v>97</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>1249</v>
@@ -24904,7 +24914,7 @@
         <v>98</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>1250</v>
@@ -24915,7 +24925,7 @@
         <v>99</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>822</v>
@@ -24926,7 +24936,7 @@
         <v>100</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>823</v>
@@ -24937,7 +24947,7 @@
         <v>101</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>824</v>
@@ -24948,7 +24958,7 @@
         <v>102</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>825</v>
@@ -24959,7 +24969,7 @@
         <v>103</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>826</v>
@@ -24970,7 +24980,7 @@
         <v>104</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>827</v>
@@ -24981,7 +24991,7 @@
         <v>104</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>827</v>
@@ -24992,7 +25002,7 @@
         <v>105</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>828</v>
@@ -25003,7 +25013,7 @@
         <v>106</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>829</v>
@@ -25014,7 +25024,7 @@
         <v>107</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>830</v>
@@ -25025,7 +25035,7 @@
         <v>108</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>831</v>
@@ -25036,7 +25046,7 @@
         <v>109</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>832</v>
@@ -25047,7 +25057,7 @@
         <v>110</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>833</v>
@@ -25058,7 +25068,7 @@
         <v>111</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>834</v>
@@ -25069,7 +25079,7 @@
         <v>112</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>835</v>
@@ -25080,7 +25090,7 @@
         <v>113</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>836</v>
@@ -25091,7 +25101,7 @@
         <v>114</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>838</v>
@@ -25102,7 +25112,7 @@
         <v>115</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>837</v>
@@ -25113,7 +25123,7 @@
         <v>116</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>923</v>
@@ -25124,7 +25134,7 @@
         <v>117</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>928</v>
@@ -25135,7 +25145,7 @@
         <v>118</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>929</v>
@@ -25146,7 +25156,7 @@
         <v>119</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>1251</v>
@@ -25157,7 +25167,7 @@
         <v>120</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>1252</v>
@@ -25168,7 +25178,7 @@
         <v>121</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>1253</v>
@@ -25179,7 +25189,7 @@
         <v>122</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>1254</v>
@@ -25190,7 +25200,7 @@
         <v>123</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>1227</v>
@@ -25201,7 +25211,7 @@
         <v>124</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>1216</v>
@@ -25212,7 +25222,7 @@
         <v>125</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>1197</v>
@@ -25223,7 +25233,7 @@
         <v>126</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>1255</v>
@@ -25234,7 +25244,7 @@
         <v>127</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>1256</v>
@@ -25256,7 +25266,7 @@
         <v>129</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>1258</v>
@@ -25267,7 +25277,7 @@
         <v>130</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>1259</v>
@@ -25278,7 +25288,7 @@
         <v>131</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>1260</v>
@@ -25289,7 +25299,7 @@
         <v>132</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>817</v>
@@ -25300,7 +25310,7 @@
         <v>133</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>818</v>
@@ -25311,7 +25321,7 @@
         <v>134</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>1112</v>
@@ -25322,7 +25332,7 @@
         <v>135</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>1113</v>
@@ -25333,7 +25343,7 @@
         <v>136</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>1261</v>
@@ -25344,7 +25354,7 @@
         <v>137</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>1262</v>
@@ -25355,7 +25365,7 @@
         <v>138</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>1263</v>
@@ -25366,7 +25376,7 @@
         <v>139</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>1264</v>
@@ -25377,7 +25387,7 @@
         <v>140</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>883</v>
@@ -25388,7 +25398,7 @@
         <v>141</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>1265</v>
@@ -25399,7 +25409,7 @@
         <v>142</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>1266</v>
@@ -25410,7 +25420,7 @@
         <v>143</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>1267</v>
@@ -25421,7 +25431,7 @@
         <v>144</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>1268</v>
@@ -25432,7 +25442,7 @@
         <v>145</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>1269</v>
@@ -25443,7 +25453,7 @@
         <v>146</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>1270</v>
@@ -25454,7 +25464,7 @@
         <v>147</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>1271</v>
@@ -25465,7 +25475,7 @@
         <v>148</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>1272</v>
@@ -25476,7 +25486,7 @@
         <v>149</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>1273</v>
@@ -25487,7 +25497,7 @@
         <v>150</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>1274</v>
@@ -25498,7 +25508,7 @@
         <v>151</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>1275</v>
@@ -25509,7 +25519,7 @@
         <v>152</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>1276</v>
@@ -25520,7 +25530,7 @@
         <v>153</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>1277</v>
@@ -25531,7 +25541,7 @@
         <v>154</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>1278</v>
@@ -25542,7 +25552,7 @@
         <v>155</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>1279</v>
@@ -25553,7 +25563,7 @@
         <v>156</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>1280</v>
@@ -25564,7 +25574,7 @@
         <v>157</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>1281</v>
@@ -25575,7 +25585,7 @@
         <v>158</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>1282</v>
@@ -25586,7 +25596,7 @@
         <v>159</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>1589</v>
@@ -25597,7 +25607,7 @@
         <v>160</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>1588</v>
@@ -25608,7 +25618,7 @@
         <v>161</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>1283</v>
@@ -25619,7 +25629,7 @@
         <v>162</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>1284</v>
@@ -25630,7 +25640,7 @@
         <v>163</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>1285</v>
@@ -25641,7 +25651,7 @@
         <v>164</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>1286</v>
@@ -25652,7 +25662,7 @@
         <v>165</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>1287</v>
@@ -25663,7 +25673,7 @@
         <v>166</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>1288</v>
@@ -25674,7 +25684,7 @@
         <v>167</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>1289</v>
@@ -25685,7 +25695,7 @@
         <v>168</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>1290</v>
@@ -25696,7 +25706,7 @@
         <v>169</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>1291</v>
@@ -25707,7 +25717,7 @@
         <v>170</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>1292</v>
@@ -25718,7 +25728,7 @@
         <v>171</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>1293</v>
@@ -25729,7 +25739,7 @@
         <v>172</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>1294</v>
@@ -25740,7 +25750,7 @@
         <v>173</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>1295</v>
@@ -25751,7 +25761,7 @@
         <v>174</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>1296</v>
@@ -25762,7 +25772,7 @@
         <v>175</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>1297</v>
@@ -25773,7 +25783,7 @@
         <v>176</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>1298</v>
@@ -25784,7 +25794,7 @@
         <v>177</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>1299</v>
@@ -25795,7 +25805,7 @@
         <v>178</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>1300</v>
@@ -25806,7 +25816,7 @@
         <v>179</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>1301</v>
@@ -25817,7 +25827,7 @@
         <v>180</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>1302</v>
@@ -25828,7 +25838,7 @@
         <v>181</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>1303</v>
@@ -25839,7 +25849,7 @@
         <v>182</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>1304</v>
@@ -25850,7 +25860,7 @@
         <v>183</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>1305</v>
@@ -25861,7 +25871,7 @@
         <v>184</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>1306</v>
@@ -25872,7 +25882,7 @@
         <v>185</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>1307</v>
@@ -25883,7 +25893,7 @@
         <v>186</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>1308</v>
@@ -25894,7 +25904,7 @@
         <v>187</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>1309</v>
@@ -25905,7 +25915,7 @@
         <v>188</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>1310</v>
@@ -25916,7 +25926,7 @@
         <v>189</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>2119</v>
+        <v>2117</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>1311</v>
@@ -25927,7 +25937,7 @@
         <v>190</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
       <c r="C197" s="3" t="s">
         <v>1312</v>
@@ -25938,7 +25948,7 @@
         <v>191</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>1313</v>
@@ -25949,7 +25959,7 @@
         <v>192</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>1314</v>
@@ -25960,7 +25970,7 @@
         <v>193</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>1315</v>
@@ -25971,7 +25981,7 @@
         <v>194</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
       <c r="C201" s="3" t="s">
         <v>1316</v>
@@ -25982,7 +25992,7 @@
         <v>195</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>1317</v>
@@ -25993,7 +26003,7 @@
         <v>196</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>1318</v>
@@ -26004,7 +26014,7 @@
         <v>197</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>1319</v>
@@ -26015,7 +26025,7 @@
         <v>198</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>2128</v>
+        <v>2126</v>
       </c>
       <c r="C205" s="3" t="s">
         <v>1320</v>
@@ -26026,7 +26036,7 @@
         <v>199</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
       <c r="C206" s="3" t="s">
         <v>1321</v>
@@ -26037,7 +26047,7 @@
         <v>200</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
       <c r="C207" s="3" t="s">
         <v>1322</v>
@@ -26048,7 +26058,7 @@
         <v>201</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
       <c r="C208" s="3" t="s">
         <v>1323</v>
@@ -26059,7 +26069,7 @@
         <v>202</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>1324</v>
@@ -26070,7 +26080,7 @@
         <v>203</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>2133</v>
+        <v>2131</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>1325</v>
@@ -26081,7 +26091,7 @@
         <v>204</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>1326</v>
@@ -26092,7 +26102,7 @@
         <v>205</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>1327</v>
@@ -26103,7 +26113,7 @@
         <v>206</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>1328</v>
@@ -26114,7 +26124,7 @@
         <v>207</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C214" s="3" t="s">
         <v>1329</v>
@@ -26125,7 +26135,7 @@
         <v>208</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
       <c r="C215" s="3" t="s">
         <v>1330</v>
@@ -26136,7 +26146,7 @@
         <v>209</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>1331</v>
@@ -26147,7 +26157,7 @@
         <v>210</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>1332</v>
@@ -26158,7 +26168,7 @@
         <v>1590</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>1591</v>
@@ -26169,7 +26179,7 @@
         <v>211</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>1333</v>
@@ -26180,7 +26190,7 @@
         <v>212</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="C220" s="3" t="s">
         <v>1334</v>
@@ -26191,7 +26201,7 @@
         <v>213</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>1335</v>
@@ -26202,7 +26212,7 @@
         <v>214</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>1336</v>
@@ -26213,7 +26223,7 @@
         <v>215</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="C223" s="3" t="s">
         <v>1337</v>
@@ -26224,7 +26234,7 @@
         <v>216</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>1338</v>
@@ -26235,7 +26245,7 @@
         <v>217</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>1339</v>
@@ -26246,7 +26256,7 @@
         <v>218</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>1340</v>
@@ -26257,7 +26267,7 @@
         <v>219</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="C227" s="3" t="s">
         <v>1341</v>
@@ -26268,7 +26278,7 @@
         <v>220</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="C228" s="3" t="s">
         <v>1342</v>
@@ -26279,7 +26289,7 @@
         <v>221</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>1343</v>
@@ -26290,7 +26300,7 @@
         <v>222</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>1344</v>
@@ -26301,7 +26311,7 @@
         <v>223</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="C231" s="3" t="s">
         <v>1345</v>
@@ -26312,7 +26322,7 @@
         <v>224</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>1346</v>
@@ -26323,7 +26333,7 @@
         <v>225</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="C233" s="3" t="s">
         <v>1347</v>
@@ -26334,7 +26344,7 @@
         <v>226</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>1348</v>
@@ -26345,7 +26355,7 @@
         <v>227</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>1349</v>
@@ -26356,7 +26366,7 @@
         <v>228</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>1350</v>
@@ -26367,7 +26377,7 @@
         <v>229</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="C237" s="3" t="s">
         <v>1351</v>
@@ -26378,7 +26388,7 @@
         <v>230</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>1352</v>
@@ -26389,7 +26399,7 @@
         <v>231</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>1353</v>
@@ -26400,7 +26410,7 @@
         <v>232</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>1354</v>
@@ -26411,7 +26421,7 @@
         <v>233</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>1355</v>
@@ -26422,7 +26432,7 @@
         <v>234</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>1356</v>
@@ -26433,7 +26443,7 @@
         <v>235</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>1357</v>
@@ -26444,7 +26454,7 @@
         <v>236</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>1358</v>
@@ -26455,7 +26465,7 @@
         <v>237</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>1359</v>
@@ -26466,7 +26476,7 @@
         <v>238</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>1360</v>
@@ -26477,7 +26487,7 @@
         <v>239</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>1361</v>
@@ -26488,7 +26498,7 @@
         <v>240</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>1362</v>
@@ -26499,7 +26509,7 @@
         <v>241</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>1363</v>
@@ -26510,7 +26520,7 @@
         <v>242</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>1364</v>
@@ -26521,7 +26531,7 @@
         <v>243</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>1365</v>
@@ -26532,7 +26542,7 @@
         <v>244</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>1366</v>
@@ -26543,7 +26553,7 @@
         <v>245</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>1367</v>
@@ -26554,7 +26564,7 @@
         <v>246</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>1368</v>
@@ -26565,7 +26575,7 @@
         <v>247</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="C255" s="3" t="s">
         <v>1369</v>
@@ -26576,7 +26586,7 @@
         <v>248</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>1370</v>
@@ -26587,7 +26597,7 @@
         <v>249</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>1371</v>
@@ -26598,7 +26608,7 @@
         <v>250</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>1372</v>
@@ -26609,7 +26619,7 @@
         <v>251</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>1373</v>
@@ -26620,7 +26630,7 @@
         <v>252</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>1374</v>
@@ -26631,7 +26641,7 @@
         <v>253</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>1375</v>
@@ -26642,7 +26652,7 @@
         <v>254</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>1376</v>
@@ -26653,7 +26663,7 @@
         <v>255</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>1377</v>
@@ -26664,7 +26674,7 @@
         <v>256</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="C264" s="3" t="s">
         <v>1378</v>
@@ -26675,7 +26685,7 @@
         <v>257</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>1379</v>
@@ -26686,7 +26696,7 @@
         <v>258</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="C266" s="3" t="s">
         <v>1380</v>
@@ -26697,7 +26707,7 @@
         <v>259</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
       <c r="C267" s="3" t="s">
         <v>1381</v>
@@ -26708,7 +26718,7 @@
         <v>260</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>1382</v>
@@ -26719,7 +26729,7 @@
         <v>261</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="C269" s="3" t="s">
         <v>1383</v>
@@ -26730,7 +26740,7 @@
         <v>262</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="C270" s="3" t="s">
         <v>1384</v>
@@ -26741,7 +26751,7 @@
         <v>263</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="C271" s="3" t="s">
         <v>1385</v>
@@ -26752,7 +26762,7 @@
         <v>264</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="C272" s="3" t="s">
         <v>1386</v>
@@ -26763,7 +26773,7 @@
         <v>265</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>1387</v>
@@ -26774,7 +26784,7 @@
         <v>266</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="C274" s="3" t="s">
         <v>1388</v>
@@ -26785,7 +26795,7 @@
         <v>267</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="C275" s="3" t="s">
         <v>1389</v>
@@ -26796,7 +26806,7 @@
         <v>268</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>1390</v>
@@ -26807,7 +26817,7 @@
         <v>269</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="C277" s="3" t="s">
         <v>1391</v>
@@ -26818,7 +26828,7 @@
         <v>270</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="C278" s="3" t="s">
         <v>1392</v>
@@ -26829,7 +26839,7 @@
         <v>271</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>1393</v>
@@ -26840,7 +26850,7 @@
         <v>272</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>1394</v>
@@ -26851,7 +26861,7 @@
         <v>273</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>1395</v>
@@ -26862,7 +26872,7 @@
         <v>274</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="C282" s="3" t="s">
         <v>1396</v>
@@ -26873,7 +26883,7 @@
         <v>275</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="C283" s="3" t="s">
         <v>1397</v>
@@ -26884,7 +26894,7 @@
         <v>276</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="C284" s="3" t="s">
         <v>1393</v>
@@ -26895,7 +26905,7 @@
         <v>277</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="C285" s="3" t="s">
         <v>1396</v>
@@ -26906,7 +26916,7 @@
         <v>278</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="C286" s="3" t="s">
         <v>1398</v>
@@ -26928,7 +26938,7 @@
         <v>280</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="C288" s="3" t="s">
         <v>1399</v>
@@ -26939,7 +26949,7 @@
         <v>281</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="C289" s="3" t="s">
         <v>1400</v>
@@ -26950,7 +26960,7 @@
         <v>282</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="C290" s="3" t="s">
         <v>1401</v>
@@ -26958,13 +26968,13 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A291" s="2" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="B291" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.4">
@@ -26972,7 +26982,7 @@
         <v>283</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="C292" s="3" t="s">
         <v>1402</v>
@@ -26983,7 +26993,7 @@
         <v>284</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="C293" s="3" t="s">
         <v>1263</v>
@@ -26994,7 +27004,7 @@
         <v>285</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="C294" s="3" t="s">
         <v>1403</v>
@@ -27005,7 +27015,7 @@
         <v>286</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="C295" s="3" t="s">
         <v>1404</v>
@@ -27016,7 +27026,7 @@
         <v>287</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="C296" s="3" t="s">
         <v>1405</v>
@@ -27027,7 +27037,7 @@
         <v>288</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="C297" s="3" t="s">
         <v>1406</v>
@@ -27038,7 +27048,7 @@
         <v>289</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="C298" s="3" t="s">
         <v>1407</v>
@@ -27049,7 +27059,7 @@
         <v>290</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="C299" s="3" t="s">
         <v>1408</v>
@@ -27060,7 +27070,7 @@
         <v>291</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="C300" s="3" t="s">
         <v>1220</v>
@@ -27071,7 +27081,7 @@
         <v>292</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="C301" s="3" t="s">
         <v>1409</v>
@@ -27082,7 +27092,7 @@
         <v>293</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="C302" s="3" t="s">
         <v>1410</v>
@@ -27093,7 +27103,7 @@
         <v>294</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="C303" s="3" t="s">
         <v>1411</v>
@@ -27104,7 +27114,7 @@
         <v>295</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C304" s="3" t="s">
         <v>888</v>
@@ -27115,7 +27125,7 @@
         <v>296</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="C305" s="3" t="s">
         <v>1412</v>
@@ -27126,7 +27136,7 @@
         <v>297</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="C306" s="3" t="s">
         <v>1413</v>
@@ -27137,7 +27147,7 @@
         <v>298</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="C307" s="3" t="s">
         <v>1414</v>
@@ -27148,7 +27158,7 @@
         <v>299</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="C308" s="3" t="s">
         <v>1397</v>
@@ -27159,7 +27169,7 @@
         <v>300</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="C309" s="3" t="s">
         <v>1263</v>
@@ -27170,7 +27180,7 @@
         <v>301</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="C310" s="3" t="s">
         <v>891</v>
@@ -27181,7 +27191,7 @@
         <v>302</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="C311" s="3" t="s">
         <v>892</v>
@@ -27192,7 +27202,7 @@
         <v>303</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>893</v>
@@ -27203,7 +27213,7 @@
         <v>304</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="C313" s="3" t="s">
         <v>1125</v>
@@ -27214,7 +27224,7 @@
         <v>305</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="C314" s="3" t="s">
         <v>1415</v>
@@ -27225,7 +27235,7 @@
         <v>306</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="C315" s="3" t="s">
         <v>1416</v>
@@ -27236,7 +27246,7 @@
         <v>307</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="C316" s="3" t="s">
         <v>1417</v>
@@ -27247,7 +27257,7 @@
         <v>308</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="C317" s="3" t="s">
         <v>1418</v>
@@ -27258,7 +27268,7 @@
         <v>309</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>1419</v>
@@ -27269,7 +27279,7 @@
         <v>310</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="C319" s="3" t="s">
         <v>1420</v>
@@ -27280,7 +27290,7 @@
         <v>311</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="C320" s="3" t="s">
         <v>1421</v>
@@ -27291,7 +27301,7 @@
         <v>312</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
       <c r="C321" s="3" t="s">
         <v>1422</v>
@@ -27302,7 +27312,7 @@
         <v>313</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="C322" s="3" t="s">
         <v>1423</v>
@@ -27313,7 +27323,7 @@
         <v>314</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="C323" s="3" t="s">
         <v>1424</v>
@@ -27324,7 +27334,7 @@
         <v>315</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
       <c r="C324" s="3" t="s">
         <v>1425</v>
@@ -27335,7 +27345,7 @@
         <v>316</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="C325" s="3" t="s">
         <v>1426</v>
@@ -27346,7 +27356,7 @@
         <v>317</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
       <c r="C326" s="3" t="s">
         <v>1427</v>
@@ -27357,7 +27367,7 @@
         <v>318</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="C327" s="3" t="s">
         <v>1428</v>
@@ -27368,7 +27378,7 @@
         <v>319</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
       <c r="C328" s="3" t="s">
         <v>1429</v>
@@ -27379,7 +27389,7 @@
         <v>320</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
       <c r="C329" s="3" t="s">
         <v>1430</v>
@@ -27390,7 +27400,7 @@
         <v>321</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>2242</v>
+        <v>2240</v>
       </c>
       <c r="C330" s="3" t="s">
         <v>1431</v>
@@ -27401,7 +27411,7 @@
         <v>322</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="C331" s="3" t="s">
         <v>1432</v>
@@ -27412,7 +27422,7 @@
         <v>323</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
       <c r="C332" s="3" t="s">
         <v>1433</v>
@@ -27423,7 +27433,7 @@
         <v>324</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
       <c r="C333" s="3" t="s">
         <v>1434</v>
@@ -27434,7 +27444,7 @@
         <v>325</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="C334" s="3" t="s">
         <v>1435</v>
@@ -27445,7 +27455,7 @@
         <v>326</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="C335" s="3" t="s">
         <v>1436</v>
@@ -27456,7 +27466,7 @@
         <v>327</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
       <c r="C336" s="3" t="s">
         <v>1437</v>
@@ -27467,7 +27477,7 @@
         <v>328</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="C337" s="3" t="s">
         <v>1215</v>
@@ -27478,7 +27488,7 @@
         <v>329</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="C338" s="3" t="s">
         <v>1216</v>
@@ -27489,7 +27499,7 @@
         <v>330</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="C339" s="3" t="s">
         <v>1438</v>
@@ -27500,7 +27510,7 @@
         <v>331</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
       <c r="C340" s="3" t="s">
         <v>1439</v>
@@ -27511,7 +27521,7 @@
         <v>332</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C341" s="3" t="s">
         <v>1197</v>
@@ -27522,7 +27532,7 @@
         <v>333</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="C342" s="3" t="s">
         <v>1440</v>
@@ -27533,7 +27543,7 @@
         <v>334</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="C343" s="3" t="s">
         <v>1256</v>
@@ -27544,7 +27554,7 @@
         <v>335</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="C344" s="3" t="s">
         <v>1441</v>
@@ -27555,7 +27565,7 @@
         <v>336</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="C345" s="3" t="s">
         <v>1442</v>
@@ -27566,7 +27576,7 @@
         <v>337</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="C346" s="3" t="s">
         <v>1443</v>
@@ -27577,7 +27587,7 @@
         <v>338</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="C347" s="3" t="s">
         <v>894</v>
@@ -27588,7 +27598,7 @@
         <v>339</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="C348" s="3" t="s">
         <v>895</v>
@@ -27599,7 +27609,7 @@
         <v>340</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="C349" s="3" t="s">
         <v>1444</v>
@@ -27610,7 +27620,7 @@
         <v>341</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="C350" s="3" t="s">
         <v>1445</v>
@@ -27621,7 +27631,7 @@
         <v>342</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="C351" s="3" t="s">
         <v>1446</v>
@@ -27632,7 +27642,7 @@
         <v>343</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
       <c r="C352" s="3" t="s">
         <v>1447</v>
@@ -27643,7 +27653,7 @@
         <v>344</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="C353" s="3" t="s">
         <v>1448</v>
@@ -27654,7 +27664,7 @@
         <v>345</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="C354" s="3" t="s">
         <v>1449</v>
@@ -27665,7 +27675,7 @@
         <v>346</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
       <c r="C355" s="3" t="s">
         <v>1450</v>
@@ -27676,7 +27686,7 @@
         <v>347</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="C356" s="3" t="s">
         <v>1392</v>
@@ -27698,7 +27708,7 @@
         <v>349</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>2264</v>
+        <v>2262</v>
       </c>
       <c r="C358" s="3" t="s">
         <v>910</v>
@@ -27709,7 +27719,7 @@
         <v>350</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="C359" s="3" t="s">
         <v>1309</v>
@@ -27720,7 +27730,7 @@
         <v>351</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>2265</v>
+        <v>2263</v>
       </c>
       <c r="C360" s="3" t="s">
         <v>914</v>
@@ -27731,7 +27741,7 @@
         <v>352</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="C361" s="3" t="s">
         <v>898</v>
@@ -27742,7 +27752,7 @@
         <v>353</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="C362" s="3" t="s">
         <v>353</v>
@@ -27753,7 +27763,7 @@
         <v>354</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>2268</v>
+        <v>2266</v>
       </c>
       <c r="C363" s="3" t="s">
         <v>354</v>
@@ -27764,7 +27774,7 @@
         <v>355</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="C364" s="3" t="s">
         <v>900</v>
@@ -27775,7 +27785,7 @@
         <v>356</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="C365" s="3" t="s">
         <v>899</v>
@@ -27786,7 +27796,7 @@
         <v>357</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>2271</v>
+        <v>2269</v>
       </c>
       <c r="C366" s="3" t="s">
         <v>901</v>
@@ -27797,7 +27807,7 @@
         <v>358</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>2272</v>
+        <v>2270</v>
       </c>
       <c r="C367" s="3" t="s">
         <v>988</v>
@@ -27808,7 +27818,7 @@
         <v>359</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>2273</v>
+        <v>2271</v>
       </c>
       <c r="C368" s="3" t="s">
         <v>987</v>
@@ -27819,7 +27829,7 @@
         <v>360</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>2274</v>
+        <v>2272</v>
       </c>
       <c r="C369" s="3" t="s">
         <v>896</v>
@@ -27830,7 +27840,7 @@
         <v>361</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>2275</v>
+        <v>2273</v>
       </c>
       <c r="C370" s="3" t="s">
         <v>897</v>
@@ -27841,7 +27851,7 @@
         <v>362</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
       <c r="C371" s="3" t="s">
         <v>1451</v>
@@ -27852,7 +27862,7 @@
         <v>363</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>2277</v>
+        <v>2275</v>
       </c>
       <c r="C372" s="3" t="s">
         <v>1452</v>
@@ -27863,7 +27873,7 @@
         <v>364</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>2278</v>
+        <v>2276</v>
       </c>
       <c r="C373" s="3" t="s">
         <v>1453</v>
@@ -27874,7 +27884,7 @@
         <v>365</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>2279</v>
+        <v>2277</v>
       </c>
       <c r="C374" s="3" t="s">
         <v>1454</v>
@@ -27885,7 +27895,7 @@
         <v>366</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>2280</v>
+        <v>2278</v>
       </c>
       <c r="C375" s="3" t="s">
         <v>874</v>
@@ -27896,7 +27906,7 @@
         <v>367</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="C376" s="3" t="s">
         <v>872</v>
@@ -27907,7 +27917,7 @@
         <v>368</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>2282</v>
+        <v>2280</v>
       </c>
       <c r="C377" s="3" t="s">
         <v>873</v>
@@ -27918,7 +27928,7 @@
         <v>369</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
       <c r="C378" s="3" t="s">
         <v>1455</v>
@@ -27929,7 +27939,7 @@
         <v>370</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>2284</v>
+        <v>2282</v>
       </c>
       <c r="C379" s="3" t="s">
         <v>922</v>
@@ -27940,7 +27950,7 @@
         <v>371</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="C380" s="3" t="s">
         <v>938</v>
@@ -27951,7 +27961,7 @@
         <v>372</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="C381" s="3" t="s">
         <v>939</v>
@@ -27962,7 +27972,7 @@
         <v>373</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
       <c r="C382" s="3" t="s">
         <v>940</v>
@@ -27973,7 +27983,7 @@
         <v>374</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>2288</v>
+        <v>2286</v>
       </c>
       <c r="C383" s="3" t="s">
         <v>941</v>
@@ -27984,7 +27994,7 @@
         <v>375</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
       <c r="C384" s="3" t="s">
         <v>942</v>
@@ -27995,7 +28005,7 @@
         <v>376</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
       <c r="C385" s="3" t="s">
         <v>943</v>
@@ -28006,7 +28016,7 @@
         <v>377</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="C386" s="3" t="s">
         <v>944</v>
@@ -28017,7 +28027,7 @@
         <v>378</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="C387" s="3" t="s">
         <v>945</v>
@@ -28028,7 +28038,7 @@
         <v>379</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="C388" s="3" t="s">
         <v>955</v>
@@ -28039,7 +28049,7 @@
         <v>380</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="C389" s="3" t="s">
         <v>946</v>
@@ -28050,7 +28060,7 @@
         <v>381</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
       <c r="C390" s="3" t="s">
         <v>947</v>
@@ -28061,7 +28071,7 @@
         <v>382</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
       <c r="C391" s="3" t="s">
         <v>948</v>
@@ -28072,7 +28082,7 @@
         <v>383</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>2297</v>
+        <v>2295</v>
       </c>
       <c r="C392" s="3" t="s">
         <v>949</v>
@@ -28083,7 +28093,7 @@
         <v>384</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="C393" s="3" t="s">
         <v>944</v>
@@ -28094,7 +28104,7 @@
         <v>385</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="C394" s="3" t="s">
         <v>945</v>
@@ -28105,7 +28115,7 @@
         <v>386</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="C395" s="3" t="s">
         <v>955</v>
@@ -28116,7 +28126,7 @@
         <v>387</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="C396" s="3" t="s">
         <v>946</v>
@@ -28127,7 +28137,7 @@
         <v>388</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
       <c r="C397" s="3" t="s">
         <v>950</v>
@@ -28138,7 +28148,7 @@
         <v>389</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="C398" s="3" t="s">
         <v>953</v>
@@ -28149,7 +28159,7 @@
         <v>390</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
       <c r="C399" s="3" t="s">
         <v>954</v>
@@ -28160,7 +28170,7 @@
         <v>391</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="C400" s="3" t="s">
         <v>944</v>
@@ -28171,7 +28181,7 @@
         <v>392</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="C401" s="3" t="s">
         <v>945</v>
@@ -28182,7 +28192,7 @@
         <v>393</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="C402" s="3" t="s">
         <v>955</v>
@@ -28193,7 +28203,7 @@
         <v>394</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="C403" s="3" t="s">
         <v>946</v>
@@ -28204,7 +28214,7 @@
         <v>395</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>2301</v>
+        <v>2299</v>
       </c>
       <c r="C404" s="3" t="s">
         <v>956</v>
@@ -28215,7 +28225,7 @@
         <v>396</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="C405" s="3" t="s">
         <v>957</v>
@@ -28226,7 +28236,7 @@
         <v>397</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="C406" s="3" t="s">
         <v>958</v>
@@ -28237,7 +28247,7 @@
         <v>398</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="C407" s="3" t="s">
         <v>944</v>
@@ -28248,7 +28258,7 @@
         <v>399</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="C408" s="3" t="s">
         <v>959</v>
@@ -28259,7 +28269,7 @@
         <v>400</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="C409" s="3" t="s">
         <v>960</v>
@@ -28270,7 +28280,7 @@
         <v>401</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>2306</v>
+        <v>2304</v>
       </c>
       <c r="C410" s="3" t="s">
         <v>962</v>
@@ -28281,7 +28291,7 @@
         <v>402</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>2307</v>
+        <v>2305</v>
       </c>
       <c r="C411" s="3" t="s">
         <v>963</v>
@@ -28292,7 +28302,7 @@
         <v>403</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>2308</v>
+        <v>2306</v>
       </c>
       <c r="C412" s="3" t="s">
         <v>964</v>
@@ -28303,7 +28313,7 @@
         <v>404</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>2309</v>
+        <v>2307</v>
       </c>
       <c r="C413" s="3" t="s">
         <v>965</v>
@@ -28314,7 +28324,7 @@
         <v>405</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
       <c r="C414" s="3" t="s">
         <v>966</v>
@@ -28325,7 +28335,7 @@
         <v>406</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
       <c r="C415" s="3" t="s">
         <v>967</v>
@@ -28336,7 +28346,7 @@
         <v>407</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="C416" s="3" t="s">
         <v>944</v>
@@ -28347,7 +28357,7 @@
         <v>408</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
       <c r="C417" s="3" t="s">
         <v>968</v>
@@ -28358,10 +28368,10 @@
         <v>409</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.4">
@@ -28369,7 +28379,7 @@
         <v>410</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="C419" s="3" t="s">
         <v>969</v>
@@ -28380,7 +28390,7 @@
         <v>411</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="C420" s="3" t="s">
         <v>970</v>
@@ -28391,7 +28401,7 @@
         <v>412</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
       <c r="C421" s="3" t="s">
         <v>971</v>
@@ -28402,7 +28412,7 @@
         <v>413</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>972</v>
@@ -28413,7 +28423,7 @@
         <v>414</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
       <c r="C423" s="3" t="s">
         <v>973</v>
@@ -28424,7 +28434,7 @@
         <v>415</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
       <c r="C424" s="3" t="s">
         <v>974</v>
@@ -28435,7 +28445,7 @@
         <v>416</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
       <c r="C425" s="3" t="s">
         <v>975</v>
@@ -28446,7 +28456,7 @@
         <v>417</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>2320</v>
+        <v>2318</v>
       </c>
       <c r="C426" s="3" t="s">
         <v>976</v>
@@ -28457,7 +28467,7 @@
         <v>418</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="C427" s="3" t="s">
         <v>977</v>
@@ -28468,7 +28478,7 @@
         <v>419</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="C428" s="3" t="s">
         <v>978</v>
@@ -28479,7 +28489,7 @@
         <v>420</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>2323</v>
+        <v>2321</v>
       </c>
       <c r="C429" s="3" t="s">
         <v>979</v>
@@ -28490,7 +28500,7 @@
         <v>421</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>2324</v>
+        <v>2322</v>
       </c>
       <c r="C430" s="3" t="s">
         <v>989</v>
@@ -28501,7 +28511,7 @@
         <v>422</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>2325</v>
+        <v>2323</v>
       </c>
       <c r="C431" s="3" t="s">
         <v>990</v>
@@ -28512,7 +28522,7 @@
         <v>423</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
       <c r="C432" s="3" t="s">
         <v>424</v>
@@ -28523,7 +28533,7 @@
         <v>425</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="C433" s="3" t="s">
         <v>992</v>
@@ -28534,7 +28544,7 @@
         <v>426</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
       <c r="C434" s="3" t="s">
         <v>427</v>
@@ -28545,7 +28555,7 @@
         <v>428</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>2329</v>
+        <v>2327</v>
       </c>
       <c r="C435" s="3" t="s">
         <v>429</v>
@@ -28556,7 +28566,7 @@
         <v>430</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="C436" s="3" t="s">
         <v>431</v>
@@ -28567,7 +28577,7 @@
         <v>432</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
       <c r="C437" s="3" t="s">
         <v>433</v>
@@ -28578,7 +28588,7 @@
         <v>434</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>2332</v>
+        <v>2330</v>
       </c>
       <c r="C438" s="3" t="s">
         <v>993</v>
@@ -28589,7 +28599,7 @@
         <v>435</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="C439" s="3" t="s">
         <v>994</v>
@@ -28600,7 +28610,7 @@
         <v>436</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="C440" s="3" t="s">
         <v>995</v>
@@ -28611,7 +28621,7 @@
         <v>437</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>2335</v>
+        <v>2333</v>
       </c>
       <c r="C441" s="3" t="s">
         <v>996</v>
@@ -28622,7 +28632,7 @@
         <v>438</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="C442" s="3" t="s">
         <v>439</v>
@@ -28633,7 +28643,7 @@
         <v>440</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
       <c r="C443" s="3" t="s">
         <v>441</v>
@@ -28644,7 +28654,7 @@
         <v>442</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="C444" s="3" t="s">
         <v>443</v>
@@ -28655,7 +28665,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="C445" s="3" t="s">
         <v>445</v>
@@ -28666,7 +28676,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="C446" s="3" t="s">
         <v>447</v>
@@ -28677,7 +28687,7 @@
         <v>448</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="C447" s="3" t="s">
         <v>449</v>
@@ -28688,7 +28698,7 @@
         <v>450</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="C448" s="3" t="s">
         <v>451</v>
@@ -28699,7 +28709,7 @@
         <v>452</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="C449" s="3" t="s">
         <v>997</v>
@@ -28710,7 +28720,7 @@
         <v>453</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="C450" s="3" t="s">
         <v>454</v>
@@ -28721,7 +28731,7 @@
         <v>455</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="C451" s="3" t="s">
         <v>456</v>
@@ -28732,7 +28742,7 @@
         <v>457</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="C452" s="3" t="s">
         <v>458</v>
@@ -28743,7 +28753,7 @@
         <v>459</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="C453" s="3" t="s">
         <v>998</v>
@@ -28754,7 +28764,7 @@
         <v>460</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>2348</v>
+        <v>2346</v>
       </c>
       <c r="C454" s="3" t="s">
         <v>999</v>
@@ -28765,7 +28775,7 @@
         <v>461</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>2349</v>
+        <v>2347</v>
       </c>
       <c r="C455" s="3" t="s">
         <v>462</v>
@@ -28776,7 +28786,7 @@
         <v>463</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
       <c r="C456" s="3" t="s">
         <v>1000</v>
@@ -28787,7 +28797,7 @@
         <v>464</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>2351</v>
+        <v>2349</v>
       </c>
       <c r="C457" s="3" t="s">
         <v>981</v>
@@ -28798,7 +28808,7 @@
         <v>465</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
       <c r="C458" s="3" t="s">
         <v>982</v>
@@ -28809,7 +28819,7 @@
         <v>466</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
       <c r="C459" s="3" t="s">
         <v>1118</v>
@@ -28820,7 +28830,7 @@
         <v>467</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
       <c r="C460" s="3" t="s">
         <v>1119</v>
@@ -28831,7 +28841,7 @@
         <v>468</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
       <c r="C461" s="3" t="s">
         <v>1005</v>
@@ -28842,7 +28852,7 @@
         <v>469</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
       <c r="C462" s="3" t="s">
         <v>1006</v>
@@ -28853,7 +28863,7 @@
         <v>470</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="C463" s="3" t="s">
         <v>1007</v>
@@ -28864,7 +28874,7 @@
         <v>471</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
       <c r="C464" s="3" t="s">
         <v>1010</v>
@@ -28875,7 +28885,7 @@
         <v>472</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="C465" s="3" t="s">
         <v>1011</v>
@@ -28886,7 +28896,7 @@
         <v>473</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>2360</v>
+        <v>2358</v>
       </c>
       <c r="C466" s="3" t="s">
         <v>1012</v>
@@ -28897,7 +28907,7 @@
         <v>474</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="C467" s="3" t="s">
         <v>1405</v>
@@ -28919,7 +28929,7 @@
         <v>476</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="C469" s="3" t="s">
         <v>1013</v>
@@ -28930,7 +28940,7 @@
         <v>477</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
       <c r="C470" s="3" t="s">
         <v>1014</v>
@@ -28941,7 +28951,7 @@
         <v>478</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C471" s="3" t="s">
         <v>888</v>
@@ -28952,7 +28962,7 @@
         <v>479</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="C472" s="3" t="s">
         <v>1015</v>
@@ -28963,7 +28973,7 @@
         <v>480</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="C473" s="3" t="s">
         <v>1016</v>
@@ -28974,7 +28984,7 @@
         <v>481</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="C474" s="3" t="s">
         <v>1456</v>
@@ -28985,7 +28995,7 @@
         <v>482</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="C475" s="3" t="s">
         <v>1457</v>
@@ -28996,7 +29006,7 @@
         <v>483</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="C476" s="3" t="s">
         <v>1114</v>
@@ -29007,7 +29017,7 @@
         <v>484</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="C477" s="3" t="s">
         <v>1458</v>
@@ -29018,7 +29028,7 @@
         <v>485</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="C478" s="3" t="s">
         <v>1459</v>
@@ -29029,7 +29039,7 @@
         <v>486</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="C479" s="3" t="s">
         <v>1460</v>
@@ -29040,7 +29050,7 @@
         <v>487</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="C480" s="3" t="s">
         <v>1461</v>
@@ -29051,7 +29061,7 @@
         <v>488</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="C481" s="3" t="s">
         <v>1462</v>
@@ -29062,7 +29072,7 @@
         <v>489</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="C482" s="3" t="s">
         <v>1463</v>
@@ -29073,7 +29083,7 @@
         <v>490</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="C483" s="3" t="s">
         <v>1464</v>
@@ -29084,7 +29094,7 @@
         <v>491</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="C484" s="3" t="s">
         <v>1465</v>
@@ -29095,7 +29105,7 @@
         <v>492</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="C485" s="3" t="s">
         <v>1466</v>
@@ -29106,7 +29116,7 @@
         <v>493</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="C486" s="3" t="s">
         <v>1467</v>
@@ -29117,7 +29127,7 @@
         <v>494</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>2119</v>
+        <v>2117</v>
       </c>
       <c r="C487" s="3" t="s">
         <v>1311</v>
@@ -29128,7 +29138,7 @@
         <v>495</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="C488" s="3" t="s">
         <v>921</v>
@@ -29139,7 +29149,7 @@
         <v>496</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="C489" s="3" t="s">
         <v>1310</v>
@@ -29150,7 +29160,7 @@
         <v>497</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="C490" s="3" t="s">
         <v>920</v>
@@ -29161,7 +29171,7 @@
         <v>498</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
       <c r="C491" s="3" t="s">
         <v>1597</v>
@@ -29172,7 +29182,7 @@
         <v>499</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="C492" s="3" t="s">
         <v>1599</v>
@@ -29183,7 +29193,7 @@
         <v>500</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
       <c r="C493" s="3" t="s">
         <v>1598</v>
@@ -29194,7 +29204,7 @@
         <v>501</v>
       </c>
       <c r="B494" s="4" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="C494" s="3" t="s">
         <v>1115</v>
@@ -29205,7 +29215,7 @@
         <v>502</v>
       </c>
       <c r="B495" s="4" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="C495" s="3" t="s">
         <v>1116</v>
@@ -29216,7 +29226,7 @@
         <v>503</v>
       </c>
       <c r="B496" s="4" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="C496" s="3" t="s">
         <v>1117</v>
@@ -29227,7 +29237,7 @@
         <v>504</v>
       </c>
       <c r="B497" s="4" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="C497" s="3" t="s">
         <v>1468</v>
@@ -29238,7 +29248,7 @@
         <v>505</v>
       </c>
       <c r="B498" s="4" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="C498" s="3" t="s">
         <v>1469</v>
@@ -29249,7 +29259,7 @@
         <v>506</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="C499" s="3" t="s">
         <v>1470</v>
@@ -29260,7 +29270,7 @@
         <v>507</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
       <c r="C500" s="3" t="s">
         <v>1471</v>
@@ -29271,7 +29281,7 @@
         <v>508</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="C501" s="3" t="s">
         <v>1472</v>
@@ -29282,7 +29292,7 @@
         <v>509</v>
       </c>
       <c r="B502" s="4" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="C502" s="3" t="s">
         <v>1473</v>
@@ -29293,7 +29303,7 @@
         <v>510</v>
       </c>
       <c r="B503" s="4" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="C503" s="3" t="s">
         <v>1474</v>
@@ -29304,7 +29314,7 @@
         <v>511</v>
       </c>
       <c r="B504" s="4" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="C504" s="3" t="s">
         <v>1475</v>
@@ -29315,7 +29325,7 @@
         <v>512</v>
       </c>
       <c r="B505" s="4" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="C505" s="3" t="s">
         <v>1476</v>
@@ -29326,7 +29336,7 @@
         <v>513</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
       <c r="C506" s="3" t="s">
         <v>1477</v>
@@ -29337,7 +29347,7 @@
         <v>514</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="C507" s="3" t="s">
         <v>1478</v>
@@ -29348,7 +29358,7 @@
         <v>515</v>
       </c>
       <c r="B508" s="4" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
       <c r="C508" s="3" t="s">
         <v>1479</v>
@@ -29359,7 +29369,7 @@
         <v>516</v>
       </c>
       <c r="B509" s="4" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="C509" s="3" t="s">
         <v>1480</v>
@@ -29370,7 +29380,7 @@
         <v>517</v>
       </c>
       <c r="B510" s="4" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="C510" s="3" t="s">
         <v>1481</v>
@@ -29381,7 +29391,7 @@
         <v>518</v>
       </c>
       <c r="B511" s="4" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="C511" s="3" t="s">
         <v>1482</v>
@@ -29392,7 +29402,7 @@
         <v>519</v>
       </c>
       <c r="B512" s="4" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="C512" s="3" t="s">
         <v>1483</v>
@@ -29403,7 +29413,7 @@
         <v>520</v>
       </c>
       <c r="B513" s="4" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="C513" s="3" t="s">
         <v>1484</v>
@@ -29414,7 +29424,7 @@
         <v>521</v>
       </c>
       <c r="B514" s="4" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="C514" s="3" t="s">
         <v>1485</v>
@@ -29425,7 +29435,7 @@
         <v>522</v>
       </c>
       <c r="B515" s="4" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="C515" s="3" t="s">
         <v>1486</v>
@@ -29436,7 +29446,7 @@
         <v>523</v>
       </c>
       <c r="B516" s="4" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="C516" s="3" t="s">
         <v>925</v>
@@ -29447,7 +29457,7 @@
         <v>524</v>
       </c>
       <c r="B517" s="4" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="C517" s="3" t="s">
         <v>927</v>
@@ -29458,7 +29468,7 @@
         <v>525</v>
       </c>
       <c r="B518" s="4" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="C518" s="3" t="s">
         <v>926</v>
@@ -29469,7 +29479,7 @@
         <v>526</v>
       </c>
       <c r="B519" s="4" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="C519" s="3" t="s">
         <v>936</v>
@@ -29480,7 +29490,7 @@
         <v>527</v>
       </c>
       <c r="B520" s="4" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="C520" s="3" t="s">
         <v>937</v>
@@ -29491,7 +29501,7 @@
         <v>528</v>
       </c>
       <c r="B521" s="4" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="C521" s="3" t="s">
         <v>932</v>
@@ -29502,7 +29512,7 @@
         <v>529</v>
       </c>
       <c r="B522" s="4" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="C522" s="3" t="s">
         <v>933</v>
@@ -29513,7 +29523,7 @@
         <v>530</v>
       </c>
       <c r="B523" s="4" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="C523" s="3" t="s">
         <v>934</v>
@@ -29524,7 +29534,7 @@
         <v>531</v>
       </c>
       <c r="B524" s="4" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="C524" s="3" t="s">
         <v>935</v>
@@ -29535,7 +29545,7 @@
         <v>532</v>
       </c>
       <c r="B525" s="4" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="C525" s="3" t="s">
         <v>1487</v>
@@ -29546,7 +29556,7 @@
         <v>533</v>
       </c>
       <c r="B526" s="4" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="C526" s="3" t="s">
         <v>902</v>
@@ -29557,7 +29567,7 @@
         <v>534</v>
       </c>
       <c r="B527" s="4" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="C527" s="3" t="s">
         <v>903</v>
@@ -29568,7 +29578,7 @@
         <v>535</v>
       </c>
       <c r="B528" s="4" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="C528" s="3" t="s">
         <v>1488</v>
@@ -29579,7 +29589,7 @@
         <v>536</v>
       </c>
       <c r="B529" s="4" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="C529" s="3" t="s">
         <v>1489</v>
@@ -29590,7 +29600,7 @@
         <v>537</v>
       </c>
       <c r="B530" s="4" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="C530" s="3" t="s">
         <v>1490</v>
@@ -29601,7 +29611,7 @@
         <v>538</v>
       </c>
       <c r="B531" s="4" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="C531" s="3" t="s">
         <v>1491</v>
@@ -29612,7 +29622,7 @@
         <v>539</v>
       </c>
       <c r="B532" s="4" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="C532" s="3" t="s">
         <v>1492</v>
@@ -29623,7 +29633,7 @@
         <v>540</v>
       </c>
       <c r="B533" s="4" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="C533" s="3" t="s">
         <v>1493</v>
@@ -29634,7 +29644,7 @@
         <v>541</v>
       </c>
       <c r="B534" s="4" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="C534" s="3" t="s">
         <v>1494</v>
@@ -29645,7 +29655,7 @@
         <v>542</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="C535" s="3" t="s">
         <v>1495</v>
@@ -29656,7 +29666,7 @@
         <v>543</v>
       </c>
       <c r="B536" s="4" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="C536" s="3" t="s">
         <v>1496</v>
@@ -29667,7 +29677,7 @@
         <v>544</v>
       </c>
       <c r="B537" s="4" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="C537" s="3" t="s">
         <v>1495</v>
@@ -29678,7 +29688,7 @@
         <v>545</v>
       </c>
       <c r="B538" s="4" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="C538" s="3" t="s">
         <v>1497</v>
@@ -29689,7 +29699,7 @@
         <v>546</v>
       </c>
       <c r="B539" s="4" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
       <c r="C539" s="3" t="s">
         <v>1498</v>
@@ -29700,7 +29710,7 @@
         <v>547</v>
       </c>
       <c r="B540" s="4" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="C540" s="3" t="s">
         <v>1499</v>
@@ -29711,7 +29721,7 @@
         <v>548</v>
       </c>
       <c r="B541" s="4" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="C541" s="3" t="s">
         <v>1500</v>
@@ -29722,7 +29732,7 @@
         <v>549</v>
       </c>
       <c r="B542" s="4" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="C542" s="3" t="s">
         <v>1501</v>
@@ -29733,7 +29743,7 @@
         <v>550</v>
       </c>
       <c r="B543" s="4" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="C543" s="3" t="s">
         <v>1502</v>
@@ -29744,7 +29754,7 @@
         <v>551</v>
       </c>
       <c r="B544" s="4" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="C544" s="3" t="s">
         <v>1503</v>
@@ -29755,7 +29765,7 @@
         <v>552</v>
       </c>
       <c r="B545" s="4" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="C545" s="3" t="s">
         <v>1504</v>
@@ -29766,7 +29776,7 @@
         <v>553</v>
       </c>
       <c r="B546" s="4" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="C546" s="3" t="s">
         <v>1505</v>
@@ -29777,7 +29787,7 @@
         <v>554</v>
       </c>
       <c r="B547" s="4" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="C547" s="3" t="s">
         <v>1128</v>
@@ -29788,7 +29798,7 @@
         <v>555</v>
       </c>
       <c r="B548" s="4" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="C548" s="3" t="s">
         <v>1126</v>
@@ -29799,7 +29809,7 @@
         <v>556</v>
       </c>
       <c r="B549" s="4" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="C549" s="3" t="s">
         <v>1127</v>
@@ -29810,7 +29820,7 @@
         <v>557</v>
       </c>
       <c r="B550" s="4" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="C550" s="3" t="s">
         <v>1595</v>
@@ -29821,7 +29831,7 @@
         <v>558</v>
       </c>
       <c r="B551" s="4" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="C551" s="3" t="s">
         <v>1506</v>
@@ -29832,7 +29842,7 @@
         <v>559</v>
       </c>
       <c r="B552" s="4" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="C552" s="3" t="s">
         <v>1507</v>
@@ -29843,7 +29853,7 @@
         <v>562</v>
       </c>
       <c r="B553" s="4" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="C553" s="3" t="s">
         <v>911</v>
@@ -29950,10 +29960,10 @@
         <v>570</v>
       </c>
       <c r="B563" s="4" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="C563" s="3" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.4">
@@ -30071,7 +30081,7 @@
         <v>586</v>
       </c>
       <c r="B574" s="4" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="C574" s="3" t="s">
         <v>1520</v>
@@ -30082,7 +30092,7 @@
         <v>585</v>
       </c>
       <c r="B575" s="4" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="C575" s="3" t="s">
         <v>1521</v>
@@ -30093,7 +30103,7 @@
         <v>584</v>
       </c>
       <c r="B576" s="4" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="C576" s="3" t="s">
         <v>1522</v>
@@ -30126,7 +30136,7 @@
         <v>582</v>
       </c>
       <c r="B579" s="4" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="C579" s="3" t="s">
         <v>1525</v>
@@ -30148,7 +30158,7 @@
         <v>594</v>
       </c>
       <c r="B581" s="4" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="C581" s="3" t="s">
         <v>1004</v>
@@ -30159,7 +30169,7 @@
         <v>593</v>
       </c>
       <c r="B582" s="4" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
       <c r="C582" s="3" t="s">
         <v>1009</v>
@@ -30170,7 +30180,7 @@
         <v>592</v>
       </c>
       <c r="B583" s="4" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
       <c r="C583" s="3" t="s">
         <v>1008</v>
@@ -30181,7 +30191,7 @@
         <v>591</v>
       </c>
       <c r="B584" s="4" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="C584" s="3" t="s">
         <v>1001</v>
@@ -30192,7 +30202,7 @@
         <v>590</v>
       </c>
       <c r="B585" s="4" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
       <c r="C585" s="3" t="s">
         <v>1003</v>
@@ -30203,7 +30213,7 @@
         <v>596</v>
       </c>
       <c r="B586" s="4" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
       <c r="C586" s="3" t="s">
         <v>1527</v>
@@ -30214,7 +30224,7 @@
         <v>595</v>
       </c>
       <c r="B587" s="4" t="s">
-        <v>2451</v>
+        <v>2449</v>
       </c>
       <c r="C587" s="3" t="s">
         <v>1528</v>
@@ -30225,7 +30235,7 @@
         <v>597</v>
       </c>
       <c r="B588" s="4" t="s">
-        <v>2452</v>
+        <v>2450</v>
       </c>
       <c r="C588" s="3" t="s">
         <v>1529</v>
@@ -30258,7 +30268,7 @@
         <v>600</v>
       </c>
       <c r="B591" s="4" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="C591" s="3" t="s">
         <v>980</v>
@@ -30269,7 +30279,7 @@
         <v>601</v>
       </c>
       <c r="B592" s="4" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="C592" s="3" t="s">
         <v>1532</v>
@@ -30280,7 +30290,7 @@
         <v>602</v>
       </c>
       <c r="B593" s="4" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="C593" s="3" t="s">
         <v>1533</v>
@@ -30291,7 +30301,7 @@
         <v>603</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="C594" s="3" t="s">
         <v>1534</v>
@@ -30302,7 +30312,7 @@
         <v>604</v>
       </c>
       <c r="B595" s="4" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="C595" s="3" t="s">
         <v>1535</v>
@@ -30313,7 +30323,7 @@
         <v>605</v>
       </c>
       <c r="B596" s="4" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="C596" s="3" t="s">
         <v>1536</v>
@@ -30335,7 +30345,7 @@
         <v>607</v>
       </c>
       <c r="B598" s="4" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="C598" s="3" t="s">
         <v>1538</v>
@@ -30346,7 +30356,7 @@
         <v>608</v>
       </c>
       <c r="B599" s="4" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="C599" s="3" t="s">
         <v>1539</v>
@@ -30357,7 +30367,7 @@
         <v>609</v>
       </c>
       <c r="B600" s="4" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="C600" s="3" t="s">
         <v>1540</v>
@@ -30368,7 +30378,7 @@
         <v>610</v>
       </c>
       <c r="B601" s="4" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="C601" s="3" t="s">
         <v>1541</v>
@@ -30379,7 +30389,7 @@
         <v>612</v>
       </c>
       <c r="B602" s="4" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="C602" s="3" t="s">
         <v>1542</v>
@@ -30390,7 +30400,7 @@
         <v>611</v>
       </c>
       <c r="B603" s="4" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
       <c r="C603" s="3" t="s">
         <v>1543</v>
@@ -30401,7 +30411,7 @@
         <v>577</v>
       </c>
       <c r="B604" s="4" t="s">
-        <v>2465</v>
+        <v>2463</v>
       </c>
       <c r="C604" s="3" t="s">
         <v>1544</v>
@@ -30423,7 +30433,7 @@
         <v>614</v>
       </c>
       <c r="B606" s="4" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="C606" s="3" t="s">
         <v>1546</v>
@@ -30434,10 +30444,10 @@
         <v>573</v>
       </c>
       <c r="B607" s="4" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="C607" s="3" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.4">
@@ -30445,7 +30455,7 @@
         <v>619</v>
       </c>
       <c r="B608" s="4" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="C608" s="3" t="s">
         <v>1547</v>
@@ -30456,7 +30466,7 @@
         <v>618</v>
       </c>
       <c r="B609" s="4" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="C609" s="3" t="s">
         <v>1548</v>
@@ -30467,7 +30477,7 @@
         <v>617</v>
       </c>
       <c r="B610" s="4" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="C610" s="3" t="s">
         <v>1438</v>
@@ -30478,7 +30488,7 @@
         <v>616</v>
       </c>
       <c r="B611" s="4" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="C611" s="3" t="s">
         <v>1549</v>
@@ -30489,7 +30499,7 @@
         <v>615</v>
       </c>
       <c r="B612" s="4" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="C612" s="3" t="s">
         <v>1215</v>
@@ -30522,7 +30532,7 @@
         <v>622</v>
       </c>
       <c r="B615" s="4" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="C615" s="3" t="s">
         <v>880</v>
@@ -30555,7 +30565,7 @@
         <v>623</v>
       </c>
       <c r="B618" s="4" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="C618" s="3" t="s">
         <v>983</v>
@@ -30566,7 +30576,7 @@
         <v>626</v>
       </c>
       <c r="B619" s="4" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="C619" s="3" t="s">
         <v>855</v>
@@ -30577,7 +30587,7 @@
         <v>627</v>
       </c>
       <c r="B620" s="4" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="C620" s="3" t="s">
         <v>856</v>
@@ -30599,7 +30609,7 @@
         <v>629</v>
       </c>
       <c r="B622" s="4" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="C622" s="3" t="s">
         <v>883</v>
@@ -30610,7 +30620,7 @@
         <v>630</v>
       </c>
       <c r="B623" s="4" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="C623" s="3" t="s">
         <v>884</v>
@@ -30621,7 +30631,7 @@
         <v>631</v>
       </c>
       <c r="B624" s="4" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
       <c r="C624" s="3" t="s">
         <v>885</v>
@@ -30632,7 +30642,7 @@
         <v>632</v>
       </c>
       <c r="B625" s="4" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
       <c r="C625" s="3" t="s">
         <v>1033</v>
@@ -30643,7 +30653,7 @@
         <v>633</v>
       </c>
       <c r="B626" s="4" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="C626" s="3" t="s">
         <v>1034</v>
@@ -30654,7 +30664,7 @@
         <v>634</v>
       </c>
       <c r="B627" s="4" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="C627" s="3" t="s">
         <v>1035</v>
@@ -30665,7 +30675,7 @@
         <v>635</v>
       </c>
       <c r="B628" s="4" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="C628" s="3" t="s">
         <v>1076</v>
@@ -30676,7 +30686,7 @@
         <v>636</v>
       </c>
       <c r="B629" s="4" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="C629" s="3" t="s">
         <v>1065</v>
@@ -30709,7 +30719,7 @@
         <v>639</v>
       </c>
       <c r="B632" s="4" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="C632" s="3" t="s">
         <v>1017</v>
@@ -30720,7 +30730,7 @@
         <v>640</v>
       </c>
       <c r="B633" s="4" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
       <c r="C633" s="3" t="s">
         <v>1018</v>
@@ -30731,7 +30741,7 @@
         <v>641</v>
       </c>
       <c r="B634" s="4" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="C634" s="3" t="s">
         <v>1019</v>
@@ -30753,7 +30763,7 @@
         <v>643</v>
       </c>
       <c r="B636" s="4" t="s">
-        <v>2487</v>
+        <v>2485</v>
       </c>
       <c r="C636" s="3" t="s">
         <v>1026</v>
@@ -30764,7 +30774,7 @@
         <v>644</v>
       </c>
       <c r="B637" s="4" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
       <c r="C637" s="3" t="s">
         <v>1056</v>
@@ -30775,7 +30785,7 @@
         <v>645</v>
       </c>
       <c r="B638" s="4" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="C638" s="3" t="s">
         <v>1059</v>
@@ -30786,7 +30796,7 @@
         <v>646</v>
       </c>
       <c r="B639" s="4" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
       <c r="C639" s="3" t="s">
         <v>1060</v>
@@ -30797,7 +30807,7 @@
         <v>647</v>
       </c>
       <c r="B640" s="4" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="C640" s="3" t="s">
         <v>1061</v>
@@ -30808,7 +30818,7 @@
         <v>648</v>
       </c>
       <c r="B641" s="4" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="C641" s="3" t="s">
         <v>1062</v>
@@ -30841,7 +30851,7 @@
         <v>651</v>
       </c>
       <c r="B644" s="4" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="C644" s="3" t="s">
         <v>1073</v>
@@ -30852,7 +30862,7 @@
         <v>652</v>
       </c>
       <c r="B645" s="4" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
       <c r="C645" s="3" t="s">
         <v>1074</v>
@@ -30863,7 +30873,7 @@
         <v>653</v>
       </c>
       <c r="B646" s="4" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
       <c r="C646" s="3" t="s">
         <v>1050</v>
@@ -30874,7 +30884,7 @@
         <v>654</v>
       </c>
       <c r="B647" s="4" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="C647" s="3" t="s">
         <v>1051</v>
@@ -30885,7 +30895,7 @@
         <v>655</v>
       </c>
       <c r="B648" s="4" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
       <c r="C648" s="3" t="s">
         <v>1027</v>
@@ -30896,7 +30906,7 @@
         <v>656</v>
       </c>
       <c r="B649" s="4" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
       <c r="C649" s="3" t="s">
         <v>1028</v>
@@ -30907,7 +30917,7 @@
         <v>657</v>
       </c>
       <c r="B650" s="4" t="s">
-        <v>2499</v>
+        <v>2497</v>
       </c>
       <c r="C650" s="3" t="s">
         <v>1052</v>
@@ -30918,7 +30928,7 @@
         <v>658</v>
       </c>
       <c r="B651" s="4" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
       <c r="C651" s="3" t="s">
         <v>1106</v>
@@ -30929,7 +30939,7 @@
         <v>659</v>
       </c>
       <c r="B652" s="4" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
       <c r="C652" s="3" t="s">
         <v>1107</v>
@@ -30940,7 +30950,7 @@
         <v>660</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>2502</v>
+        <v>2500</v>
       </c>
       <c r="C653" s="3" t="s">
         <v>1108</v>
@@ -30951,7 +30961,7 @@
         <v>661</v>
       </c>
       <c r="B654" s="4" t="s">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="C654" s="3" t="s">
         <v>1077</v>
@@ -30962,7 +30972,7 @@
         <v>662</v>
       </c>
       <c r="B655" s="4" t="s">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="C655" s="3" t="s">
         <v>1078</v>
@@ -30973,7 +30983,7 @@
         <v>663</v>
       </c>
       <c r="B656" s="4" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
       <c r="C656" s="3" t="s">
         <v>1089</v>
@@ -30984,7 +30994,7 @@
         <v>664</v>
       </c>
       <c r="B657" s="4" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
       <c r="C657" s="3" t="s">
         <v>1090</v>
@@ -31006,7 +31016,7 @@
         <v>666</v>
       </c>
       <c r="B659" s="4" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="C659" s="3" t="s">
         <v>1091</v>
@@ -31017,7 +31027,7 @@
         <v>667</v>
       </c>
       <c r="B660" s="4" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="C660" s="3" t="s">
         <v>1094</v>
@@ -31028,7 +31038,7 @@
         <v>668</v>
       </c>
       <c r="B661" s="4" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="C661" s="3" t="s">
         <v>1095</v>
@@ -31039,7 +31049,7 @@
         <v>669</v>
       </c>
       <c r="B662" s="4" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="C662" s="3" t="s">
         <v>1096</v>
@@ -31050,7 +31060,7 @@
         <v>670</v>
       </c>
       <c r="B663" s="4" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="C663" s="3" t="s">
         <v>1053</v>
@@ -31061,7 +31071,7 @@
         <v>671</v>
       </c>
       <c r="B664" s="4" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
       <c r="C664" s="3" t="s">
         <v>1049</v>
@@ -31083,7 +31093,7 @@
         <v>673</v>
       </c>
       <c r="B666" s="4" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="C666" s="3" t="s">
         <v>1100</v>
@@ -31094,7 +31104,7 @@
         <v>674</v>
       </c>
       <c r="B667" s="4" t="s">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="C667" s="3" t="s">
         <v>1101</v>
@@ -31105,7 +31115,7 @@
         <v>675</v>
       </c>
       <c r="B668" s="4" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="C668" s="3" t="s">
         <v>1102</v>
@@ -31116,7 +31126,7 @@
         <v>676</v>
       </c>
       <c r="B669" s="4" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="C669" s="3" t="s">
         <v>1103</v>
@@ -31127,7 +31137,7 @@
         <v>677</v>
       </c>
       <c r="B670" s="4" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="C670" s="3" t="s">
         <v>1104</v>
@@ -31138,7 +31148,7 @@
         <v>678</v>
       </c>
       <c r="B671" s="4" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="C671" s="3" t="s">
         <v>1105</v>
@@ -31149,7 +31159,7 @@
         <v>679</v>
       </c>
       <c r="B672" s="4" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="C672" s="3" t="s">
         <v>1110</v>
@@ -31160,7 +31170,7 @@
         <v>680</v>
       </c>
       <c r="B673" s="4" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="C673" s="3" t="s">
         <v>1111</v>
@@ -31171,7 +31181,7 @@
         <v>681</v>
       </c>
       <c r="B674" s="4" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="C674" s="3" t="s">
         <v>1032</v>
@@ -31182,7 +31192,7 @@
         <v>682</v>
       </c>
       <c r="B675" s="4" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="C675" s="3" t="s">
         <v>1066</v>
@@ -31193,7 +31203,7 @@
         <v>683</v>
       </c>
       <c r="B676" s="4" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="C676" s="3" t="s">
         <v>1067</v>
@@ -31204,7 +31214,7 @@
         <v>684</v>
       </c>
       <c r="B677" s="4" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="C677" s="3" t="s">
         <v>1069</v>
@@ -31215,7 +31225,7 @@
         <v>685</v>
       </c>
       <c r="B678" s="4" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="C678" s="3" t="s">
         <v>1070</v>
@@ -31226,7 +31236,7 @@
         <v>686</v>
       </c>
       <c r="B679" s="4" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="C679" s="3" t="s">
         <v>1071</v>
@@ -31237,7 +31247,7 @@
         <v>687</v>
       </c>
       <c r="B680" s="4" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="C680" s="3" t="s">
         <v>1072</v>
@@ -31248,7 +31258,7 @@
         <v>688</v>
       </c>
       <c r="B681" s="4" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="C681" s="3" t="s">
         <v>1038</v>
@@ -31259,7 +31269,7 @@
         <v>689</v>
       </c>
       <c r="B682" s="4" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="C682" s="3" t="s">
         <v>1039</v>
@@ -31270,7 +31280,7 @@
         <v>690</v>
       </c>
       <c r="B683" s="4" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="C683" s="3" t="s">
         <v>1040</v>
@@ -31292,7 +31302,7 @@
         <v>692</v>
       </c>
       <c r="B685" s="4" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="C685" s="3" t="s">
         <v>1043</v>
@@ -31303,7 +31313,7 @@
         <v>693</v>
       </c>
       <c r="B686" s="4" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="C686" s="3" t="s">
         <v>1042</v>
@@ -31314,7 +31324,7 @@
         <v>694</v>
       </c>
       <c r="B687" s="4" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="C687" s="3" t="s">
         <v>1044</v>
@@ -31325,7 +31335,7 @@
         <v>695</v>
       </c>
       <c r="B688" s="4" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="C688" s="3" t="s">
         <v>1047</v>
@@ -31336,7 +31346,7 @@
         <v>696</v>
       </c>
       <c r="B689" s="4" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="C689" s="3" t="s">
         <v>1048</v>
@@ -31358,7 +31368,7 @@
         <v>698</v>
       </c>
       <c r="B691" s="4" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="C691" s="3" t="s">
         <v>1064</v>
@@ -31369,7 +31379,7 @@
         <v>699</v>
       </c>
       <c r="B692" s="4" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="C692" s="3" t="s">
         <v>1097</v>
@@ -31380,7 +31390,7 @@
         <v>700</v>
       </c>
       <c r="B693" s="4" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="C693" s="3" t="s">
         <v>1068</v>
@@ -31391,7 +31401,7 @@
         <v>701</v>
       </c>
       <c r="B694" s="4" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
       <c r="C694" s="3" t="s">
         <v>1022</v>
@@ -31402,7 +31412,7 @@
         <v>702</v>
       </c>
       <c r="B695" s="4" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="C695" s="3" t="s">
         <v>1023</v>
@@ -31413,7 +31423,7 @@
         <v>703</v>
       </c>
       <c r="B696" s="4" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
       <c r="C696" s="3" t="s">
         <v>1024</v>
@@ -31424,7 +31434,7 @@
         <v>704</v>
       </c>
       <c r="B697" s="4" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="C697" s="3" t="s">
         <v>1025</v>
@@ -31435,7 +31445,7 @@
         <v>705</v>
       </c>
       <c r="B698" s="4" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
       <c r="C698" s="3" t="s">
         <v>1021</v>
@@ -31457,7 +31467,7 @@
         <v>707</v>
       </c>
       <c r="B700" s="4" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
       <c r="C700" s="3" t="s">
         <v>1123</v>
@@ -31479,7 +31489,7 @@
         <v>709</v>
       </c>
       <c r="B702" s="4" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="C702" s="3" t="s">
         <v>1121</v>
@@ -31490,7 +31500,7 @@
         <v>710</v>
       </c>
       <c r="B703" s="4" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
       <c r="C703" s="3" t="s">
         <v>1122</v>
@@ -31523,7 +31533,7 @@
         <v>713</v>
       </c>
       <c r="B706" s="4" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="C706" s="3" t="s">
         <v>1054</v>
@@ -31534,7 +31544,7 @@
         <v>718</v>
       </c>
       <c r="B707" s="4" t="s">
-        <v>2547</v>
+        <v>2545</v>
       </c>
       <c r="C707" s="3" t="s">
         <v>986</v>
@@ -31545,7 +31555,7 @@
         <v>717</v>
       </c>
       <c r="B708" s="4" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
       <c r="C708" s="3" t="s">
         <v>714</v>
@@ -31556,7 +31566,7 @@
         <v>716</v>
       </c>
       <c r="B709" s="4" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
       <c r="C709" s="3" t="s">
         <v>715</v>
@@ -31567,7 +31577,7 @@
         <v>719</v>
       </c>
       <c r="B710" s="4" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
       <c r="C710" s="3" t="s">
         <v>930</v>
@@ -31589,7 +31599,7 @@
         <v>721</v>
       </c>
       <c r="B712" s="4" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="C712" s="3" t="s">
         <v>952</v>
@@ -31600,7 +31610,7 @@
         <v>723</v>
       </c>
       <c r="B713" s="4" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="C713" s="3" t="s">
         <v>1085</v>
@@ -31611,7 +31621,7 @@
         <v>722</v>
       </c>
       <c r="B714" s="4" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
       <c r="C714" s="3" t="s">
         <v>1086</v>
@@ -31622,7 +31632,7 @@
         <v>724</v>
       </c>
       <c r="B715" s="4" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="C715" s="3" t="s">
         <v>1063</v>
@@ -31633,7 +31643,7 @@
         <v>725</v>
       </c>
       <c r="B716" s="4" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="C716" s="3" t="s">
         <v>1552</v>
@@ -31644,7 +31654,7 @@
         <v>726</v>
       </c>
       <c r="B717" s="4" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
       <c r="C717" s="3" t="s">
         <v>1075</v>
@@ -31655,7 +31665,7 @@
         <v>727</v>
       </c>
       <c r="B718" s="4" t="s">
-        <v>2557</v>
+        <v>2555</v>
       </c>
       <c r="C718" s="3" t="s">
         <v>1088</v>
@@ -31666,7 +31676,7 @@
         <v>728</v>
       </c>
       <c r="B719" s="4" t="s">
-        <v>2558</v>
+        <v>2556</v>
       </c>
       <c r="C719" s="3" t="s">
         <v>1109</v>
@@ -31677,7 +31687,7 @@
         <v>729</v>
       </c>
       <c r="B720" s="4" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
       <c r="C720" s="3" t="s">
         <v>931</v>
@@ -31688,7 +31698,7 @@
         <v>730</v>
       </c>
       <c r="B721" s="4" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
       <c r="C721" s="3" t="s">
         <v>1087</v>
@@ -31699,7 +31709,7 @@
         <v>734</v>
       </c>
       <c r="B722" s="4" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C722" s="3" t="s">
         <v>888</v>
@@ -31710,7 +31720,7 @@
         <v>733</v>
       </c>
       <c r="B723" s="4" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="C723" s="3" t="s">
         <v>1408</v>
@@ -31721,7 +31731,7 @@
         <v>732</v>
       </c>
       <c r="B724" s="4" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="C724" s="3" t="s">
         <v>1413</v>
@@ -31743,7 +31753,7 @@
         <v>735</v>
       </c>
       <c r="B726" s="4" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
       <c r="C726" s="3" t="s">
         <v>1553</v>
@@ -31754,7 +31764,7 @@
         <v>736</v>
       </c>
       <c r="B727" s="4" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="C727" s="3" t="s">
         <v>839</v>
@@ -31765,7 +31775,7 @@
         <v>737</v>
       </c>
       <c r="B728" s="4" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
       <c r="C728" s="3" t="s">
         <v>840</v>
@@ -31776,7 +31786,7 @@
         <v>738</v>
       </c>
       <c r="B729" s="4" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="C729" s="3" t="s">
         <v>841</v>
@@ -31787,7 +31797,7 @@
         <v>739</v>
       </c>
       <c r="B730" s="4" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="C730" s="3" t="s">
         <v>842</v>
@@ -31798,7 +31808,7 @@
         <v>740</v>
       </c>
       <c r="B731" s="4" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
       <c r="C731" s="3" t="s">
         <v>844</v>
@@ -31809,7 +31819,7 @@
         <v>741</v>
       </c>
       <c r="B732" s="4" t="s">
-        <v>2567</v>
+        <v>2565</v>
       </c>
       <c r="C732" s="3" t="s">
         <v>847</v>
@@ -31820,7 +31830,7 @@
         <v>742</v>
       </c>
       <c r="B733" s="4" t="s">
-        <v>2568</v>
+        <v>2566</v>
       </c>
       <c r="C733" s="3" t="s">
         <v>848</v>
@@ -31831,7 +31841,7 @@
         <v>756</v>
       </c>
       <c r="B734" s="4" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="C734" s="3" t="s">
         <v>849</v>
@@ -31842,7 +31852,7 @@
         <v>743</v>
       </c>
       <c r="B735" s="4" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="C735" s="3" t="s">
         <v>850</v>
@@ -31853,7 +31863,7 @@
         <v>744</v>
       </c>
       <c r="B736" s="4" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="C736" s="3" t="s">
         <v>851</v>
@@ -31864,7 +31874,7 @@
         <v>745</v>
       </c>
       <c r="B737" s="4" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="C737" s="3" t="s">
         <v>852</v>
@@ -31908,7 +31918,7 @@
         <v>753</v>
       </c>
       <c r="B741" s="4" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="C741" s="3" t="s">
         <v>905</v>
@@ -31930,7 +31940,7 @@
         <v>751</v>
       </c>
       <c r="B743" s="4" t="s">
-        <v>2574</v>
+        <v>2572</v>
       </c>
       <c r="C743" s="3" t="s">
         <v>906</v>
@@ -31941,7 +31951,7 @@
         <v>750</v>
       </c>
       <c r="B744" s="4" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="C744" s="3" t="s">
         <v>908</v>
@@ -31952,7 +31962,7 @@
         <v>749</v>
       </c>
       <c r="B745" s="4" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
       <c r="C745" s="3" t="s">
         <v>909</v>
@@ -31963,7 +31973,7 @@
         <v>754</v>
       </c>
       <c r="B746" s="4" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
       <c r="C746" s="3" t="s">
         <v>1029</v>
@@ -31974,7 +31984,7 @@
         <v>755</v>
       </c>
       <c r="B747" s="4" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="C747" s="3" t="s">
         <v>1031</v>
@@ -31985,7 +31995,7 @@
         <v>757</v>
       </c>
       <c r="B748" s="4" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="C748" s="3" t="s">
         <v>853</v>
@@ -31996,7 +32006,7 @@
         <v>758</v>
       </c>
       <c r="B749" s="4" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
       <c r="C749" s="3" t="s">
         <v>843</v>
@@ -32007,7 +32017,7 @@
         <v>759</v>
       </c>
       <c r="B750" s="4" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
       <c r="C750" s="3" t="s">
         <v>1055</v>
@@ -32018,7 +32028,7 @@
         <v>760</v>
       </c>
       <c r="B751" s="4" t="s">
-        <v>2582</v>
+        <v>2580</v>
       </c>
       <c r="C751" s="3" t="s">
         <v>1045</v>
@@ -32040,7 +32050,7 @@
         <v>762</v>
       </c>
       <c r="B753" s="4" t="s">
-        <v>2583</v>
+        <v>2581</v>
       </c>
       <c r="C753" s="3" t="s">
         <v>924</v>
@@ -32062,7 +32072,7 @@
         <v>766</v>
       </c>
       <c r="B755" s="4" t="s">
-        <v>2584</v>
+        <v>2582</v>
       </c>
       <c r="C755" s="3" t="s">
         <v>1555</v>
@@ -32073,7 +32083,7 @@
         <v>765</v>
       </c>
       <c r="B756" s="4" t="s">
-        <v>2585</v>
+        <v>2583</v>
       </c>
       <c r="C756" s="3" t="s">
         <v>1556</v>
@@ -32084,7 +32094,7 @@
         <v>764</v>
       </c>
       <c r="B757" s="4" t="s">
-        <v>2586</v>
+        <v>2584</v>
       </c>
       <c r="C757" s="3" t="s">
         <v>1557</v>
@@ -32095,7 +32105,7 @@
         <v>763</v>
       </c>
       <c r="B758" s="4" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="C758" s="3" t="s">
         <v>1558</v>
@@ -32106,7 +32116,7 @@
         <v>768</v>
       </c>
       <c r="B759" s="4" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="C759" s="3" t="s">
         <v>1030</v>
@@ -32117,7 +32127,7 @@
         <v>769</v>
       </c>
       <c r="B760" s="4" t="s">
-        <v>2589</v>
+        <v>2587</v>
       </c>
       <c r="C760" s="3" t="s">
         <v>985</v>
@@ -32128,7 +32138,7 @@
         <v>771</v>
       </c>
       <c r="B761" s="4" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
       <c r="C761" s="3" t="s">
         <v>1559</v>
@@ -32139,7 +32149,7 @@
         <v>770</v>
       </c>
       <c r="B762" s="4" t="s">
-        <v>2591</v>
+        <v>2589</v>
       </c>
       <c r="C762" s="3" t="s">
         <v>890</v>
@@ -32150,7 +32160,7 @@
         <v>774</v>
       </c>
       <c r="B763" s="4" t="s">
-        <v>2592</v>
+        <v>2590</v>
       </c>
       <c r="C763" s="3" t="s">
         <v>1596</v>
@@ -32161,7 +32171,7 @@
         <v>773</v>
       </c>
       <c r="B764" s="4" t="s">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="C764" s="3" t="s">
         <v>1057</v>
@@ -32172,7 +32182,7 @@
         <v>772</v>
       </c>
       <c r="B765" s="4" t="s">
-        <v>2594</v>
+        <v>2592</v>
       </c>
       <c r="C765" s="3" t="s">
         <v>1058</v>
@@ -32183,7 +32193,7 @@
         <v>775</v>
       </c>
       <c r="B766" s="4" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="C766" s="3" t="s">
         <v>1560</v>
@@ -32194,7 +32204,7 @@
         <v>776</v>
       </c>
       <c r="B767" s="4" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="C767" s="3" t="s">
         <v>1561</v>
@@ -32205,7 +32215,7 @@
         <v>777</v>
       </c>
       <c r="B768" s="4" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
       <c r="C768" s="3" t="s">
         <v>915</v>
@@ -32216,7 +32226,7 @@
         <v>784</v>
       </c>
       <c r="B769" s="4" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
       <c r="C769" s="3" t="s">
         <v>1562</v>
@@ -32227,7 +32237,7 @@
         <v>783</v>
       </c>
       <c r="B770" s="4" t="s">
-        <v>2599</v>
+        <v>2597</v>
       </c>
       <c r="C770" s="3" t="s">
         <v>1563</v>
@@ -32238,7 +32248,7 @@
         <v>782</v>
       </c>
       <c r="B771" s="4" t="s">
-        <v>2600</v>
+        <v>2598</v>
       </c>
       <c r="C771" s="3" t="s">
         <v>1564</v>
@@ -32249,7 +32259,7 @@
         <v>781</v>
       </c>
       <c r="B772" s="4" t="s">
-        <v>2601</v>
+        <v>2599</v>
       </c>
       <c r="C772" s="3" t="s">
         <v>1565</v>
@@ -32260,7 +32270,7 @@
         <v>780</v>
       </c>
       <c r="B773" s="4" t="s">
-        <v>2602</v>
+        <v>2600</v>
       </c>
       <c r="C773" s="3" t="s">
         <v>1566</v>
@@ -32271,7 +32281,7 @@
         <v>779</v>
       </c>
       <c r="B774" s="4" t="s">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="C774" s="3" t="s">
         <v>1567</v>
@@ -32282,7 +32292,7 @@
         <v>778</v>
       </c>
       <c r="B775" s="4" t="s">
-        <v>2604</v>
+        <v>2602</v>
       </c>
       <c r="C775" s="3" t="s">
         <v>1568</v>
@@ -32304,7 +32314,7 @@
         <v>786</v>
       </c>
       <c r="B777" s="4" t="s">
-        <v>2605</v>
+        <v>2603</v>
       </c>
       <c r="C777" s="3" t="s">
         <v>1570</v>
@@ -32326,7 +32336,7 @@
         <v>788</v>
       </c>
       <c r="B779" s="4" t="s">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="C779" s="3" t="s">
         <v>919</v>
@@ -32337,7 +32347,7 @@
         <v>789</v>
       </c>
       <c r="B780" s="4" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="C780" s="3" t="s">
         <v>917</v>
@@ -32348,7 +32358,7 @@
         <v>790</v>
       </c>
       <c r="B781" s="4" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="C781" s="3" t="s">
         <v>918</v>
@@ -32359,7 +32369,7 @@
         <v>799</v>
       </c>
       <c r="B782" s="4" t="s">
-        <v>2609</v>
+        <v>2607</v>
       </c>
       <c r="C782" s="3" t="s">
         <v>1572</v>
@@ -32370,7 +32380,7 @@
         <v>798</v>
       </c>
       <c r="B783" s="4" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
       <c r="C783" s="3" t="s">
         <v>1573</v>
@@ -32381,7 +32391,7 @@
         <v>797</v>
       </c>
       <c r="B784" s="4" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="C784" s="3" t="s">
         <v>1372</v>
@@ -32392,7 +32402,7 @@
         <v>796</v>
       </c>
       <c r="B785" s="4" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="C785" s="3" t="s">
         <v>1373</v>
@@ -32403,7 +32413,7 @@
         <v>795</v>
       </c>
       <c r="B786" s="4" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="C786" s="3" t="s">
         <v>1374</v>
@@ -32414,7 +32424,7 @@
         <v>794</v>
       </c>
       <c r="B787" s="4" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="C787" s="3" t="s">
         <v>1375</v>
@@ -32436,7 +32446,7 @@
         <v>792</v>
       </c>
       <c r="B789" s="4" t="s">
-        <v>2611</v>
+        <v>2609</v>
       </c>
       <c r="C789" s="3" t="s">
         <v>1575</v>
@@ -32447,7 +32457,7 @@
         <v>791</v>
       </c>
       <c r="B790" s="4" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="C790" s="3" t="s">
         <v>1576</v>
@@ -32458,7 +32468,7 @@
         <v>800</v>
       </c>
       <c r="B791" s="4" t="s">
-        <v>2613</v>
+        <v>2611</v>
       </c>
       <c r="C791" s="3" t="s">
         <v>916</v>
@@ -32469,7 +32479,7 @@
         <v>803</v>
       </c>
       <c r="B792" s="4" t="s">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="C792" s="3" t="s">
         <v>1577</v>
@@ -32480,7 +32490,7 @@
         <v>802</v>
       </c>
       <c r="B793" s="4" t="s">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="C793" s="3" t="s">
         <v>1578</v>
@@ -32491,7 +32501,7 @@
         <v>801</v>
       </c>
       <c r="B794" s="4" t="s">
-        <v>2616</v>
+        <v>2614</v>
       </c>
       <c r="C794" s="3" t="s">
         <v>1579</v>
@@ -32502,7 +32512,7 @@
         <v>804</v>
       </c>
       <c r="B795" s="4" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
       <c r="C795" s="3" t="s">
         <v>1046</v>
@@ -32524,7 +32534,7 @@
         <v>809</v>
       </c>
       <c r="B797" s="4" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="C797" s="3" t="s">
         <v>1581</v>
@@ -32535,7 +32545,7 @@
         <v>808</v>
       </c>
       <c r="B798" s="4" t="s">
-        <v>2619</v>
+        <v>2617</v>
       </c>
       <c r="C798" s="3" t="s">
         <v>1582</v>
@@ -32546,7 +32556,7 @@
         <v>807</v>
       </c>
       <c r="B799" s="4" t="s">
-        <v>2620</v>
+        <v>2618</v>
       </c>
       <c r="C799" s="3" t="s">
         <v>1036</v>
@@ -32557,7 +32567,7 @@
         <v>806</v>
       </c>
       <c r="B800" s="4" t="s">
-        <v>2621</v>
+        <v>2619</v>
       </c>
       <c r="C800" s="3" t="s">
         <v>1037</v>
@@ -32568,7 +32578,7 @@
         <v>810</v>
       </c>
       <c r="B801" s="4" t="s">
-        <v>2622</v>
+        <v>2620</v>
       </c>
       <c r="C801" s="3" t="s">
         <v>1583</v>
@@ -32590,7 +32600,7 @@
         <v>812</v>
       </c>
       <c r="B803" s="4" t="s">
-        <v>2623</v>
+        <v>2621</v>
       </c>
       <c r="C803" s="3" t="s">
         <v>1585</v>
@@ -32612,7 +32622,7 @@
         <v>814</v>
       </c>
       <c r="B805" s="4" t="s">
-        <v>2624</v>
+        <v>2622</v>
       </c>
       <c r="C805" s="3" t="s">
         <v>1587</v>
@@ -32634,7 +32644,7 @@
         <v>1593</v>
       </c>
       <c r="B807" s="4" t="s">
-        <v>2625</v>
+        <v>2623</v>
       </c>
       <c r="C807" s="3" t="s">
         <v>1502</v>
@@ -32645,7 +32655,7 @@
         <v>1592</v>
       </c>
       <c r="B808" s="4" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="C808" s="3" t="s">
         <v>1594</v>
@@ -32662,463 +32672,463 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="810" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A810" s="3" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B810" s="4" t="s">
-        <v>1605</v>
+        <v>2711</v>
       </c>
       <c r="C810" s="3" t="s">
-        <v>1607</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A811" s="3" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="B811" s="4" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C811" s="3" t="s">
         <v>1616</v>
-      </c>
-      <c r="C811" s="3" t="s">
-        <v>1618</v>
       </c>
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A812" s="3" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B812" s="4" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C812" s="3" t="s">
         <v>1613</v>
-      </c>
-      <c r="B812" s="4" t="s">
-        <v>1614</v>
-      </c>
-      <c r="C812" s="3" t="s">
-        <v>1615</v>
       </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A813" s="3" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="B813" s="4" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="C813" s="3" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A814" s="3" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="B814" s="4" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="C814" s="3" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A815" s="3" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="B815" s="4" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="C815" s="3" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A816" s="3" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="B816" s="4" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="C816" s="3" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A817" s="3" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="B817" s="4" t="s">
-        <v>2631</v>
+        <v>2629</v>
       </c>
       <c r="C817" s="3" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A818" s="3" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="B818" s="4" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="C818" s="3" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A819" s="3" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="B819" s="4" t="s">
-        <v>2633</v>
+        <v>2631</v>
       </c>
       <c r="C819" s="3" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A820" s="3" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="B820" s="4" t="s">
-        <v>2634</v>
+        <v>2632</v>
       </c>
       <c r="C820" s="3" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A821" s="3" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="B821" s="4" t="s">
-        <v>2635</v>
+        <v>2633</v>
       </c>
       <c r="C821" s="3" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A822" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B822" s="4" t="s">
+        <v>2634</v>
+      </c>
+      <c r="C822" s="3" t="s">
         <v>1637</v>
-      </c>
-      <c r="B822" s="4" t="s">
-        <v>2636</v>
-      </c>
-      <c r="C822" s="3" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="823" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A823" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B823" s="4" t="s">
+        <v>2635</v>
+      </c>
+      <c r="C823" s="3" t="s">
         <v>1638</v>
-      </c>
-      <c r="B823" s="4" t="s">
-        <v>2637</v>
-      </c>
-      <c r="C823" s="3" t="s">
-        <v>1640</v>
       </c>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A824" s="3" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="B824" s="4" t="s">
-        <v>2638</v>
+        <v>2636</v>
       </c>
       <c r="C824" s="3" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A825" s="3" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="B825" s="4" t="s">
-        <v>2639</v>
+        <v>2637</v>
       </c>
       <c r="C825" s="3" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A826" s="3" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="B826" s="4" t="s">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="C826" s="3" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A827" s="3" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="B827" s="4" t="s">
-        <v>2641</v>
+        <v>2639</v>
       </c>
       <c r="C827" s="3" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A828" s="3" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="B828" s="4" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="C828" s="3" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A829" s="3" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="B829" s="4" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="C829" s="3" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="830" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A830" s="3" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="B830" s="4" t="s">
-        <v>2644</v>
+        <v>2642</v>
       </c>
       <c r="C830" s="3" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="831" spans="1:3" ht="95" x14ac:dyDescent="0.4">
       <c r="A831" s="3" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="B831" s="4" t="s">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="C831" s="3" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A832" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B832" s="4" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C832" s="3" t="s">
         <v>1657</v>
-      </c>
-      <c r="B832" s="4" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C832" s="3" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="833" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A833" s="3" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="B833" s="4" t="s">
-        <v>2646</v>
+        <v>2644</v>
       </c>
       <c r="C833" s="3" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="834" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A834" s="3" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B834" s="4" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C834" s="3" t="s">
         <v>1667</v>
-      </c>
-      <c r="B834" s="4" t="s">
-        <v>1668</v>
-      </c>
-      <c r="C834" s="3" t="s">
-        <v>1669</v>
       </c>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A835" s="3" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="B835" s="4" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="C835" s="3" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A836" s="3" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="B836" s="4" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="C836" s="3" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A837" s="3" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B837" s="4" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C837" s="3" t="s">
         <v>1675</v>
-      </c>
-      <c r="B837" s="4" t="s">
-        <v>1676</v>
-      </c>
-      <c r="C837" s="3" t="s">
-        <v>1677</v>
       </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A838" s="3" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="B838" s="4" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="C838" s="3" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A839" s="3" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="B839" s="4" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
       <c r="C839" s="3" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A840" s="3" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="B840" s="4" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
       <c r="C840" s="3" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A841" s="3" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="B841" s="4" t="s">
-        <v>2650</v>
+        <v>2648</v>
       </c>
       <c r="C841" s="3" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A842" s="3" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="B842" s="4" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="C842" s="3" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A843" s="3" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="B843" s="4" t="s">
-        <v>2652</v>
+        <v>2650</v>
       </c>
       <c r="C843" s="3" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A844" s="3" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="B844" s="4" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="C844" s="3" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A845" s="3" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="B845" s="4" t="s">
-        <v>2653</v>
+        <v>2651</v>
       </c>
       <c r="C845" s="3" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A846" s="3" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="B846" s="4" t="s">
-        <v>2654</v>
+        <v>2652</v>
       </c>
       <c r="C846" s="3" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A847" s="3" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="B847" s="4" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="C847" s="3" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A848" s="3" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="B848" s="4" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C848" s="3" t="s">
         <v>1695</v>
-      </c>
-      <c r="C848" s="3" t="s">
-        <v>1697</v>
       </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A849" s="3" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B849" s="4" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C849" s="3" t="s">
         <v>1698</v>
-      </c>
-      <c r="B849" s="4" t="s">
-        <v>1699</v>
-      </c>
-      <c r="C849" s="3" t="s">
-        <v>1700</v>
       </c>
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A850" s="3" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B850" s="4" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C850" s="3" t="s">
         <v>1701</v>
-      </c>
-      <c r="B850" s="4" t="s">
-        <v>1702</v>
-      </c>
-      <c r="C850" s="3" t="s">
-        <v>1703</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A851" s="3" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="B851" s="4" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="C851" s="3" t="s">
         <v>1235</v>
@@ -33126,901 +33136,901 @@
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A852" s="3" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="B852" s="4" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="C852" s="3" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A853" s="3" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="B853" s="4" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="C853" s="3" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A854" s="3" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="B854" s="4" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="C854" s="3" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A855" s="3" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="B855" s="4" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="C855" s="3" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A856" s="3" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="B856" s="4" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="C856" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A857" s="3" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="B857" s="4" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="C857" s="3" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A858" s="3" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="B858" s="4" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="C858" s="3" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A859" s="3" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="B859" s="4" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="C859" s="3" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A860" s="3" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="B860" s="4" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="C860" s="3" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A861" s="3" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="B861" s="4" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="C861" s="3" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A862" s="3" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="B862" s="4" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="C862" s="3" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A863" s="3" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="B863" s="4" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="C863" s="3" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A864" s="3" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="B864" s="4" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="C864" s="3" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A865" s="3" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="B865" s="4" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="C865" s="3" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A866" s="3" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="B866" s="4" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="C866" s="3" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A867" s="3" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="B867" s="4" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="C867" s="3" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A868" s="3" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="B868" s="4" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="C868" s="3" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A869" s="3" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="B869" s="4" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="C869" s="3" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A870" s="3" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="B870" s="4" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="C870" s="3" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A871" s="3" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="B871" s="4" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="C871" s="3" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="872" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A872" s="3" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B872" s="4" t="s">
         <v>1766</v>
       </c>
-      <c r="B872" s="4" t="s">
-        <v>1768</v>
-      </c>
       <c r="C872" s="3" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="873" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A873" s="3" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B873" s="4" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C873" s="3" t="s">
         <v>1769</v>
-      </c>
-      <c r="B873" s="4" t="s">
-        <v>1770</v>
-      </c>
-      <c r="C873" s="3" t="s">
-        <v>1771</v>
       </c>
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A874" s="3" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="B874" s="4" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="C874" s="3" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A875" s="3" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="B875" s="4" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="C875" s="3" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A876" s="3" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="B876" s="4" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="C876" s="3" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="877" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A877" s="3" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="B877" s="4" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="C877" s="3" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="878" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A878" s="3" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="B878" s="4" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="C878" s="3" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A879" s="3" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="B879" s="4" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="C879" s="3" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A880" s="3" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="B880" s="4" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="C880" s="3" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A881" s="3" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="B881" s="4" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="C881" s="3" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A882" s="3" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="B882" s="4" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="C882" s="3" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="883" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A883" s="3" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="B883" s="4" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="C883" s="3" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="884" spans="1:3" ht="285" x14ac:dyDescent="0.4">
       <c r="A884" s="3" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="B884" s="4" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="C884" s="3" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="885" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A885" s="3" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="B885" s="4" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C885" s="3" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="886" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A886" s="3" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="B886" s="4" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="C886" s="3" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="887" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A887" s="3" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="B887" s="4" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="C887" s="3" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="888" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A888" s="3" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="B888" s="4" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="C888" s="3" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="889" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A889" s="3" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="B889" s="4" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="C889" s="3" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="890" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A890" s="3" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="B890" s="4" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="C890" s="3" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A891" s="3" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="B891" s="4" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="C891" s="3" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A892" s="3" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="B892" s="4" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="C892" s="3" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A893" s="3" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="B893" s="4" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="C893" s="3" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="894" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A894" s="3" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="B894" s="4" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="C894" s="3" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="895" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A895" s="3" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B895" s="4" t="s">
         <v>1825</v>
       </c>
-      <c r="B895" s="4" t="s">
+      <c r="C895" s="3" t="s">
         <v>1827</v>
-      </c>
-      <c r="C895" s="3" t="s">
-        <v>1829</v>
       </c>
     </row>
     <row r="896" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A896" s="3" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B896" s="4" t="s">
         <v>1826</v>
       </c>
-      <c r="B896" s="4" t="s">
+      <c r="C896" s="3" t="s">
         <v>1828</v>
-      </c>
-      <c r="C896" s="3" t="s">
-        <v>1830</v>
       </c>
     </row>
     <row r="897" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A897" s="3" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B897" s="4" t="s">
         <v>1831</v>
       </c>
-      <c r="B897" s="4" t="s">
-        <v>1833</v>
-      </c>
       <c r="C897" s="3" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="898" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A898" s="3" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B898" s="4" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C898" s="3" t="s">
         <v>1834</v>
-      </c>
-      <c r="B898" s="4" t="s">
-        <v>1835</v>
-      </c>
-      <c r="C898" s="3" t="s">
-        <v>1836</v>
       </c>
     </row>
     <row r="899" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A899" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B899" s="4" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C899" s="3" t="s">
         <v>1837</v>
-      </c>
-      <c r="B899" s="4" t="s">
-        <v>1838</v>
-      </c>
-      <c r="C899" s="3" t="s">
-        <v>1839</v>
       </c>
     </row>
     <row r="900" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A900" s="3" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="B900" s="4" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C900" s="3" t="s">
         <v>1840</v>
-      </c>
-      <c r="C900" s="3" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="901" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A901" s="3" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="B901" s="4" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="C901" s="3" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A902" s="3" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B902" s="4" t="s">
         <v>1847</v>
       </c>
-      <c r="B902" s="4" t="s">
-        <v>1849</v>
-      </c>
       <c r="C902" s="3" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="903" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A903" s="3" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="B903" s="4" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
       <c r="C903" s="3" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="904" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A904" s="3" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="B904" s="4" t="s">
-        <v>2659</v>
+        <v>2657</v>
       </c>
       <c r="C904" s="3" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="905" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A905" s="3" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B905" s="4" t="s">
         <v>1855</v>
       </c>
-      <c r="B905" s="4" t="s">
-        <v>1857</v>
-      </c>
       <c r="C905" s="3" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="906" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A906" s="3" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="B906" s="4" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="C906" s="3" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="907" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A907" s="3" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="B907" s="4" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="C907" s="3" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="908" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A908" s="3" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="B908" s="4" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="C908" s="3" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="909" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A909" s="3" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="B909" s="4" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="C909" s="3" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="910" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A910" s="3" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="B910" s="4" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="C910" s="3" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="911" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A911" s="3" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="B911" s="4" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="C911" s="3" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="912" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A912" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B912" s="4" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C912" s="3" t="s">
         <v>1870</v>
-      </c>
-      <c r="B912" s="4" t="s">
-        <v>1871</v>
-      </c>
-      <c r="C912" s="3" t="s">
-        <v>1872</v>
       </c>
     </row>
     <row r="913" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A913" s="3" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="B913" s="4" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="C913" s="3" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="914" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A914" s="3" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B914" s="4" t="s">
         <v>1874</v>
       </c>
-      <c r="B914" s="4" t="s">
-        <v>1876</v>
-      </c>
       <c r="C914" s="3" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A915" s="3" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="B915" s="4" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="C915" s="3" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="916" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A916" s="3" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="B916" s="4" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
       <c r="C916" s="3" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="917" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A917" s="3" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B917" s="4" t="s">
         <v>1882</v>
       </c>
-      <c r="B917" s="4" t="s">
-        <v>1884</v>
-      </c>
       <c r="C917" s="3" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="918" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A918" s="3" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="B918" s="4" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="C918" s="3" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="919" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A919" s="3" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="B919" s="4" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="C919" s="3" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="920" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A920" s="3" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B920" s="4" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C920" s="3" t="s">
         <v>1916</v>
-      </c>
-      <c r="B920" s="4" t="s">
-        <v>1917</v>
-      </c>
-      <c r="C920" s="3" t="s">
-        <v>1918</v>
       </c>
     </row>
     <row r="921" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A921" s="3" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="B921" s="4" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="C921" s="3" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="922" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A922" s="3" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="B922" s="4" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="C922" s="3" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="923" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A923" s="3" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="B923" s="4" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="C923" s="3" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="924" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A924" s="3" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="B924" s="4" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="C924" s="3" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="925" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A925" s="3" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="B925" s="4" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="C925" s="3" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A926" s="3" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="B926" s="4" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="C926" s="3" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="927" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A927" s="3" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="B927" s="4" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="C927" s="3" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="928" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A928" s="3" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="B928" s="4" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="C928" s="3" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="929" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A929" s="3" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="B929" s="4" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="C929" s="3" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="930" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A930" s="3" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="B930" s="4" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="C930" s="3" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="931" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A931" s="3" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="B931" s="4" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C931" s="3" t="s">
         <v>1920</v>
-      </c>
-      <c r="C931" s="3" t="s">
-        <v>1922</v>
       </c>
     </row>
     <row r="932" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A932" s="3" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="B932" s="4" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="C932" s="3" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="933" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A933" s="3" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="B933" s="4" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="C933" s="3" t="s">
         <v>1551</v>
@@ -34028,233 +34038,244 @@
     </row>
     <row r="934" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A934" s="3" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="B934" s="4" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="C934" s="3" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="935" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A935" s="3" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="B935" s="4" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="C935" s="3" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="936" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A936" s="3" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="B936" s="4" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="C936" s="3" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A937" s="3" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="B937" s="4" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="C937" s="3" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="938" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A938" s="3" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="B938" s="4" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="C938" s="3" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="939" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A939" s="3" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="B939" s="4" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="C939" s="3" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="940" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A940" s="3" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="B940" s="4" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="C940" s="3" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="941" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A941" s="3" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="B941" s="4" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="C941" s="3" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="942" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A942" s="3" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="B942" s="4" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="C942" s="3" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="943" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A943" s="3" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="B943" s="4" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="C943" s="3" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="944" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A944" s="3" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="B944" s="4" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="C944" s="3" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="945" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A945" s="3" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B945" s="4" t="s">
+        <v>2679</v>
+      </c>
+      <c r="C945" s="3" t="s">
         <v>2680</v>
-      </c>
-      <c r="B945" s="4" t="s">
-        <v>2681</v>
-      </c>
-      <c r="C945" s="3" t="s">
-        <v>2682</v>
       </c>
     </row>
     <row r="946" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A946" s="3" t="s">
-        <v>2696</v>
+        <v>2694</v>
       </c>
       <c r="B946" s="4" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
       <c r="C946" s="3" t="s">
-        <v>2697</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="947" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A947" s="3" t="s">
-        <v>2695</v>
+        <v>2693</v>
       </c>
       <c r="B947" s="4" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="C947" s="3" t="s">
-        <v>2698</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A948" s="3" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
       <c r="B948" s="4" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
       <c r="C948" s="3" t="s">
-        <v>2699</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="949" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A949" s="3" t="s">
-        <v>2693</v>
+        <v>2691</v>
       </c>
       <c r="B949" s="4" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="C949" s="3" t="s">
-        <v>2700</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="950" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A950" s="3" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
       <c r="B950" s="4" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="C950" s="3" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="951" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A951" s="3" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
       <c r="B951" s="4" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
       <c r="C951" s="3" t="s">
-        <v>2702</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="952" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A952" s="3" t="s">
-        <v>2690</v>
+        <v>2688</v>
       </c>
       <c r="B952" s="4" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
       <c r="C952" s="3" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="953" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A953" s="3" t="s">
+        <v>2702</v>
+      </c>
+      <c r="B953" s="4" t="s">
+        <v>2703</v>
+      </c>
+      <c r="C953" s="3" t="s">
         <v>2704</v>
-      </c>
-      <c r="B953" s="4" t="s">
-        <v>2705</v>
-      </c>
-      <c r="C953" s="3" t="s">
-        <v>2706</v>
       </c>
     </row>
     <row r="954" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A954" s="3" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B954" s="4" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C954" s="3" t="s">
         <v>2707</v>
       </c>
-      <c r="B954" s="4" t="s">
+    </row>
+    <row r="955" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A955" s="3" t="s">
+        <v>2709</v>
+      </c>
+      <c r="B955" s="4" t="s">
+        <v>2710</v>
+      </c>
+      <c r="C955" s="3" t="s">
         <v>2708</v>
-      </c>
-      <c r="C954" s="3" t="s">
-        <v>2709</v>
       </c>
     </row>
   </sheetData>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FA97EA-A56C-4AC2-B5F4-D9CF7CEC6493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB06740-AF92-4831-B1CF-DF650C2FC295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="2713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="2716">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23388,6 +23388,16 @@
   </si>
   <si>
     <t>Always assign the next incremental index when creating triggers and teams</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.SecondScreenSupport</t>
+  </si>
+  <si>
+    <t>Support displaying IsoView on non-primary screens (slower)</t>
+  </si>
+  <si>
+    <t>支持副屏显示绘图界面（轻微影响性能）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23782,7 +23792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C955"/>
+  <dimension ref="A1:C956"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34278,6 +34288,17 @@
         <v>2708</v>
       </c>
     </row>
+    <row r="956" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A956" s="3" t="s">
+        <v>2713</v>
+      </c>
+      <c r="B956" s="4" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C956" s="3" t="s">
+        <v>2714</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB06740-AF92-4831-B1CF-DF650C2FC295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F193F983-4F94-44FC-B6BB-8CB645883D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="2716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="2728">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23399,6 +23399,46 @@
   <si>
     <t>支持副屏显示绘图界面（轻微影响性能）</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.CircleTool</t>
+  </si>
+  <si>
+    <t>MeasurementToolbox.PlaceCircleCenter</t>
+  </si>
+  <si>
+    <t>MeasurementToolbox.ClearCircles</t>
+  </si>
+  <si>
+    <t>圆形工具</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.Radius</t>
+  </si>
+  <si>
+    <t>半径:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置圆心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除圆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Radius:</t>
+  </si>
+  <si>
+    <t>Place Circle Center</t>
+  </si>
+  <si>
+    <t>Clear Circles</t>
+  </si>
+  <si>
+    <t>Circle Tool</t>
   </si>
 </sst>
 </file>
@@ -23792,7 +23832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C956"/>
+  <dimension ref="A1:C960"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34299,6 +34339,50 @@
         <v>2714</v>
       </c>
     </row>
+    <row r="957" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A957" s="3" t="s">
+        <v>2716</v>
+      </c>
+      <c r="B957" s="4" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C957" s="3" t="s">
+        <v>2727</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A958" s="3" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B958" s="4" t="s">
+        <v>2722</v>
+      </c>
+      <c r="C958" s="3" t="s">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="959" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A959" s="3" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B959" s="4" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C959" s="3" t="s">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="960" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A960" s="3" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B960" s="4" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C960" s="3" t="s">
+        <v>2724</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F193F983-4F94-44FC-B6BB-8CB645883D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B20F63-9F70-41A7-A477-333899E291FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="2728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2877" uniqueCount="2731">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23439,6 +23439,16 @@
   </si>
   <si>
     <t>Circle Tool</t>
+  </si>
+  <si>
+    <t>MeasurementToolbox.LineSegment</t>
+  </si>
+  <si>
+    <t>线段(无文本)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line Segment (no text)</t>
   </si>
 </sst>
 </file>
@@ -23832,7 +23842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C960"/>
+  <dimension ref="A1:C961"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34383,6 +34393,17 @@
         <v>2724</v>
       </c>
     </row>
+    <row r="961" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A961" s="3" t="s">
+        <v>2728</v>
+      </c>
+      <c r="B961" s="4" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C961" s="3" t="s">
+        <v>2730</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B20F63-9F70-41A7-A477-333899E291FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41765373-225A-464A-A5FF-9C8574C16A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2877" uniqueCount="2731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="2734">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23449,6 +23449,17 @@
   </si>
   <si>
     <t>Line Segment (no text)</t>
+  </si>
+  <si>
+    <t>Classify smudges/terrains/overlays in the object viewer based on their ObjectBrowser group</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.GridObjectViewer.LoadObjectBrowserCategory</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据污染/地形对象/覆盖物在物品浏览器中的分组在对象查看器中分类</t>
   </si>
 </sst>
 </file>
@@ -23842,7 +23853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C961"/>
+  <dimension ref="A1:C962"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34404,6 +34415,17 @@
         <v>2730</v>
       </c>
     </row>
+    <row r="962" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A962" s="3" t="s">
+        <v>2732</v>
+      </c>
+      <c r="B962" s="4" t="s">
+        <v>2733</v>
+      </c>
+      <c r="C962" s="3" t="s">
+        <v>2731</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41765373-225A-464A-A5FF-9C8574C16A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6CDC4E-866B-4070-9390-002121C0E425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="2734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="2737">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23460,6 +23460,17 @@
   </si>
   <si>
     <t>根据污染/地形对象/覆盖物在物品浏览器中的分组在对象查看器中分类</t>
+  </si>
+  <si>
+    <t>ScriptTypesRenderPath</t>
+  </si>
+  <si>
+    <t>渲染路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Render path</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -23853,7 +23864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C962"/>
+  <dimension ref="A1:C963"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34426,6 +34437,17 @@
         <v>2731</v>
       </c>
     </row>
+    <row r="963" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A963" s="3" t="s">
+        <v>2734</v>
+      </c>
+      <c r="B963" s="4" t="s">
+        <v>2735</v>
+      </c>
+      <c r="C963" s="3" t="s">
+        <v>2736</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6CDC4E-866B-4070-9390-002121C0E425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D141E8-64BD-4988-A75E-0DF043002BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5940" yWindow="2730" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="2737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="2740">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23471,6 +23471,16 @@
   <si>
     <t>Render path</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>忽视地表类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ignore Landtypes</t>
+  </si>
+  <si>
+    <t>CTerrainGenerator.IgnoreLandtypes</t>
   </si>
 </sst>
 </file>
@@ -23864,7 +23874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C963"/>
+  <dimension ref="A1:C964"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34448,6 +34458,17 @@
         <v>2736</v>
       </c>
     </row>
+    <row r="964" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A964" s="3" t="s">
+        <v>2739</v>
+      </c>
+      <c r="B964" s="4" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C964" s="3" t="s">
+        <v>2738</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D141E8-64BD-4988-A75E-0DF043002BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460C50B5-8CFB-4057-BA05-AF7DA47A98E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5940" yWindow="2730" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="2740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2895" uniqueCount="2749">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23481,6 +23481,42 @@
   </si>
   <si>
     <t>CTerrainGenerator.IgnoreLandtypes</t>
+  </si>
+  <si>
+    <t>There are already houses in your map. You need to delete these first</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No houses do exist, if you want to use houses, you should use Prepare houses before doing anything else.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sorry this name is not available. %s is already used in the map file. You need to use another name.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HouseDialog.NoHousesExist</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HouseDialog.AlreadyHouses</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HouseDialog.NotAvailable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图还没有任何所属方。你需要使用标准所属方，或新建所属方。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图已经存在所属方，要使用此功能，需要先删除它们。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属方名称 %s 已经被使用，你需要换一个名字。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -23874,7 +23910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C964"/>
+  <dimension ref="A1:C967"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34469,6 +34505,39 @@
         <v>2738</v>
       </c>
     </row>
+    <row r="965" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A965" s="3" t="s">
+        <v>2743</v>
+      </c>
+      <c r="B965" s="4" t="s">
+        <v>2746</v>
+      </c>
+      <c r="C965" s="3" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="966" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A966" s="3" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B966" s="4" t="s">
+        <v>2747</v>
+      </c>
+      <c r="C966" s="3" t="s">
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A967" s="3" t="s">
+        <v>2745</v>
+      </c>
+      <c r="B967" s="4" t="s">
+        <v>2748</v>
+      </c>
+      <c r="C967" s="3" t="s">
+        <v>2742</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sources\FA2sp\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C004E3C-4231-4149-B4C9-3EC987434E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C037BA9-599B-40FC-99EA-1AF60FBB4B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4780" yWindow="160" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2901" uniqueCount="2755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2943" uniqueCount="2796">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23530,13 +23530,150 @@
   </si>
   <si>
     <t>禁止下拉菜单的自动搜索，若禁止，需要按Enter执行搜索</t>
+  </si>
+  <si>
+    <t>标签编辑器</t>
+  </si>
+  <si>
+    <t>标签使触发能够工作。如果没有标签，触发通常是无用的，因为它不会被执行。一个触发可以关联多个标签，一个标签也可以关联多个触发。</t>
+  </si>
+  <si>
+    <t>标签:</t>
+  </si>
+  <si>
+    <t>新建</t>
+  </si>
+  <si>
+    <t>Tag.Title</t>
+  </si>
+  <si>
+    <t>Tag.Description</t>
+  </si>
+  <si>
+    <t>Tag.Tag</t>
+  </si>
+  <si>
+    <t>Tag.Add</t>
+  </si>
+  <si>
+    <t>Tag.Clone</t>
+  </si>
+  <si>
+    <t>复制</t>
+  </si>
+  <si>
+    <t>Tag.Delete</t>
+  </si>
+  <si>
+    <t>删除</t>
+  </si>
+  <si>
+    <t>Tag.Name</t>
+  </si>
+  <si>
+    <t>名称:</t>
+  </si>
+  <si>
+    <t>Tag.Repeat</t>
+  </si>
+  <si>
+    <t>重复类型:</t>
+  </si>
+  <si>
+    <t>Tag.Trigger</t>
+  </si>
+  <si>
+    <t>触发:</t>
+  </si>
+  <si>
+    <t>Tag.RepeatCases</t>
+  </si>
+  <si>
+    <t>重复类型:\n 0 - 任一关联对象满足条件，执行一次；\n 1 - 所有关联对象满足条件，执行一次；\n 2 - 任一关联对象满足条件，重复执行。</t>
+  </si>
+  <si>
+    <t>Options.SortByLabelName.Tag</t>
+  </si>
+  <si>
+    <t>按名称而非ID排序标签，覆盖全局设置</t>
+  </si>
+  <si>
+    <t>Tag Editor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tags make Triggers work. Without a tag, a trigger is usually useless, because it won't be executed (except if another triggers fires it directly).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tag:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Delete</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Repeat:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trigger:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Repeat Cases:\nOne time OR: Fire once when any of the attached map elements to this Tag satisfies the given event.\nOne time AND: Fire once when all of the attached map elements to this Tag satisfies the given event.\nRepeating OR: Fire repeatedly when any of the attached map elements to this Tag satisfies the given event.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sort Tags by label name, override global setting</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在创建标签前，需要至少有一个触发。</t>
+  </si>
+  <si>
+    <t>删除标签</t>
+  </si>
+  <si>
+    <t>是否要删除此标签？这可能导致关联的触发无法执行。</t>
+  </si>
+  <si>
+    <t>Tag.DelWarn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tag.DelTitle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tag.NewTagFailed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Before creating tags, you need at least one trigger.</t>
+  </si>
+  <si>
+    <t>Delete tag</t>
+  </si>
+  <si>
+    <t>Are you sure to delete the selected tag? This may cause the attached trigger to don't work anymore, if no other tag has the trigger attached.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -23595,6 +23732,14 @@
       <family val="1"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -23628,7 +23773,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -23642,6 +23787,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="标题 1" xfId="1" builtinId="16"/>
@@ -23923,7 +24069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C969"/>
+  <dimension ref="A1:D983"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34474,7 +34620,7 @@
         <v>2722</v>
       </c>
     </row>
-    <row r="961" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="961" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A961" s="3" t="s">
         <v>2726</v>
       </c>
@@ -34485,7 +34631,7 @@
         <v>2728</v>
       </c>
     </row>
-    <row r="962" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+    <row r="962" spans="1:4" ht="38" x14ac:dyDescent="0.4">
       <c r="A962" s="3" t="s">
         <v>2730</v>
       </c>
@@ -34496,7 +34642,7 @@
         <v>2729</v>
       </c>
     </row>
-    <row r="963" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="963" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A963" s="3" t="s">
         <v>2732</v>
       </c>
@@ -34507,7 +34653,7 @@
         <v>2734</v>
       </c>
     </row>
-    <row r="964" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="964" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A964" s="3" t="s">
         <v>2737</v>
       </c>
@@ -34518,7 +34664,7 @@
         <v>2736</v>
       </c>
     </row>
-    <row r="965" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+    <row r="965" spans="1:4" ht="38" x14ac:dyDescent="0.4">
       <c r="A965" s="3" t="s">
         <v>2741</v>
       </c>
@@ -34529,7 +34675,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="966" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+    <row r="966" spans="1:4" ht="38" x14ac:dyDescent="0.4">
       <c r="A966" s="3" t="s">
         <v>2742</v>
       </c>
@@ -34540,7 +34686,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="967" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+    <row r="967" spans="1:4" ht="38" x14ac:dyDescent="0.4">
       <c r="A967" s="3" t="s">
         <v>2743</v>
       </c>
@@ -34551,7 +34697,7 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="968" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+    <row r="968" spans="1:4" ht="38" x14ac:dyDescent="0.4">
       <c r="A968" s="3" t="s">
         <v>2749</v>
       </c>
@@ -34562,7 +34708,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="969" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+    <row r="969" spans="1:4" ht="38" x14ac:dyDescent="0.4">
       <c r="A969" s="3" t="s">
         <v>2750</v>
       </c>
@@ -34571,6 +34717,171 @@
       </c>
       <c r="C969" s="3" t="s">
         <v>2751</v>
+      </c>
+    </row>
+    <row r="970" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A970" s="3" t="s">
+        <v>2759</v>
+      </c>
+      <c r="B970" s="4" t="s">
+        <v>2755</v>
+      </c>
+      <c r="C970" s="3" t="s">
+        <v>2777</v>
+      </c>
+      <c r="D970" s="5"/>
+    </row>
+    <row r="971" spans="1:4" ht="57" x14ac:dyDescent="0.4">
+      <c r="A971" s="3" t="s">
+        <v>2760</v>
+      </c>
+      <c r="B971" s="4" t="s">
+        <v>2756</v>
+      </c>
+      <c r="C971" s="3" t="s">
+        <v>2778</v>
+      </c>
+      <c r="D971" s="5"/>
+    </row>
+    <row r="972" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A972" s="3" t="s">
+        <v>2761</v>
+      </c>
+      <c r="B972" s="4" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C972" s="3" t="s">
+        <v>2779</v>
+      </c>
+      <c r="D972" s="5"/>
+    </row>
+    <row r="973" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A973" s="3" t="s">
+        <v>2762</v>
+      </c>
+      <c r="B973" s="4" t="s">
+        <v>2758</v>
+      </c>
+      <c r="C973" s="3" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D973" s="5"/>
+    </row>
+    <row r="974" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A974" s="3" t="s">
+        <v>2763</v>
+      </c>
+      <c r="B974" s="4" t="s">
+        <v>2764</v>
+      </c>
+      <c r="C974" s="3" t="s">
+        <v>2780</v>
+      </c>
+      <c r="D974" s="5"/>
+    </row>
+    <row r="975" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A975" s="3" t="s">
+        <v>2765</v>
+      </c>
+      <c r="B975" s="4" t="s">
+        <v>2766</v>
+      </c>
+      <c r="C975" s="3" t="s">
+        <v>2781</v>
+      </c>
+      <c r="D975" s="5"/>
+    </row>
+    <row r="976" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A976" s="3" t="s">
+        <v>2767</v>
+      </c>
+      <c r="B976" s="4" t="s">
+        <v>2768</v>
+      </c>
+      <c r="C976" s="3" t="s">
+        <v>2782</v>
+      </c>
+      <c r="D976" s="5"/>
+    </row>
+    <row r="977" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A977" s="3" t="s">
+        <v>2769</v>
+      </c>
+      <c r="B977" s="4" t="s">
+        <v>2770</v>
+      </c>
+      <c r="C977" s="3" t="s">
+        <v>2783</v>
+      </c>
+      <c r="D977" s="5"/>
+    </row>
+    <row r="978" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A978" s="3" t="s">
+        <v>2771</v>
+      </c>
+      <c r="B978" s="4" t="s">
+        <v>2772</v>
+      </c>
+      <c r="C978" s="3" t="s">
+        <v>2784</v>
+      </c>
+      <c r="D978" s="5"/>
+    </row>
+    <row r="979" spans="1:4" ht="95" x14ac:dyDescent="0.4">
+      <c r="A979" s="3" t="s">
+        <v>2773</v>
+      </c>
+      <c r="B979" s="4" t="s">
+        <v>2774</v>
+      </c>
+      <c r="C979" s="3" t="s">
+        <v>2785</v>
+      </c>
+      <c r="D979" s="5"/>
+    </row>
+    <row r="980" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A980" s="3" t="s">
+        <v>2775</v>
+      </c>
+      <c r="B980" s="4" t="s">
+        <v>2776</v>
+      </c>
+      <c r="C980" s="3" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D980" s="5"/>
+    </row>
+    <row r="981" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A981" s="3" t="s">
+        <v>2792</v>
+      </c>
+      <c r="B981" s="4" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C981" s="3" t="s">
+        <v>2793</v>
+      </c>
+    </row>
+    <row r="982" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A982" s="3" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B982" s="4" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C982" s="3" t="s">
+        <v>2794</v>
+      </c>
+    </row>
+    <row r="983" spans="1:4" ht="57" x14ac:dyDescent="0.4">
+      <c r="A983" s="3" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B983" s="4" t="s">
+        <v>2789</v>
+      </c>
+      <c r="C983" s="3" t="s">
+        <v>2795</v>
       </c>
     </row>
   </sheetData>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sources\FA2sp\Supplementary\文档\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C037BA9-599B-40FC-99EA-1AF60FBB4B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA3DEF5-3904-4E46-BB25-5824237A3D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4780" yWindow="160" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20277,6 +20277,3345 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
+      <t>不将所属方翻译为其</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>UIName</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>翻译所属方的同时显示英文原名</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地图检查器的新检查仅弹出提示而非错误</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地图检查器的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>INI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>长度限制为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>512</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>而非</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>128 (Ares)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>加载素材启用严格</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>NewTheater</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>逻辑</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>禁止摆放重叠建筑</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自动填写</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Upgrade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数量</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>建筑存在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Upgrade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>时设为满血</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>使用默认光照时调整单位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>RGB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>值</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在小地图显示可视地图边界</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>编辑步兵时考虑鼠标位置</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元格只有单步兵时仍判断鼠标位置</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>拖拽步兵时考虑鼠标位置</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>放置步兵时考虑鼠标位置</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>固定中间步兵位置同</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>InfantrySubCell.GameDefault</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>放置步兵时考虑地形对象占用</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>强制</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>CString</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>内存在堆上分配</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>启用严格错误捕获</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>会捕获</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C++ EH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>错误</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>使用新的工具栏图标</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不显示今日提示窗口</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选择地形工具时不改变笔刷大小</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>放置地形时跳过隐藏单元格</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>INI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>编辑器中忽略小队</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>特遣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>脚本小节</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ctrl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>填充地形时同时填充</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>LAT</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ctrl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>填充地形时将水面视为一类</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>加载并显示阴影</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>加载并显示可部署单位的更换图像</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>加载并显示水中单位的更换图像</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>将悬浮单位渲染的更高</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>显示建筑物和地形对象的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AlphaImage</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>将桥梁上单位渲染的更高</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>开启平面显示时隐藏地形</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ExtraImage</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>显示地图边界外的游戏对象</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>检测地图文件的外部修改</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>粘贴地形时默认显示描边</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>按名称而非</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>排序触发，覆盖全局设置</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>按名称而非</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>排序小队，覆盖全局设置</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>按名称而非</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>排序特遣部队，覆盖全局设置</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>按名称而非</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>排序脚本，覆盖全局设置</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>按名称而非</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>排序</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>触发，覆盖全局设置</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>设置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>NewTheater</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Y = Ares, N = YR)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>设置包含类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Y = Phobos, N = Ares)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>设置继承类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Y = Phobos, N = Ares)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>按照当前光照渲染地形浏览器图像</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>距离</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: %s</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XY: %d, %d, ΔXY: %d, %d</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XY: %d, %d</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>按</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>键以切换悬崖类型</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>水上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>启用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>向面向</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>启用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>向拖拽</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>保存时维持已有的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小节顺序</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏好设置</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录游戏对象修改历史</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>启用新的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mix</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>加载方式</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单击以绘制隧道，双击以设置终点并完成编辑。隧道长度不能超过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>拖拽面向时实时预览</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>彩蛋</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>游戏结束</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>按</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> R </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>键重新开始</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你发现了彩蛋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> :-)     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>按</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> R </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>键重新开始，按</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Z </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>键悔棋</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>胜利</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>游戏结束</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你胜利了！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>将军！你胜利了！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>被困毙，你胜利了！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>禁止长将，你胜利了！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>将军！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>胜利了！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你被困毙，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>胜利了！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你吃掉了红将！你胜利了！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请输入覆盖物的索引</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(0-254)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，不要超过这个范围。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>手动设置覆盖物</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请输入覆盖物数据的索引</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(0-59)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，不要超过这个范围。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>手动设置覆盖物数据</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>启用暗色模式</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>启用暗色模式时，将地图视图整体变暗</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>禁止长将，你输了！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>棋盘已满，和棋！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>缩小地形浏览器的地形图像</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>调节建筑动画图层，可能与游戏内不一致</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>死亡武器范围</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CSF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>标签</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最小玩家数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最大玩家数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>MMX\YRO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选项</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>根据系统设置或手动指定，自动切换暗色模式</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>缩放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: %.02fx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，按鼠标中键恢复</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>触发注释</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前对象</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: %s</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>本文件编码为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> UTF8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，请使用此格式打开</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>打开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>和地图文件时自动推断编码</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>总是以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>UTF8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>编码保存地图</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地图注释</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>\tAlt+9</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>受损火焰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>\tAlt+Num0</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>内存分配失败，无法渲染全图</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地图渲染选项</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>渲染区域</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>渲染图层</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可见区域</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全地图</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>游戏内效果</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前图层</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>触发注释</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>\tCtrl+Shift+A</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地图渲染已输出至：</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地图渲染器：渲染区块</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (%d/%d)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地图渲染器：存储</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>PNG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图像至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> %s</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>渲染光照</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前光照</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>标记矿物</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>忽略指定单位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>见</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>FAData.ini)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>渲染中，请稍后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>...</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>批处理</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请输入地图路径，每行一个。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>批处理渲染</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>隐形单位半透明显示</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>绘制矿石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>绘制矿石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>摆放矿石时随机图像</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>支持额外矿石类型的摆放</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>剪切</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>\tCtrl+X</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>向相连</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>显示游戏内不可见对象</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正矩形添加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正矩形删除</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>最大降低高度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>最大抬升高度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>起伏强度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(0-200):</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>斜坡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>宏观起伏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(0-200):</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>指定基础高度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高度渐变</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>起始终结坐标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(x,y):</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>对应高度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>宏观最大降低高度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>宏观最大抬升高度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>避让选区边界</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>半透明绘制单元标记</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置路径点颜色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移除路径点颜色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置单元标记颜色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移除单元标记颜色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在地面上而不是体素的最底部渲染阴影</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>本工具生成随机斜坡地形。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地形高度由两层起伏叠加而成：左侧参数控制局部细节起伏，影响地面陡峭程度；右侧宏观参数控制大尺度整体起伏，影响区域间的高低变化。最终效果为两者叠加。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>保存地图时保留注释</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>禁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>简</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>困</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>复</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>删</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>查找</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>从左侧触发列表多选后，点击“添加”加入右侧栏目中。仅有一个事件和行为会被显示，修改事件索引与行为索引以显示你需要修改的部分。双击任意单元格对目标参数进行修改。不论是否修改，被双击过的单元格都会呈现红色高亮状态。当在同一纵列中连续两个参数处于高亮，且这两个参数存在可识别的递增规律（例如 TEST01 → TEST02）时，点击“自动填充”，系统将自动按该规律推断并填充后续参数。点击“清除高亮”重置所有单元格的状态。默认显示触发、标签、小队参数的的名称，以数字方式显示路径点，勾选“使用ID”则显示其注册ID，以字母方式显示路径点。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>为没有图像的车辆、步兵与飞行器显示缺省图像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将%s文件的默认程序设为FA2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用椭圆绘制除了受高度影响的武器外的所有范围</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>锁定布局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐藏工具栏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重置工具栏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0 - 无聚光灯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 - 使用Rules设置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2 - 圆/目标聚光灯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>双击打开地图文件时，从地图目录加载资源文件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对象分组:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>搜索:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>根据对象的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>EditorCategory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在对象查看器中分类</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>距离标尺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>轴对称工具</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中心对称工具</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>两点距离</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>跟随测距</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除测距点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置对称轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置对称点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除对称点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置对称中心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.CentralSymmetryCenter</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center</t>
+  </si>
+  <si>
+    <t>地表类型: %#x, 高度 %d /</t>
+  </si>
+  <si>
+    <t>覆盖物: %#x, 覆盖物数据: %#x /</t>
+  </si>
+  <si>
+    <t>建筑: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>车辆: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>飞行器: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>步兵: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>单元标记: %s (%s) /</t>
+  </si>
+  <si>
+    <t>StatusBarText7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusBarText6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusBarText5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusBarText4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusBarText3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusBarText2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusBarText1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Terrain type: %#x, height %d /</t>
+  </si>
+  <si>
+    <t>Overlay: %#x, OverlayData %#x /</t>
+  </si>
+  <si>
+    <t>Structure: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>Vehicle: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>Aircraft: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>Infantry: ID %d, %s (%s, %s) /</t>
+  </si>
+  <si>
+    <t>CellTag: %s (%s) /</t>
+  </si>
+  <si>
+    <t>GridObjectViewer.OverlayText</t>
+  </si>
+  <si>
+    <t>索引: %d, 覆盖物数据: %d</t>
+  </si>
+  <si>
+    <t>Index: %d, OverlayData: %d</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NewVersionAvailable</t>
+  </si>
+  <si>
+    <t>发现新版本:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New version available:</t>
+  </si>
+  <si>
+    <t>Assign independent suffixes to different types (triggers, teams...)</t>
+  </si>
+  <si>
+    <t>Options.UseSeparateIndexing</t>
+  </si>
+  <si>
+    <t>为触发、小队等分配带有独立后缀的ID</t>
+  </si>
+  <si>
+    <t>在创建触发、小队时始终使用下一个递增索引号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Always assign the next incremental index when creating triggers and teams</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.SecondScreenSupport</t>
+  </si>
+  <si>
+    <t>Support displaying IsoView on non-primary screens (slower)</t>
+  </si>
+  <si>
+    <t>支持副屏显示绘图界面（轻微影响性能）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.CircleTool</t>
+  </si>
+  <si>
+    <t>MeasurementToolbox.PlaceCircleCenter</t>
+  </si>
+  <si>
+    <t>MeasurementToolbox.ClearCircles</t>
+  </si>
+  <si>
+    <t>圆形工具</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.Radius</t>
+  </si>
+  <si>
+    <t>半径:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置圆心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除圆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Radius:</t>
+  </si>
+  <si>
+    <t>Place Circle Center</t>
+  </si>
+  <si>
+    <t>Clear Circles</t>
+  </si>
+  <si>
+    <t>Circle Tool</t>
+  </si>
+  <si>
+    <t>MeasurementToolbox.LineSegment</t>
+  </si>
+  <si>
+    <t>线段(无文本)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line Segment (no text)</t>
+  </si>
+  <si>
+    <t>Classify smudges/terrains/overlays in the object viewer based on their ObjectBrowser group</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.GridObjectViewer.LoadObjectBrowserCategory</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据污染/地形对象/覆盖物在物品浏览器中的分组在对象查看器中分类</t>
+  </si>
+  <si>
+    <t>ScriptTypesRenderPath</t>
+  </si>
+  <si>
+    <t>渲染路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Render path</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>忽视地表类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ignore Landtypes</t>
+  </si>
+  <si>
+    <t>CTerrainGenerator.IgnoreLandtypes</t>
+  </si>
+  <si>
+    <t>There are already houses in your map. You need to delete these first</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No houses do exist, if you want to use houses, you should use Prepare houses before doing anything else.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sorry this name is not available. %s is already used in the map file. You need to use another name.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HouseDialog.NoHousesExist</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HouseDialog.AlreadyHouses</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HouseDialog.NotAvailable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图还没有任何所属方。你需要使用标准所属方，或新建所属方。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图已经存在所属方，要使用此功能，需要先删除它们。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属方名称 %s 已经被使用，你需要换一个名字。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Automatically perform search when editing waypoint params</t>
+  </si>
+  <si>
+    <t>编辑路径点参数时自动执行搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.SearchCombobox.AllowNonParams</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.SearchCombobox.Disabled</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disable automatic search for dropdown menus; search only when pressing Enter</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allow automatic search for non-parameter dropdown menus</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>允许非参数项下拉菜单的自动搜索</t>
+  </si>
+  <si>
+    <t>禁止下拉菜单的自动搜索，若禁止，需要按Enter执行搜索</t>
+  </si>
+  <si>
+    <t>标签编辑器</t>
+  </si>
+  <si>
+    <t>标签使触发能够工作。如果没有标签，触发通常是无用的，因为它不会被执行。一个触发可以关联多个标签，一个标签也可以关联多个触发。</t>
+  </si>
+  <si>
+    <t>标签:</t>
+  </si>
+  <si>
+    <t>新建</t>
+  </si>
+  <si>
+    <t>Tag.Title</t>
+  </si>
+  <si>
+    <t>Tag.Description</t>
+  </si>
+  <si>
+    <t>Tag.Tag</t>
+  </si>
+  <si>
+    <t>Tag.Add</t>
+  </si>
+  <si>
+    <t>Tag.Clone</t>
+  </si>
+  <si>
+    <t>复制</t>
+  </si>
+  <si>
+    <t>Tag.Delete</t>
+  </si>
+  <si>
+    <t>删除</t>
+  </si>
+  <si>
+    <t>Tag.Name</t>
+  </si>
+  <si>
+    <t>名称:</t>
+  </si>
+  <si>
+    <t>Tag.Repeat</t>
+  </si>
+  <si>
+    <t>重复类型:</t>
+  </si>
+  <si>
+    <t>Tag.Trigger</t>
+  </si>
+  <si>
+    <t>触发:</t>
+  </si>
+  <si>
+    <t>Tag.RepeatCases</t>
+  </si>
+  <si>
+    <t>重复类型:\n 0 - 任一关联对象满足条件，执行一次；\n 1 - 所有关联对象满足条件，执行一次；\n 2 - 任一关联对象满足条件，重复执行。</t>
+  </si>
+  <si>
+    <t>Options.SortByLabelName.Tag</t>
+  </si>
+  <si>
+    <t>按名称而非ID排序标签，覆盖全局设置</t>
+  </si>
+  <si>
+    <t>Tag Editor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tags make Triggers work. Without a tag, a trigger is usually useless, because it won't be executed (except if another triggers fires it directly).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tag:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Delete</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Repeat:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trigger:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Repeat Cases:\nOne time OR: Fire once when any of the attached map elements to this Tag satisfies the given event.\nOne time AND: Fire once when all of the attached map elements to this Tag satisfies the given event.\nRepeating OR: Fire repeatedly when any of the attached map elements to this Tag satisfies the given event.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sort Tags by label name, override global setting</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在创建标签前，需要至少有一个触发。</t>
+  </si>
+  <si>
+    <t>删除标签</t>
+  </si>
+  <si>
+    <t>是否要删除此标签？这可能导致关联的触发无法执行。</t>
+  </si>
+  <si>
+    <t>Tag.DelWarn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tag.DelTitle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tag.NewTagFailed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Before creating tags, you need at least one trigger.</t>
+  </si>
+  <si>
+    <t>Delete tag</t>
+  </si>
+  <si>
+    <t>Are you sure to delete the selected tag? This may cause the attached trigger to don't work anymore, if no other tag has the trigger attached.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>使用双线性插值缩放绘图界面</t>
     </r>
     <r>
@@ -20310,3362 +23649,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不将所属方翻译为其</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>UIName</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>翻译所属方的同时显示英文原名</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>地图检查器的新检查仅弹出提示而非错误</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>地图检查器的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>INI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>长度限制为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>512</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>而非</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>128 (Ares)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>加载素材启用严格</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>NewTheater</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>逻辑</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>禁止摆放重叠建筑</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>自动填写</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Upgrade</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>数量</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>建筑存在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Upgrade</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>时设为满血</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>使用默认光照时调整单位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>RGB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>值</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>在小地图显示可视地图边界</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>编辑步兵时考虑鼠标位置</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元格只有单步兵时仍判断鼠标位置</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>拖拽步兵时考虑鼠标位置</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>放置步兵时考虑鼠标位置</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>固定中间步兵位置同</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>InfantrySubCell.GameDefault</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>放置步兵时考虑地形对象占用</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>强制</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>CString</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>内存在堆上分配</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>启用严格错误捕获</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>会捕获</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>C++ EH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>错误</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>使用新的工具栏图标</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不显示今日提示窗口</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>选择地形工具时不改变笔刷大小</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>放置地形时跳过隐藏单元格</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>INI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>编辑器中忽略小队</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>特遣</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>脚本小节</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>ctrl</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>填充地形时同时填充</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>LAT</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>ctrl</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>填充地形时将水面视为一类</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>加载并显示阴影</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>加载并显示可部署单位的更换图像</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>加载并显示水中单位的更换图像</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>将悬浮单位渲染的更高</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>显示建筑物和地形对象的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>AlphaImage</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>将桥梁上单位渲染的更高</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>开启平面显示时隐藏地形</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ExtraImage</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>显示地图边界外的游戏对象</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>检测地图文件的外部修改</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>粘贴地形时默认显示描边</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按名称而非</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>排序触发，覆盖全局设置</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按名称而非</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>排序小队，覆盖全局设置</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按名称而非</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>排序特遣部队，覆盖全局设置</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按名称而非</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>排序脚本，覆盖全局设置</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按名称而非</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>排序</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>触发，覆盖全局设置</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>设置</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>NewTheater</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>类型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (Y = Ares, N = YR)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>设置包含类型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (Y = Phobos, N = Ares)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>设置继承类型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (Y = Phobos, N = Ares)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按照当前光照渲染地形浏览器图像</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>距离</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>: %s</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>XY: %d, %d, ΔXY: %d, %d</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>XY: %d, %d</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>键以切换悬崖类型</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>启用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>32</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>向面向</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>启用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>32</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>向拖拽</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>保存时维持已有的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ini</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小节顺序</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>偏好设置</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>记录游戏对象修改历史</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>启用新的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Mix</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>加载方式</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>仅在缩小时使用双线性插值</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单击以绘制隧道，双击以设置终点并完成编辑。隧道长度不能超过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>拖拽面向时实时预览</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>彩蛋</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>游戏结束</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> R </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>键重新开始</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你发现了彩蛋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> :-)     </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> R </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>键重新开始，按</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Z </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>键悔棋</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>胜利</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>游戏结束</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你胜利了！</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>将军！你胜利了！</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>被困毙，你胜利了！</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>禁止长将，你胜利了！</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>将军！</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>胜利了！</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你被困毙，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>胜利了！</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你吃掉了红将！你胜利了！</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>请输入覆盖物的索引</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(0-254)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，不要超过这个范围。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>手动设置覆盖物</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>请输入覆盖物数据的索引</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(0-59)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，不要超过这个范围。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>手动设置覆盖物数据</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>启用暗色模式</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>启用暗色模式时，将地图视图整体变暗</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>禁止长将，你输了！</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>棋盘已满，和棋！</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>缩小地形浏览器的地形图像</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>调节建筑动画图层，可能与游戏内不一致</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>死亡武器范围</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>CSF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>标签</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最小玩家数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最大玩家数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>MMX\YRO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>选项</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>根据系统设置或手动指定，自动切换暗色模式</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>缩放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>: %.02fx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，按鼠标中键恢复</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>触发注释</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>当前对象</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>: %s</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>本文件编码为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> UTF8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，请使用此格式打开</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>打开</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ini</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>和地图文件时自动推断编码</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>总是以</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>UTF8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>编码保存地图</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>地图注释</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>\tAlt+9</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>受损火焰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>\tAlt+Num0</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>内存分配失败，无法渲染全图</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>地图渲染选项</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>渲染区域</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>渲染图层</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>可见区域</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全地图</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>游戏内效果</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>当前图层</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>触发注释</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>\tCtrl+Shift+A</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>地图渲染已输出至：</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>地图渲染器：渲染区块</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (%d/%d)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>地图渲染器：存储</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>PNG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>图像至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> %s</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>渲染光照</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>当前光照</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>标记矿物</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>忽略指定单位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>见</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>FAData.ini)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>渲染中，请稍后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>...</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>批处理</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>请输入地图路径，每行一个。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>批处理渲染</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>隐形单位半透明显示</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>绘制矿石</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>绘制矿石</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>摆放矿石时随机图像</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>支持额外矿石类型的摆放</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>剪切</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>\tCtrl+X</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>向相连</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>显示游戏内不可见对象</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>正矩形添加</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>正矩形删除</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>最大降低高度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>最大抬升高度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>起伏强度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(0-200):</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>斜坡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>宏观起伏</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(0-200):</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>指定基础高度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>高度渐变</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>起始终结坐标</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(x,y):</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>对应高度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>宏观最大降低高度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>宏观最大抬升高度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>避让选区边界</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>半透明绘制单元标记</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置路径点颜色</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>移除路径点颜色</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置单元标记颜色</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>移除单元标记颜色</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>在地面上而不是体素的最底部渲染阴影</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>本工具生成随机斜坡地形。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>\n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>地形高度由两层起伏叠加而成：左侧参数控制局部细节起伏，影响地面陡峭程度；右侧宏观参数控制大尺度整体起伏，影响区域间的高低变化。最终效果为两者叠加。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>保存地图时保留注释</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>放置</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>禁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>简</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>普</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>困</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>复</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>删</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>查找</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>从左侧触发列表多选后，点击“添加”加入右侧栏目中。仅有一个事件和行为会被显示，修改事件索引与行为索引以显示你需要修改的部分。双击任意单元格对目标参数进行修改。不论是否修改，被双击过的单元格都会呈现红色高亮状态。当在同一纵列中连续两个参数处于高亮，且这两个参数存在可识别的递增规律（例如 TEST01 → TEST02）时，点击“自动填充”，系统将自动按该规律推断并填充后续参数。点击“清除高亮”重置所有单元格的状态。默认显示触发、标签、小队参数的的名称，以数字方式显示路径点，勾选“使用ID”则显示其注册ID，以字母方式显示路径点。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>为没有图像的车辆、步兵与飞行器显示缺省图像</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>将%s文件的默认程序设为FA2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用椭圆绘制除了受高度影响的武器外的所有范围</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>锁定布局</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>隐藏工具栏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>重置工具栏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0 - 无聚光灯</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 - 使用Rules设置</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2 - 圆/目标聚光灯</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>双击打开地图文件时，从地图目录加载资源文件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>对象分组:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>搜索:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>根据对象的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>EditorCategory</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>在对象查看器中分类</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>距离标尺</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>轴对称工具</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中心对称工具</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>两点距离</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>跟随测距</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>清除测距点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置对称轴</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>放置对称点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>清除对称点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置对称中心</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MeasurementToolbox.CentralSymmetryCenter</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中心</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Center</t>
-  </si>
-  <si>
-    <t>地表类型: %#x, 高度 %d /</t>
-  </si>
-  <si>
-    <t>覆盖物: %#x, 覆盖物数据: %#x /</t>
-  </si>
-  <si>
-    <t>建筑: ID %d, %s (%s, %s) /</t>
-  </si>
-  <si>
-    <t>车辆: ID %d, %s (%s, %s) /</t>
-  </si>
-  <si>
-    <t>飞行器: ID %d, %s (%s, %s) /</t>
-  </si>
-  <si>
-    <t>步兵: ID %d, %s (%s, %s) /</t>
-  </si>
-  <si>
-    <t>单元标记: %s (%s) /</t>
-  </si>
-  <si>
-    <t>StatusBarText7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatusBarText6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatusBarText5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatusBarText4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatusBarText3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatusBarText2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatusBarText1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Terrain type: %#x, height %d /</t>
-  </si>
-  <si>
-    <t>Overlay: %#x, OverlayData %#x /</t>
-  </si>
-  <si>
-    <t>Structure: ID %d, %s (%s, %s) /</t>
-  </si>
-  <si>
-    <t>Vehicle: ID %d, %s (%s, %s) /</t>
-  </si>
-  <si>
-    <t>Aircraft: ID %d, %s (%s, %s) /</t>
-  </si>
-  <si>
-    <t>Infantry: ID %d, %s (%s, %s) /</t>
-  </si>
-  <si>
-    <t>CellTag: %s (%s) /</t>
-  </si>
-  <si>
-    <t>GridObjectViewer.OverlayText</t>
-  </si>
-  <si>
-    <t>索引: %d, 覆盖物数据: %d</t>
-  </si>
-  <si>
-    <t>Index: %d, OverlayData: %d</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NewVersionAvailable</t>
-  </si>
-  <si>
-    <t>发现新版本:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>New version available:</t>
-  </si>
-  <si>
-    <t>Assign independent suffixes to different types (triggers, teams...)</t>
-  </si>
-  <si>
-    <t>Options.UseSeparateIndexing</t>
-  </si>
-  <si>
-    <t>为触发、小队等分配带有独立后缀的ID</t>
-  </si>
-  <si>
-    <t>在创建触发、小队时始终使用下一个递增索引号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Always assign the next incremental index when creating triggers and teams</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Options.SecondScreenSupport</t>
-  </si>
-  <si>
-    <t>Support displaying IsoView on non-primary screens (slower)</t>
-  </si>
-  <si>
-    <t>支持副屏显示绘图界面（轻微影响性能）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MeasurementToolbox.CircleTool</t>
-  </si>
-  <si>
-    <t>MeasurementToolbox.PlaceCircleCenter</t>
-  </si>
-  <si>
-    <t>MeasurementToolbox.ClearCircles</t>
-  </si>
-  <si>
-    <t>圆形工具</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MeasurementToolbox.Radius</t>
-  </si>
-  <si>
-    <t>半径:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>放置圆心</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>清除圆</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Radius:</t>
-  </si>
-  <si>
-    <t>Place Circle Center</t>
-  </si>
-  <si>
-    <t>Clear Circles</t>
-  </si>
-  <si>
-    <t>Circle Tool</t>
-  </si>
-  <si>
-    <t>MeasurementToolbox.LineSegment</t>
-  </si>
-  <si>
-    <t>线段(无文本)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Line Segment (no text)</t>
-  </si>
-  <si>
-    <t>Classify smudges/terrains/overlays in the object viewer based on their ObjectBrowser group</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Options.GridObjectViewer.LoadObjectBrowserCategory</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>根据污染/地形对象/覆盖物在物品浏览器中的分组在对象查看器中分类</t>
-  </si>
-  <si>
-    <t>ScriptTypesRenderPath</t>
-  </si>
-  <si>
-    <t>渲染路径</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Render path</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>忽视地表类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ignore Landtypes</t>
-  </si>
-  <si>
-    <t>CTerrainGenerator.IgnoreLandtypes</t>
-  </si>
-  <si>
-    <t>There are already houses in your map. You need to delete these first</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No houses do exist, if you want to use houses, you should use Prepare houses before doing anything else.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sorry this name is not available. %s is already used in the map file. You need to use another name.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HouseDialog.NoHousesExist</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HouseDialog.AlreadyHouses</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HouseDialog.NotAvailable</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>地图还没有任何所属方。你需要使用标准所属方，或新建所属方。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>地图已经存在所属方，要使用此功能，需要先删除它们。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>所属方名称 %s 已经被使用，你需要换一个名字。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Automatically perform search when editing waypoint params</t>
-  </si>
-  <si>
-    <t>编辑路径点参数时自动执行搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Options.SearchCombobox.AllowNonParams</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Options.SearchCombobox.Disabled</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Disable automatic search for dropdown menus; search only when pressing Enter</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Allow automatic search for non-parameter dropdown menus</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>允许非参数项下拉菜单的自动搜索</t>
-  </si>
-  <si>
-    <t>禁止下拉菜单的自动搜索，若禁止，需要按Enter执行搜索</t>
-  </si>
-  <si>
-    <t>标签编辑器</t>
-  </si>
-  <si>
-    <t>标签使触发能够工作。如果没有标签，触发通常是无用的，因为它不会被执行。一个触发可以关联多个标签，一个标签也可以关联多个触发。</t>
-  </si>
-  <si>
-    <t>标签:</t>
-  </si>
-  <si>
-    <t>新建</t>
-  </si>
-  <si>
-    <t>Tag.Title</t>
-  </si>
-  <si>
-    <t>Tag.Description</t>
-  </si>
-  <si>
-    <t>Tag.Tag</t>
-  </si>
-  <si>
-    <t>Tag.Add</t>
-  </si>
-  <si>
-    <t>Tag.Clone</t>
-  </si>
-  <si>
-    <t>复制</t>
-  </si>
-  <si>
-    <t>Tag.Delete</t>
-  </si>
-  <si>
-    <t>删除</t>
-  </si>
-  <si>
-    <t>Tag.Name</t>
-  </si>
-  <si>
-    <t>名称:</t>
-  </si>
-  <si>
-    <t>Tag.Repeat</t>
-  </si>
-  <si>
-    <t>重复类型:</t>
-  </si>
-  <si>
-    <t>Tag.Trigger</t>
-  </si>
-  <si>
-    <t>触发:</t>
-  </si>
-  <si>
-    <t>Tag.RepeatCases</t>
-  </si>
-  <si>
-    <t>重复类型:\n 0 - 任一关联对象满足条件，执行一次；\n 1 - 所有关联对象满足条件，执行一次；\n 2 - 任一关联对象满足条件，重复执行。</t>
-  </si>
-  <si>
-    <t>Options.SortByLabelName.Tag</t>
-  </si>
-  <si>
-    <t>按名称而非ID排序标签，覆盖全局设置</t>
-  </si>
-  <si>
-    <t>Tag Editor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tags make Triggers work. Without a tag, a trigger is usually useless, because it won't be executed (except if another triggers fires it directly).</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tag:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Clone</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Delete</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Repeat:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Trigger:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Repeat Cases:\nOne time OR: Fire once when any of the attached map elements to this Tag satisfies the given event.\nOne time AND: Fire once when all of the attached map elements to this Tag satisfies the given event.\nRepeating OR: Fire repeatedly when any of the attached map elements to this Tag satisfies the given event.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sort Tags by label name, override global setting</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>在创建标签前，需要至少有一个触发。</t>
-  </si>
-  <si>
-    <t>删除标签</t>
-  </si>
-  <si>
-    <t>是否要删除此标签？这可能导致关联的触发无法执行。</t>
-  </si>
-  <si>
-    <t>Tag.DelWarn</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tag.DelTitle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tag.NewTagFailed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Before creating tags, you need at least one trigger.</t>
-  </si>
-  <si>
-    <t>Delete tag</t>
-  </si>
-  <si>
-    <t>Are you sure to delete the selected tag? This may cause the attached trigger to don't work anymore, if no other tag has the trigger attached.</t>
+    <t>仅在缩小时使用双线性插值缩放</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -31050,10 +31034,10 @@
         <v>643</v>
       </c>
       <c r="B636" s="4" t="s">
-        <v>2748</v>
+        <v>2746</v>
       </c>
       <c r="C636" s="3" t="s">
-        <v>2747</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="637" spans="1:3" ht="38" x14ac:dyDescent="0.4">
@@ -31237,7 +31221,7 @@
         <v>660</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>2498</v>
+        <v>2794</v>
       </c>
       <c r="C653" s="3" t="s">
         <v>1107</v>
@@ -31248,7 +31232,7 @@
         <v>661</v>
       </c>
       <c r="B654" s="4" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="C654" s="3" t="s">
         <v>1076</v>
@@ -31259,7 +31243,7 @@
         <v>662</v>
       </c>
       <c r="B655" s="4" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="C655" s="3" t="s">
         <v>1077</v>
@@ -31270,7 +31254,7 @@
         <v>663</v>
       </c>
       <c r="B656" s="4" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="C656" s="3" t="s">
         <v>1088</v>
@@ -31281,7 +31265,7 @@
         <v>664</v>
       </c>
       <c r="B657" s="4" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="C657" s="3" t="s">
         <v>1089</v>
@@ -31303,7 +31287,7 @@
         <v>666</v>
       </c>
       <c r="B659" s="4" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="C659" s="3" t="s">
         <v>1090</v>
@@ -31314,7 +31298,7 @@
         <v>667</v>
       </c>
       <c r="B660" s="4" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="C660" s="3" t="s">
         <v>1093</v>
@@ -31325,7 +31309,7 @@
         <v>668</v>
       </c>
       <c r="B661" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="C661" s="3" t="s">
         <v>1094</v>
@@ -31336,7 +31320,7 @@
         <v>669</v>
       </c>
       <c r="B662" s="4" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="C662" s="3" t="s">
         <v>1095</v>
@@ -31347,7 +31331,7 @@
         <v>670</v>
       </c>
       <c r="B663" s="4" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="C663" s="3" t="s">
         <v>1052</v>
@@ -31358,7 +31342,7 @@
         <v>671</v>
       </c>
       <c r="B664" s="4" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="C664" s="3" t="s">
         <v>1048</v>
@@ -31380,7 +31364,7 @@
         <v>673</v>
       </c>
       <c r="B666" s="4" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="C666" s="3" t="s">
         <v>1099</v>
@@ -31391,7 +31375,7 @@
         <v>674</v>
       </c>
       <c r="B667" s="4" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="C667" s="3" t="s">
         <v>1100</v>
@@ -31402,7 +31386,7 @@
         <v>675</v>
       </c>
       <c r="B668" s="4" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="C668" s="3" t="s">
         <v>1101</v>
@@ -31413,7 +31397,7 @@
         <v>676</v>
       </c>
       <c r="B669" s="4" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="C669" s="3" t="s">
         <v>1102</v>
@@ -31424,7 +31408,7 @@
         <v>677</v>
       </c>
       <c r="B670" s="4" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="C670" s="3" t="s">
         <v>1103</v>
@@ -31435,7 +31419,7 @@
         <v>678</v>
       </c>
       <c r="B671" s="4" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="C671" s="3" t="s">
         <v>1104</v>
@@ -31446,7 +31430,7 @@
         <v>679</v>
       </c>
       <c r="B672" s="4" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="C672" s="3" t="s">
         <v>1109</v>
@@ -31457,7 +31441,7 @@
         <v>680</v>
       </c>
       <c r="B673" s="4" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="C673" s="3" t="s">
         <v>1110</v>
@@ -31468,7 +31452,7 @@
         <v>681</v>
       </c>
       <c r="B674" s="4" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="C674" s="3" t="s">
         <v>1031</v>
@@ -31479,7 +31463,7 @@
         <v>682</v>
       </c>
       <c r="B675" s="4" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="C675" s="3" t="s">
         <v>1065</v>
@@ -31490,7 +31474,7 @@
         <v>683</v>
       </c>
       <c r="B676" s="4" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="C676" s="3" t="s">
         <v>1066</v>
@@ -31501,7 +31485,7 @@
         <v>684</v>
       </c>
       <c r="B677" s="4" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="C677" s="3" t="s">
         <v>1068</v>
@@ -31512,7 +31496,7 @@
         <v>685</v>
       </c>
       <c r="B678" s="4" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="C678" s="3" t="s">
         <v>1069</v>
@@ -31523,7 +31507,7 @@
         <v>686</v>
       </c>
       <c r="B679" s="4" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="C679" s="3" t="s">
         <v>1070</v>
@@ -31534,7 +31518,7 @@
         <v>687</v>
       </c>
       <c r="B680" s="4" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="C680" s="3" t="s">
         <v>1071</v>
@@ -31545,7 +31529,7 @@
         <v>688</v>
       </c>
       <c r="B681" s="4" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="C681" s="3" t="s">
         <v>1037</v>
@@ -31556,7 +31540,7 @@
         <v>689</v>
       </c>
       <c r="B682" s="4" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="C682" s="3" t="s">
         <v>1038</v>
@@ -31567,7 +31551,7 @@
         <v>690</v>
       </c>
       <c r="B683" s="4" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="C683" s="3" t="s">
         <v>1039</v>
@@ -31589,7 +31573,7 @@
         <v>692</v>
       </c>
       <c r="B685" s="4" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="C685" s="3" t="s">
         <v>1042</v>
@@ -31600,7 +31584,7 @@
         <v>693</v>
       </c>
       <c r="B686" s="4" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="C686" s="3" t="s">
         <v>1041</v>
@@ -31611,7 +31595,7 @@
         <v>694</v>
       </c>
       <c r="B687" s="4" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="C687" s="3" t="s">
         <v>1043</v>
@@ -31622,7 +31606,7 @@
         <v>695</v>
       </c>
       <c r="B688" s="4" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="C688" s="3" t="s">
         <v>1046</v>
@@ -31633,7 +31617,7 @@
         <v>696</v>
       </c>
       <c r="B689" s="4" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="C689" s="3" t="s">
         <v>1047</v>
@@ -31655,7 +31639,7 @@
         <v>698</v>
       </c>
       <c r="B691" s="4" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="C691" s="3" t="s">
         <v>1063</v>
@@ -31677,7 +31661,7 @@
         <v>700</v>
       </c>
       <c r="B693" s="4" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="C693" s="3" t="s">
         <v>1067</v>
@@ -31688,7 +31672,7 @@
         <v>701</v>
       </c>
       <c r="B694" s="4" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="C694" s="3" t="s">
         <v>1022</v>
@@ -31699,7 +31683,7 @@
         <v>702</v>
       </c>
       <c r="B695" s="4" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="C695" s="3" t="s">
         <v>1023</v>
@@ -31710,7 +31694,7 @@
         <v>703</v>
       </c>
       <c r="B696" s="4" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="C696" s="3" t="s">
         <v>1024</v>
@@ -31721,7 +31705,7 @@
         <v>704</v>
       </c>
       <c r="B697" s="4" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="C697" s="3" t="s">
         <v>1025</v>
@@ -31732,7 +31716,7 @@
         <v>705</v>
       </c>
       <c r="B698" s="4" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="C698" s="3" t="s">
         <v>1021</v>
@@ -31754,7 +31738,7 @@
         <v>707</v>
       </c>
       <c r="B700" s="4" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="C700" s="3" t="s">
         <v>1122</v>
@@ -31776,7 +31760,7 @@
         <v>709</v>
       </c>
       <c r="B702" s="4" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="C702" s="3" t="s">
         <v>1120</v>
@@ -31787,7 +31771,7 @@
         <v>710</v>
       </c>
       <c r="B703" s="4" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="C703" s="3" t="s">
         <v>1121</v>
@@ -31820,7 +31804,7 @@
         <v>713</v>
       </c>
       <c r="B706" s="4" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C706" s="3" t="s">
         <v>1053</v>
@@ -31831,7 +31815,7 @@
         <v>718</v>
       </c>
       <c r="B707" s="4" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="C707" s="3" t="s">
         <v>986</v>
@@ -31842,7 +31826,7 @@
         <v>717</v>
       </c>
       <c r="B708" s="4" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C708" s="3" t="s">
         <v>714</v>
@@ -31853,7 +31837,7 @@
         <v>716</v>
       </c>
       <c r="B709" s="4" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C709" s="3" t="s">
         <v>715</v>
@@ -31864,7 +31848,7 @@
         <v>719</v>
       </c>
       <c r="B710" s="4" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C710" s="3" t="s">
         <v>930</v>
@@ -31886,7 +31870,7 @@
         <v>721</v>
       </c>
       <c r="B712" s="4" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C712" s="3" t="s">
         <v>952</v>
@@ -31897,7 +31881,7 @@
         <v>723</v>
       </c>
       <c r="B713" s="4" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="C713" s="3" t="s">
         <v>1084</v>
@@ -31908,7 +31892,7 @@
         <v>722</v>
       </c>
       <c r="B714" s="4" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C714" s="3" t="s">
         <v>1085</v>
@@ -31919,7 +31903,7 @@
         <v>724</v>
       </c>
       <c r="B715" s="4" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C715" s="3" t="s">
         <v>1062</v>
@@ -31930,7 +31914,7 @@
         <v>725</v>
       </c>
       <c r="B716" s="4" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="C716" s="3" t="s">
         <v>1551</v>
@@ -31941,7 +31925,7 @@
         <v>726</v>
       </c>
       <c r="B717" s="4" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C717" s="3" t="s">
         <v>1074</v>
@@ -31952,7 +31936,7 @@
         <v>727</v>
       </c>
       <c r="B718" s="4" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C718" s="3" t="s">
         <v>1087</v>
@@ -31963,7 +31947,7 @@
         <v>728</v>
       </c>
       <c r="B719" s="4" t="s">
-        <v>2554</v>
+        <v>2795</v>
       </c>
       <c r="C719" s="3" t="s">
         <v>1108</v>
@@ -31974,7 +31958,7 @@
         <v>729</v>
       </c>
       <c r="B720" s="4" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="C720" s="3" t="s">
         <v>931</v>
@@ -31985,7 +31969,7 @@
         <v>730</v>
       </c>
       <c r="B721" s="4" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
       <c r="C721" s="3" t="s">
         <v>1086</v>
@@ -32040,7 +32024,7 @@
         <v>735</v>
       </c>
       <c r="B726" s="4" t="s">
-        <v>2557</v>
+        <v>2555</v>
       </c>
       <c r="C726" s="3" t="s">
         <v>1552</v>
@@ -32051,7 +32035,7 @@
         <v>736</v>
       </c>
       <c r="B727" s="4" t="s">
-        <v>2558</v>
+        <v>2556</v>
       </c>
       <c r="C727" s="3" t="s">
         <v>839</v>
@@ -32062,7 +32046,7 @@
         <v>737</v>
       </c>
       <c r="B728" s="4" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
       <c r="C728" s="3" t="s">
         <v>840</v>
@@ -32073,7 +32057,7 @@
         <v>738</v>
       </c>
       <c r="B729" s="4" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
       <c r="C729" s="3" t="s">
         <v>841</v>
@@ -32084,7 +32068,7 @@
         <v>739</v>
       </c>
       <c r="B730" s="4" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
       <c r="C730" s="3" t="s">
         <v>842</v>
@@ -32095,7 +32079,7 @@
         <v>740</v>
       </c>
       <c r="B731" s="4" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="C731" s="3" t="s">
         <v>844</v>
@@ -32106,7 +32090,7 @@
         <v>741</v>
       </c>
       <c r="B732" s="4" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
       <c r="C732" s="3" t="s">
         <v>847</v>
@@ -32117,7 +32101,7 @@
         <v>742</v>
       </c>
       <c r="B733" s="4" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="C733" s="3" t="s">
         <v>848</v>
@@ -32128,7 +32112,7 @@
         <v>756</v>
       </c>
       <c r="B734" s="4" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="C734" s="3" t="s">
         <v>849</v>
@@ -32139,7 +32123,7 @@
         <v>743</v>
       </c>
       <c r="B735" s="4" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
       <c r="C735" s="3" t="s">
         <v>850</v>
@@ -32150,7 +32134,7 @@
         <v>744</v>
       </c>
       <c r="B736" s="4" t="s">
-        <v>2567</v>
+        <v>2565</v>
       </c>
       <c r="C736" s="3" t="s">
         <v>851</v>
@@ -32161,7 +32145,7 @@
         <v>745</v>
       </c>
       <c r="B737" s="4" t="s">
-        <v>2568</v>
+        <v>2566</v>
       </c>
       <c r="C737" s="3" t="s">
         <v>852</v>
@@ -32205,7 +32189,7 @@
         <v>753</v>
       </c>
       <c r="B741" s="4" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="C741" s="3" t="s">
         <v>905</v>
@@ -32227,7 +32211,7 @@
         <v>751</v>
       </c>
       <c r="B743" s="4" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="C743" s="3" t="s">
         <v>906</v>
@@ -32238,7 +32222,7 @@
         <v>750</v>
       </c>
       <c r="B744" s="4" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="C744" s="3" t="s">
         <v>908</v>
@@ -32249,7 +32233,7 @@
         <v>749</v>
       </c>
       <c r="B745" s="4" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="C745" s="3" t="s">
         <v>909</v>
@@ -32260,7 +32244,7 @@
         <v>754</v>
       </c>
       <c r="B746" s="4" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="C746" s="3" t="s">
         <v>1028</v>
@@ -32271,7 +32255,7 @@
         <v>755</v>
       </c>
       <c r="B747" s="4" t="s">
-        <v>2574</v>
+        <v>2572</v>
       </c>
       <c r="C747" s="3" t="s">
         <v>1030</v>
@@ -32282,7 +32266,7 @@
         <v>757</v>
       </c>
       <c r="B748" s="4" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="C748" s="3" t="s">
         <v>853</v>
@@ -32293,7 +32277,7 @@
         <v>758</v>
       </c>
       <c r="B749" s="4" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
       <c r="C749" s="3" t="s">
         <v>843</v>
@@ -32304,7 +32288,7 @@
         <v>759</v>
       </c>
       <c r="B750" s="4" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
       <c r="C750" s="3" t="s">
         <v>1054</v>
@@ -32315,7 +32299,7 @@
         <v>760</v>
       </c>
       <c r="B751" s="4" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="C751" s="3" t="s">
         <v>1044</v>
@@ -32337,7 +32321,7 @@
         <v>762</v>
       </c>
       <c r="B753" s="4" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="C753" s="3" t="s">
         <v>924</v>
@@ -32359,7 +32343,7 @@
         <v>766</v>
       </c>
       <c r="B755" s="4" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
       <c r="C755" s="3" t="s">
         <v>1554</v>
@@ -32370,7 +32354,7 @@
         <v>765</v>
       </c>
       <c r="B756" s="4" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
       <c r="C756" s="3" t="s">
         <v>1555</v>
@@ -32381,7 +32365,7 @@
         <v>764</v>
       </c>
       <c r="B757" s="4" t="s">
-        <v>2582</v>
+        <v>2580</v>
       </c>
       <c r="C757" s="3" t="s">
         <v>1556</v>
@@ -32392,7 +32376,7 @@
         <v>763</v>
       </c>
       <c r="B758" s="4" t="s">
-        <v>2583</v>
+        <v>2581</v>
       </c>
       <c r="C758" s="3" t="s">
         <v>1557</v>
@@ -32403,7 +32387,7 @@
         <v>768</v>
       </c>
       <c r="B759" s="4" t="s">
-        <v>2584</v>
+        <v>2582</v>
       </c>
       <c r="C759" s="3" t="s">
         <v>1029</v>
@@ -32414,7 +32398,7 @@
         <v>769</v>
       </c>
       <c r="B760" s="4" t="s">
-        <v>2585</v>
+        <v>2583</v>
       </c>
       <c r="C760" s="3" t="s">
         <v>985</v>
@@ -32425,7 +32409,7 @@
         <v>771</v>
       </c>
       <c r="B761" s="4" t="s">
-        <v>2586</v>
+        <v>2584</v>
       </c>
       <c r="C761" s="3" t="s">
         <v>1558</v>
@@ -32436,7 +32420,7 @@
         <v>770</v>
       </c>
       <c r="B762" s="4" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="C762" s="3" t="s">
         <v>890</v>
@@ -32447,7 +32431,7 @@
         <v>774</v>
       </c>
       <c r="B763" s="4" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="C763" s="3" t="s">
         <v>1595</v>
@@ -32458,7 +32442,7 @@
         <v>773</v>
       </c>
       <c r="B764" s="4" t="s">
-        <v>2589</v>
+        <v>2587</v>
       </c>
       <c r="C764" s="3" t="s">
         <v>1056</v>
@@ -32469,7 +32453,7 @@
         <v>772</v>
       </c>
       <c r="B765" s="4" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
       <c r="C765" s="3" t="s">
         <v>1057</v>
@@ -32480,7 +32464,7 @@
         <v>775</v>
       </c>
       <c r="B766" s="4" t="s">
-        <v>2591</v>
+        <v>2589</v>
       </c>
       <c r="C766" s="3" t="s">
         <v>1559</v>
@@ -32491,7 +32475,7 @@
         <v>776</v>
       </c>
       <c r="B767" s="4" t="s">
-        <v>2592</v>
+        <v>2590</v>
       </c>
       <c r="C767" s="3" t="s">
         <v>1560</v>
@@ -32502,7 +32486,7 @@
         <v>777</v>
       </c>
       <c r="B768" s="4" t="s">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="C768" s="3" t="s">
         <v>915</v>
@@ -32513,7 +32497,7 @@
         <v>784</v>
       </c>
       <c r="B769" s="4" t="s">
-        <v>2594</v>
+        <v>2592</v>
       </c>
       <c r="C769" s="3" t="s">
         <v>1561</v>
@@ -32524,7 +32508,7 @@
         <v>783</v>
       </c>
       <c r="B770" s="4" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="C770" s="3" t="s">
         <v>1562</v>
@@ -32535,7 +32519,7 @@
         <v>782</v>
       </c>
       <c r="B771" s="4" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="C771" s="3" t="s">
         <v>1563</v>
@@ -32546,7 +32530,7 @@
         <v>781</v>
       </c>
       <c r="B772" s="4" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
       <c r="C772" s="3" t="s">
         <v>1564</v>
@@ -32557,7 +32541,7 @@
         <v>780</v>
       </c>
       <c r="B773" s="4" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
       <c r="C773" s="3" t="s">
         <v>1565</v>
@@ -32568,7 +32552,7 @@
         <v>779</v>
       </c>
       <c r="B774" s="4" t="s">
-        <v>2599</v>
+        <v>2597</v>
       </c>
       <c r="C774" s="3" t="s">
         <v>1566</v>
@@ -32579,7 +32563,7 @@
         <v>778</v>
       </c>
       <c r="B775" s="4" t="s">
-        <v>2600</v>
+        <v>2598</v>
       </c>
       <c r="C775" s="3" t="s">
         <v>1567</v>
@@ -32601,7 +32585,7 @@
         <v>786</v>
       </c>
       <c r="B777" s="4" t="s">
-        <v>2601</v>
+        <v>2599</v>
       </c>
       <c r="C777" s="3" t="s">
         <v>1569</v>
@@ -32623,7 +32607,7 @@
         <v>788</v>
       </c>
       <c r="B779" s="4" t="s">
-        <v>2602</v>
+        <v>2600</v>
       </c>
       <c r="C779" s="3" t="s">
         <v>919</v>
@@ -32634,7 +32618,7 @@
         <v>789</v>
       </c>
       <c r="B780" s="4" t="s">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="C780" s="3" t="s">
         <v>917</v>
@@ -32645,7 +32629,7 @@
         <v>790</v>
       </c>
       <c r="B781" s="4" t="s">
-        <v>2604</v>
+        <v>2602</v>
       </c>
       <c r="C781" s="3" t="s">
         <v>918</v>
@@ -32656,7 +32640,7 @@
         <v>799</v>
       </c>
       <c r="B782" s="4" t="s">
-        <v>2605</v>
+        <v>2603</v>
       </c>
       <c r="C782" s="3" t="s">
         <v>1571</v>
@@ -32667,7 +32651,7 @@
         <v>798</v>
       </c>
       <c r="B783" s="4" t="s">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="C783" s="3" t="s">
         <v>1572</v>
@@ -32733,7 +32717,7 @@
         <v>792</v>
       </c>
       <c r="B789" s="4" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="C789" s="3" t="s">
         <v>1574</v>
@@ -32744,7 +32728,7 @@
         <v>791</v>
       </c>
       <c r="B790" s="4" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="C790" s="3" t="s">
         <v>1575</v>
@@ -32755,7 +32739,7 @@
         <v>800</v>
       </c>
       <c r="B791" s="4" t="s">
-        <v>2609</v>
+        <v>2607</v>
       </c>
       <c r="C791" s="3" t="s">
         <v>916</v>
@@ -32766,7 +32750,7 @@
         <v>803</v>
       </c>
       <c r="B792" s="4" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
       <c r="C792" s="3" t="s">
         <v>1576</v>
@@ -32777,7 +32761,7 @@
         <v>802</v>
       </c>
       <c r="B793" s="4" t="s">
-        <v>2611</v>
+        <v>2609</v>
       </c>
       <c r="C793" s="3" t="s">
         <v>1577</v>
@@ -32788,7 +32772,7 @@
         <v>801</v>
       </c>
       <c r="B794" s="4" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="C794" s="3" t="s">
         <v>1578</v>
@@ -32799,7 +32783,7 @@
         <v>804</v>
       </c>
       <c r="B795" s="4" t="s">
-        <v>2613</v>
+        <v>2611</v>
       </c>
       <c r="C795" s="3" t="s">
         <v>1045</v>
@@ -32821,7 +32805,7 @@
         <v>809</v>
       </c>
       <c r="B797" s="4" t="s">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="C797" s="3" t="s">
         <v>1580</v>
@@ -32832,7 +32816,7 @@
         <v>808</v>
       </c>
       <c r="B798" s="4" t="s">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="C798" s="3" t="s">
         <v>1581</v>
@@ -32843,7 +32827,7 @@
         <v>807</v>
       </c>
       <c r="B799" s="4" t="s">
-        <v>2616</v>
+        <v>2614</v>
       </c>
       <c r="C799" s="3" t="s">
         <v>1035</v>
@@ -32854,7 +32838,7 @@
         <v>806</v>
       </c>
       <c r="B800" s="4" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
       <c r="C800" s="3" t="s">
         <v>1036</v>
@@ -32865,7 +32849,7 @@
         <v>810</v>
       </c>
       <c r="B801" s="4" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="C801" s="3" t="s">
         <v>1582</v>
@@ -32887,7 +32871,7 @@
         <v>812</v>
       </c>
       <c r="B803" s="4" t="s">
-        <v>2619</v>
+        <v>2617</v>
       </c>
       <c r="C803" s="3" t="s">
         <v>1584</v>
@@ -32909,7 +32893,7 @@
         <v>814</v>
       </c>
       <c r="B805" s="4" t="s">
-        <v>2620</v>
+        <v>2618</v>
       </c>
       <c r="C805" s="3" t="s">
         <v>1586</v>
@@ -32931,7 +32915,7 @@
         <v>1592</v>
       </c>
       <c r="B807" s="4" t="s">
-        <v>2621</v>
+        <v>2619</v>
       </c>
       <c r="C807" s="3" t="s">
         <v>1501</v>
@@ -32942,7 +32926,7 @@
         <v>1591</v>
       </c>
       <c r="B808" s="4" t="s">
-        <v>2622</v>
+        <v>2620</v>
       </c>
       <c r="C808" s="3" t="s">
         <v>1593</v>
@@ -32964,10 +32948,10 @@
         <v>1604</v>
       </c>
       <c r="B810" s="4" t="s">
-        <v>2709</v>
+        <v>2707</v>
       </c>
       <c r="C810" s="3" t="s">
-        <v>2710</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.4">
@@ -32997,7 +32981,7 @@
         <v>1623</v>
       </c>
       <c r="B813" s="4" t="s">
-        <v>2623</v>
+        <v>2621</v>
       </c>
       <c r="C813" s="3" t="s">
         <v>1616</v>
@@ -33008,7 +32992,7 @@
         <v>1622</v>
       </c>
       <c r="B814" s="4" t="s">
-        <v>2624</v>
+        <v>2622</v>
       </c>
       <c r="C814" s="3" t="s">
         <v>1617</v>
@@ -33019,7 +33003,7 @@
         <v>1621</v>
       </c>
       <c r="B815" s="4" t="s">
-        <v>2625</v>
+        <v>2623</v>
       </c>
       <c r="C815" s="3" t="s">
         <v>1618</v>
@@ -33030,7 +33014,7 @@
         <v>1620</v>
       </c>
       <c r="B816" s="4" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="C816" s="3" t="s">
         <v>1619</v>
@@ -33041,7 +33025,7 @@
         <v>1624</v>
       </c>
       <c r="B817" s="4" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="C817" s="3" t="s">
         <v>1629</v>
@@ -33052,7 +33036,7 @@
         <v>1625</v>
       </c>
       <c r="B818" s="4" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="C818" s="3" t="s">
         <v>1630</v>
@@ -33063,7 +33047,7 @@
         <v>1626</v>
       </c>
       <c r="B819" s="4" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="C819" s="3" t="s">
         <v>1631</v>
@@ -33074,7 +33058,7 @@
         <v>1627</v>
       </c>
       <c r="B820" s="4" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="C820" s="3" t="s">
         <v>1632</v>
@@ -33085,7 +33069,7 @@
         <v>1628</v>
       </c>
       <c r="B821" s="4" t="s">
-        <v>2631</v>
+        <v>2629</v>
       </c>
       <c r="C821" s="3" t="s">
         <v>1633</v>
@@ -33096,7 +33080,7 @@
         <v>1634</v>
       </c>
       <c r="B822" s="4" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="C822" s="3" t="s">
         <v>1636</v>
@@ -33107,7 +33091,7 @@
         <v>1635</v>
       </c>
       <c r="B823" s="4" t="s">
-        <v>2633</v>
+        <v>2631</v>
       </c>
       <c r="C823" s="3" t="s">
         <v>1637</v>
@@ -33118,7 +33102,7 @@
         <v>1638</v>
       </c>
       <c r="B824" s="4" t="s">
-        <v>2634</v>
+        <v>2632</v>
       </c>
       <c r="C824" s="3" t="s">
         <v>1639</v>
@@ -33129,7 +33113,7 @@
         <v>1649</v>
       </c>
       <c r="B825" s="4" t="s">
-        <v>2635</v>
+        <v>2633</v>
       </c>
       <c r="C825" s="3" t="s">
         <v>1640</v>
@@ -33140,7 +33124,7 @@
         <v>1648</v>
       </c>
       <c r="B826" s="4" t="s">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="C826" s="3" t="s">
         <v>1641</v>
@@ -33151,7 +33135,7 @@
         <v>1647</v>
       </c>
       <c r="B827" s="4" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
       <c r="C827" s="3" t="s">
         <v>1642</v>
@@ -33162,7 +33146,7 @@
         <v>1646</v>
       </c>
       <c r="B828" s="4" t="s">
-        <v>2638</v>
+        <v>2636</v>
       </c>
       <c r="C828" s="3" t="s">
         <v>1643</v>
@@ -33173,7 +33157,7 @@
         <v>1645</v>
       </c>
       <c r="B829" s="4" t="s">
-        <v>2639</v>
+        <v>2637</v>
       </c>
       <c r="C829" s="3" t="s">
         <v>1644</v>
@@ -33184,7 +33168,7 @@
         <v>1651</v>
       </c>
       <c r="B830" s="4" t="s">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="C830" s="3" t="s">
         <v>1650</v>
@@ -33195,7 +33179,7 @@
         <v>1652</v>
       </c>
       <c r="B831" s="4" t="s">
-        <v>2641</v>
+        <v>2639</v>
       </c>
       <c r="C831" s="3" t="s">
         <v>1653</v>
@@ -33217,7 +33201,7 @@
         <v>1662</v>
       </c>
       <c r="B833" s="4" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="C833" s="3" t="s">
         <v>1663</v>
@@ -33272,7 +33256,7 @@
         <v>1675</v>
       </c>
       <c r="B838" s="4" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="C838" s="3" t="s">
         <v>1676</v>
@@ -33283,7 +33267,7 @@
         <v>1677</v>
       </c>
       <c r="B839" s="4" t="s">
-        <v>2644</v>
+        <v>2642</v>
       </c>
       <c r="C839" s="3" t="s">
         <v>1678</v>
@@ -33294,7 +33278,7 @@
         <v>1679</v>
       </c>
       <c r="B840" s="4" t="s">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="C840" s="3" t="s">
         <v>1680</v>
@@ -33305,7 +33289,7 @@
         <v>1681</v>
       </c>
       <c r="B841" s="4" t="s">
-        <v>2646</v>
+        <v>2644</v>
       </c>
       <c r="C841" s="3" t="s">
         <v>1682</v>
@@ -33316,7 +33300,7 @@
         <v>1683</v>
       </c>
       <c r="B842" s="4" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="C842" s="3" t="s">
         <v>1676</v>
@@ -33327,7 +33311,7 @@
         <v>1684</v>
       </c>
       <c r="B843" s="4" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
       <c r="C843" s="3" t="s">
         <v>1685</v>
@@ -33338,7 +33322,7 @@
         <v>1686</v>
       </c>
       <c r="B844" s="4" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="C844" s="3" t="s">
         <v>1676</v>
@@ -33349,7 +33333,7 @@
         <v>1687</v>
       </c>
       <c r="B845" s="4" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
       <c r="C845" s="3" t="s">
         <v>1688</v>
@@ -33360,7 +33344,7 @@
         <v>1689</v>
       </c>
       <c r="B846" s="4" t="s">
-        <v>2650</v>
+        <v>2648</v>
       </c>
       <c r="C846" s="3" t="s">
         <v>1680</v>
@@ -33371,7 +33355,7 @@
         <v>1690</v>
       </c>
       <c r="B847" s="4" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="C847" s="3" t="s">
         <v>1691</v>
@@ -33778,7 +33762,7 @@
         <v>1840</v>
       </c>
       <c r="B884" s="4" t="s">
-        <v>2652</v>
+        <v>2650</v>
       </c>
       <c r="C884" s="3" t="s">
         <v>1841</v>
@@ -33965,7 +33949,7 @@
         <v>1842</v>
       </c>
       <c r="B901" s="4" t="s">
-        <v>2653</v>
+        <v>2651</v>
       </c>
       <c r="C901" s="3" t="s">
         <v>1843</v>
@@ -33987,7 +33971,7 @@
         <v>1847</v>
       </c>
       <c r="B903" s="4" t="s">
-        <v>2654</v>
+        <v>2652</v>
       </c>
       <c r="C903" s="3" t="s">
         <v>1848</v>
@@ -33998,7 +33982,7 @@
         <v>1850</v>
       </c>
       <c r="B904" s="4" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="C904" s="3" t="s">
         <v>1851</v>
@@ -34020,7 +34004,7 @@
         <v>1858</v>
       </c>
       <c r="B906" s="4" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="C906" s="3" t="s">
         <v>1855</v>
@@ -34031,7 +34015,7 @@
         <v>1859</v>
       </c>
       <c r="B907" s="4" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="C907" s="3" t="s">
         <v>1856</v>
@@ -34042,7 +34026,7 @@
         <v>1860</v>
       </c>
       <c r="B908" s="4" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
       <c r="C908" s="3" t="s">
         <v>1857</v>
@@ -34053,7 +34037,7 @@
         <v>1864</v>
       </c>
       <c r="B909" s="4" t="s">
-        <v>2659</v>
+        <v>2657</v>
       </c>
       <c r="C909" s="3" t="s">
         <v>1861</v>
@@ -34064,7 +34048,7 @@
         <v>1865</v>
       </c>
       <c r="B910" s="4" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="C910" s="3" t="s">
         <v>1862</v>
@@ -34075,7 +34059,7 @@
         <v>1866</v>
       </c>
       <c r="B911" s="4" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="C911" s="3" t="s">
         <v>1863</v>
@@ -34130,7 +34114,7 @@
         <v>1877</v>
       </c>
       <c r="B916" s="4" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="C916" s="3" t="s">
         <v>1878</v>
@@ -34152,7 +34136,7 @@
         <v>1883</v>
       </c>
       <c r="B918" s="4" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="C918" s="3" t="s">
         <v>1884</v>
@@ -34163,7 +34147,7 @@
         <v>1885</v>
       </c>
       <c r="B919" s="4" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="C919" s="3" t="s">
         <v>1886</v>
@@ -34273,7 +34257,7 @@
         <v>1930</v>
       </c>
       <c r="B929" s="4" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="C929" s="3" t="s">
         <v>1910</v>
@@ -34317,7 +34301,7 @@
         <v>1933</v>
       </c>
       <c r="B933" s="4" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
       <c r="C933" s="3" t="s">
         <v>1550</v>
@@ -34328,7 +34312,7 @@
         <v>1934</v>
       </c>
       <c r="B934" s="4" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="C934" s="3" t="s">
         <v>1920</v>
@@ -34339,7 +34323,7 @@
         <v>1935</v>
       </c>
       <c r="B935" s="4" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="C935" s="3" t="s">
         <v>1921</v>
@@ -34350,7 +34334,7 @@
         <v>1936</v>
       </c>
       <c r="B936" s="4" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="C936" s="3" t="s">
         <v>1922</v>
@@ -34361,7 +34345,7 @@
         <v>1937</v>
       </c>
       <c r="B937" s="4" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="C937" s="3" t="s">
         <v>1923</v>
@@ -34372,7 +34356,7 @@
         <v>1938</v>
       </c>
       <c r="B938" s="4" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="C938" s="3" t="s">
         <v>1924</v>
@@ -34383,7 +34367,7 @@
         <v>1939</v>
       </c>
       <c r="B939" s="4" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="C939" s="3" t="s">
         <v>1925</v>
@@ -34394,7 +34378,7 @@
         <v>1940</v>
       </c>
       <c r="B940" s="4" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="C940" s="3" t="s">
         <v>1926</v>
@@ -34405,7 +34389,7 @@
         <v>1941</v>
       </c>
       <c r="B941" s="4" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="C941" s="3" t="s">
         <v>1927</v>
@@ -34416,7 +34400,7 @@
         <v>1942</v>
       </c>
       <c r="B942" s="4" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="C942" s="3" t="s">
         <v>1928</v>
@@ -34427,7 +34411,7 @@
         <v>1943</v>
       </c>
       <c r="B943" s="4" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="C943" s="3" t="s">
         <v>1926</v>
@@ -34438,7 +34422,7 @@
         <v>1944</v>
       </c>
       <c r="B944" s="4" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="C944" s="3" t="s">
         <v>1927</v>
@@ -34446,321 +34430,321 @@
     </row>
     <row r="945" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A945" s="3" t="s">
+        <v>2674</v>
+      </c>
+      <c r="B945" s="4" t="s">
+        <v>2675</v>
+      </c>
+      <c r="C945" s="3" t="s">
         <v>2676</v>
-      </c>
-      <c r="B945" s="4" t="s">
-        <v>2677</v>
-      </c>
-      <c r="C945" s="3" t="s">
-        <v>2678</v>
       </c>
     </row>
     <row r="946" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A946" s="3" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
       <c r="B946" s="4" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="C946" s="3" t="s">
-        <v>2693</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="947" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A947" s="3" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
       <c r="B947" s="4" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
       <c r="C947" s="3" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A948" s="3" t="s">
-        <v>2690</v>
+        <v>2688</v>
       </c>
       <c r="B948" s="4" t="s">
-        <v>2681</v>
+        <v>2679</v>
       </c>
       <c r="C948" s="3" t="s">
-        <v>2695</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="949" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A949" s="3" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
       <c r="B949" s="4" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="C949" s="3" t="s">
-        <v>2696</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="950" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A950" s="3" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
       <c r="B950" s="4" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
       <c r="C950" s="3" t="s">
-        <v>2697</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="951" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A951" s="3" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="B951" s="4" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="C951" s="3" t="s">
-        <v>2698</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="952" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A952" s="3" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="B952" s="4" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
       <c r="C952" s="3" t="s">
-        <v>2699</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="953" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A953" s="3" t="s">
+        <v>2698</v>
+      </c>
+      <c r="B953" s="4" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C953" s="3" t="s">
         <v>2700</v>
-      </c>
-      <c r="B953" s="4" t="s">
-        <v>2701</v>
-      </c>
-      <c r="C953" s="3" t="s">
-        <v>2702</v>
       </c>
     </row>
     <row r="954" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A954" s="3" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B954" s="4" t="s">
+        <v>2702</v>
+      </c>
+      <c r="C954" s="3" t="s">
         <v>2703</v>
-      </c>
-      <c r="B954" s="4" t="s">
-        <v>2704</v>
-      </c>
-      <c r="C954" s="3" t="s">
-        <v>2705</v>
       </c>
     </row>
     <row r="955" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A955" s="3" t="s">
-        <v>2707</v>
+        <v>2705</v>
       </c>
       <c r="B955" s="4" t="s">
-        <v>2708</v>
+        <v>2706</v>
       </c>
       <c r="C955" s="3" t="s">
-        <v>2706</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="956" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A956" s="3" t="s">
+        <v>2709</v>
+      </c>
+      <c r="B956" s="4" t="s">
         <v>2711</v>
       </c>
-      <c r="B956" s="4" t="s">
-        <v>2713</v>
-      </c>
       <c r="C956" s="3" t="s">
-        <v>2712</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="957" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A957" s="3" t="s">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="B957" s="4" t="s">
-        <v>2717</v>
+        <v>2715</v>
       </c>
       <c r="C957" s="3" t="s">
-        <v>2725</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="958" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A958" s="3" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="B958" s="4" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
       <c r="C958" s="3" t="s">
-        <v>2723</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A959" s="3" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
       <c r="B959" s="4" t="s">
-        <v>2721</v>
+        <v>2719</v>
       </c>
       <c r="C959" s="3" t="s">
-        <v>2724</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="960" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A960" s="3" t="s">
-        <v>2718</v>
+        <v>2716</v>
       </c>
       <c r="B960" s="4" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="C960" s="3" t="s">
-        <v>2722</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="961" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A961" s="3" t="s">
+        <v>2724</v>
+      </c>
+      <c r="B961" s="4" t="s">
+        <v>2725</v>
+      </c>
+      <c r="C961" s="3" t="s">
         <v>2726</v>
-      </c>
-      <c r="B961" s="4" t="s">
-        <v>2727</v>
-      </c>
-      <c r="C961" s="3" t="s">
-        <v>2728</v>
       </c>
     </row>
     <row r="962" spans="1:4" ht="38" x14ac:dyDescent="0.4">
       <c r="A962" s="3" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
       <c r="B962" s="4" t="s">
-        <v>2731</v>
+        <v>2729</v>
       </c>
       <c r="C962" s="3" t="s">
-        <v>2729</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="963" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A963" s="3" t="s">
+        <v>2730</v>
+      </c>
+      <c r="B963" s="4" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C963" s="3" t="s">
         <v>2732</v>
-      </c>
-      <c r="B963" s="4" t="s">
-        <v>2733</v>
-      </c>
-      <c r="C963" s="3" t="s">
-        <v>2734</v>
       </c>
     </row>
     <row r="964" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A964" s="3" t="s">
-        <v>2737</v>
+        <v>2735</v>
       </c>
       <c r="B964" s="4" t="s">
-        <v>2735</v>
+        <v>2733</v>
       </c>
       <c r="C964" s="3" t="s">
-        <v>2736</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="965" spans="1:4" ht="38" x14ac:dyDescent="0.4">
       <c r="A965" s="3" t="s">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="B965" s="4" t="s">
-        <v>2744</v>
+        <v>2742</v>
       </c>
       <c r="C965" s="3" t="s">
-        <v>2739</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="966" spans="1:4" ht="38" x14ac:dyDescent="0.4">
       <c r="A966" s="3" t="s">
-        <v>2742</v>
+        <v>2740</v>
       </c>
       <c r="B966" s="4" t="s">
-        <v>2745</v>
+        <v>2743</v>
       </c>
       <c r="C966" s="3" t="s">
-        <v>2738</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="967" spans="1:4" ht="38" x14ac:dyDescent="0.4">
       <c r="A967" s="3" t="s">
-        <v>2743</v>
+        <v>2741</v>
       </c>
       <c r="B967" s="4" t="s">
-        <v>2746</v>
+        <v>2744</v>
       </c>
       <c r="C967" s="3" t="s">
-        <v>2740</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="968" spans="1:4" ht="38" x14ac:dyDescent="0.4">
       <c r="A968" s="3" t="s">
-        <v>2749</v>
+        <v>2747</v>
       </c>
       <c r="B968" s="4" t="s">
-        <v>2753</v>
+        <v>2751</v>
       </c>
       <c r="C968" s="3" t="s">
-        <v>2752</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="969" spans="1:4" ht="38" x14ac:dyDescent="0.4">
       <c r="A969" s="3" t="s">
-        <v>2750</v>
+        <v>2748</v>
       </c>
       <c r="B969" s="4" t="s">
-        <v>2754</v>
+        <v>2752</v>
       </c>
       <c r="C969" s="3" t="s">
-        <v>2751</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="970" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A970" s="3" t="s">
-        <v>2759</v>
+        <v>2757</v>
       </c>
       <c r="B970" s="4" t="s">
-        <v>2755</v>
+        <v>2753</v>
       </c>
       <c r="C970" s="3" t="s">
-        <v>2777</v>
+        <v>2775</v>
       </c>
       <c r="D970" s="5"/>
     </row>
     <row r="971" spans="1:4" ht="57" x14ac:dyDescent="0.4">
       <c r="A971" s="3" t="s">
-        <v>2760</v>
+        <v>2758</v>
       </c>
       <c r="B971" s="4" t="s">
-        <v>2756</v>
+        <v>2754</v>
       </c>
       <c r="C971" s="3" t="s">
-        <v>2778</v>
+        <v>2776</v>
       </c>
       <c r="D971" s="5"/>
     </row>
     <row r="972" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A972" s="3" t="s">
-        <v>2761</v>
+        <v>2759</v>
       </c>
       <c r="B972" s="4" t="s">
-        <v>2757</v>
+        <v>2755</v>
       </c>
       <c r="C972" s="3" t="s">
-        <v>2779</v>
+        <v>2777</v>
       </c>
       <c r="D972" s="5"/>
     </row>
     <row r="973" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A973" s="3" t="s">
-        <v>2762</v>
+        <v>2760</v>
       </c>
       <c r="B973" s="4" t="s">
-        <v>2758</v>
+        <v>2756</v>
       </c>
       <c r="C973" s="3" t="s">
         <v>1812</v>
@@ -34769,119 +34753,119 @@
     </row>
     <row r="974" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A974" s="3" t="s">
-        <v>2763</v>
+        <v>2761</v>
       </c>
       <c r="B974" s="4" t="s">
-        <v>2764</v>
+        <v>2762</v>
       </c>
       <c r="C974" s="3" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
       <c r="D974" s="5"/>
     </row>
     <row r="975" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A975" s="3" t="s">
-        <v>2765</v>
+        <v>2763</v>
       </c>
       <c r="B975" s="4" t="s">
-        <v>2766</v>
+        <v>2764</v>
       </c>
       <c r="C975" s="3" t="s">
-        <v>2781</v>
+        <v>2779</v>
       </c>
       <c r="D975" s="5"/>
     </row>
     <row r="976" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A976" s="3" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="B976" s="4" t="s">
-        <v>2768</v>
+        <v>2766</v>
       </c>
       <c r="C976" s="3" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
       <c r="D976" s="5"/>
     </row>
     <row r="977" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A977" s="3" t="s">
-        <v>2769</v>
+        <v>2767</v>
       </c>
       <c r="B977" s="4" t="s">
-        <v>2770</v>
+        <v>2768</v>
       </c>
       <c r="C977" s="3" t="s">
-        <v>2783</v>
+        <v>2781</v>
       </c>
       <c r="D977" s="5"/>
     </row>
     <row r="978" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A978" s="3" t="s">
-        <v>2771</v>
+        <v>2769</v>
       </c>
       <c r="B978" s="4" t="s">
-        <v>2772</v>
+        <v>2770</v>
       </c>
       <c r="C978" s="3" t="s">
-        <v>2784</v>
+        <v>2782</v>
       </c>
       <c r="D978" s="5"/>
     </row>
     <row r="979" spans="1:4" ht="95" x14ac:dyDescent="0.4">
       <c r="A979" s="3" t="s">
-        <v>2773</v>
+        <v>2771</v>
       </c>
       <c r="B979" s="4" t="s">
-        <v>2774</v>
+        <v>2772</v>
       </c>
       <c r="C979" s="3" t="s">
-        <v>2785</v>
+        <v>2783</v>
       </c>
       <c r="D979" s="5"/>
     </row>
     <row r="980" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A980" s="3" t="s">
-        <v>2775</v>
+        <v>2773</v>
       </c>
       <c r="B980" s="4" t="s">
-        <v>2776</v>
+        <v>2774</v>
       </c>
       <c r="C980" s="3" t="s">
-        <v>2786</v>
+        <v>2784</v>
       </c>
       <c r="D980" s="5"/>
     </row>
     <row r="981" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A981" s="3" t="s">
-        <v>2792</v>
+        <v>2790</v>
       </c>
       <c r="B981" s="4" t="s">
-        <v>2787</v>
+        <v>2785</v>
       </c>
       <c r="C981" s="3" t="s">
-        <v>2793</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="982" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A982" s="3" t="s">
-        <v>2791</v>
+        <v>2789</v>
       </c>
       <c r="B982" s="4" t="s">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="C982" s="3" t="s">
-        <v>2794</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="983" spans="1:4" ht="57" x14ac:dyDescent="0.4">
       <c r="A983" s="3" t="s">
-        <v>2790</v>
+        <v>2788</v>
       </c>
       <c r="B983" s="4" t="s">
-        <v>2789</v>
+        <v>2787</v>
       </c>
       <c r="C983" s="3" t="s">
-        <v>2795</v>
+        <v>2793</v>
       </c>
     </row>
   </sheetData>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA3DEF5-3904-4E46-BB25-5824237A3D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B31319E-0C4A-4B3B-8BCA-26903BD47817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="160" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2943" uniqueCount="2796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="2799">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23651,6 +23651,16 @@
   <si>
     <t>仅在缩小时使用双线性插值缩放</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.DirectXRendering</t>
+  </si>
+  <si>
+    <t>使用DirectX 11绘图</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Draw using DirectX 11</t>
   </si>
 </sst>
 </file>
@@ -24053,7 +24063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D983"/>
+  <dimension ref="A1:D984"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34868,6 +34878,17 @@
         <v>2793</v>
       </c>
     </row>
+    <row r="984" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A984" s="3" t="s">
+        <v>2796</v>
+      </c>
+      <c r="B984" s="4" t="s">
+        <v>2797</v>
+      </c>
+      <c r="C984" s="3" t="s">
+        <v>2798</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B31319E-0C4A-4B3B-8BCA-26903BD47817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0853A6F3-5326-4322-9439-EF7C04196A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="160" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="2799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2952" uniqueCount="2805">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23661,6 +23661,26 @@
   </si>
   <si>
     <t>Draw using DirectX 11</t>
+  </si>
+  <si>
+    <t>ViewDesignatorRangeInfo</t>
+  </si>
+  <si>
+    <t>ViewInhibitorRangeInfo</t>
+  </si>
+  <si>
+    <t>指示者范围</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抑制者范围</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Designator Range</t>
+  </si>
+  <si>
+    <t>Inhibitor Range</t>
   </si>
 </sst>
 </file>
@@ -24063,7 +24083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D984"/>
+  <dimension ref="A1:D986"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34889,6 +34909,28 @@
         <v>2798</v>
       </c>
     </row>
+    <row r="985" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A985" s="3" t="s">
+        <v>2799</v>
+      </c>
+      <c r="B985" s="4" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C985" s="3" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="986" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A986" s="3" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B986" s="4" t="s">
+        <v>2802</v>
+      </c>
+      <c r="C986" s="3" t="s">
+        <v>2804</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0853A6F3-5326-4322-9439-EF7C04196A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB91445-8BC7-4D24-B1D8-E701294B965B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="160" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2952" uniqueCount="2805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2955" uniqueCount="2808">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23681,6 +23681,16 @@
   </si>
   <si>
     <t>Inhibitor Range</t>
+  </si>
+  <si>
+    <t>Options.PreciseDepthCalculation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Precisely calculate the depth relationship of game objects (slower)</t>
+  </si>
+  <si>
+    <t>精确计算游戏对象间的深度关系（轻微影响性能）</t>
   </si>
 </sst>
 </file>
@@ -24083,7 +24093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D986"/>
+  <dimension ref="A1:D987"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34931,6 +34941,17 @@
         <v>2804</v>
       </c>
     </row>
+    <row r="987" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A987" s="3" t="s">
+        <v>2805</v>
+      </c>
+      <c r="B987" s="4" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C987" s="3" t="s">
+        <v>2806</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB91445-8BC7-4D24-B1D8-E701294B965B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD610A29-C5D1-4DAF-9F6F-18B56E954BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="160" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23656,13 +23656,6 @@
     <t>Options.DirectXRendering</t>
   </si>
   <si>
-    <t>使用DirectX 11绘图</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Draw using DirectX 11</t>
-  </si>
-  <si>
     <t>ViewDesignatorRangeInfo</t>
   </si>
   <si>
@@ -23691,6 +23684,13 @@
   </si>
   <si>
     <t>精确计算游戏对象间的深度关系（轻微影响性能）</t>
+  </si>
+  <si>
+    <t>使用 DirectX 11 (显卡) 绘图</t>
+  </si>
+  <si>
+    <t>Draw map using DirectX 11 (GPU)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -34913,43 +34913,43 @@
         <v>2796</v>
       </c>
       <c r="B984" s="4" t="s">
-        <v>2797</v>
+        <v>2806</v>
       </c>
       <c r="C984" s="3" t="s">
-        <v>2798</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="985" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A985" s="3" t="s">
+        <v>2797</v>
+      </c>
+      <c r="B985" s="4" t="s">
         <v>2799</v>
       </c>
-      <c r="B985" s="4" t="s">
+      <c r="C985" s="3" t="s">
         <v>2801</v>
-      </c>
-      <c r="C985" s="3" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="986" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A986" s="3" t="s">
+        <v>2798</v>
+      </c>
+      <c r="B986" s="4" t="s">
         <v>2800</v>
       </c>
-      <c r="B986" s="4" t="s">
+      <c r="C986" s="3" t="s">
         <v>2802</v>
-      </c>
-      <c r="C986" s="3" t="s">
-        <v>2804</v>
       </c>
     </row>
     <row r="987" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A987" s="3" t="s">
+        <v>2803</v>
+      </c>
+      <c r="B987" s="4" t="s">
         <v>2805</v>
       </c>
-      <c r="B987" s="4" t="s">
-        <v>2807</v>
-      </c>
       <c r="C987" s="3" t="s">
-        <v>2806</v>
+        <v>2804</v>
       </c>
     </row>
   </sheetData>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD610A29-C5D1-4DAF-9F6F-18B56E954BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BED8C9-323D-474C-BCD6-F8BE4C47CB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="160" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2955" uniqueCount="2808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="2814">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23691,6 +23691,26 @@
   <si>
     <t>Draw map using DirectX 11 (GPU)</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Loading objects, please wait...</t>
+  </si>
+  <si>
+    <t>InitAllObjectsProgressText</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.LoadObjectsOnInit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Load all in-map objects during map initialization</t>
+  </si>
+  <si>
+    <t>加载单位中，请稍后...</t>
+  </si>
+  <si>
+    <t>在地图初始化时加载所有地图内对象</t>
   </si>
 </sst>
 </file>
@@ -24093,7 +24113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D987"/>
+  <dimension ref="A1:D989"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34952,6 +34972,28 @@
         <v>2804</v>
       </c>
     </row>
+    <row r="988" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A988" s="3" t="s">
+        <v>2809</v>
+      </c>
+      <c r="B988" s="4" t="s">
+        <v>2812</v>
+      </c>
+      <c r="C988" s="3" t="s">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="989" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A989" s="3" t="s">
+        <v>2810</v>
+      </c>
+      <c r="B989" s="4" t="s">
+        <v>2813</v>
+      </c>
+      <c r="C989" s="3" t="s">
+        <v>2811</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BED8C9-323D-474C-BCD6-F8BE4C47CB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849AF069-0AFF-4989-8D15-F548FF991162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4780" yWindow="160" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4830" yWindow="130" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="2814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2979" uniqueCount="2830">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23711,6 +23711,64 @@
   </si>
   <si>
     <t>在地图初始化时加载所有地图内对象</t>
+  </si>
+  <si>
+    <t>Please select parent country:</t>
+  </si>
+  <si>
+    <t>HousesRepairBaseNodes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HouseDialog.SelectParentCountry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择继承国家：</t>
+  </si>
+  <si>
+    <t>维修基地节点 (Phobos B32+)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Repair BaseNodes (Phobos B32+)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Display whether triggers are disabled in the dropdown menu</t>
+  </si>
+  <si>
+    <t>在下拉菜单中显示触发是否被禁止</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.DisplayTriggerEnableInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HousesRepairBaseNodesMedium</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>简单</t>
+  </si>
+  <si>
+    <t>困难</t>
+  </si>
+  <si>
+    <t>普通</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HousesRepairBaseNodesEasy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>HousesRepairBaseNodesHard</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -24113,7 +24171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D989"/>
+  <dimension ref="A1:D995"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -34994,6 +35052,72 @@
         <v>2811</v>
       </c>
     </row>
+    <row r="990" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A990" s="3" t="s">
+        <v>2816</v>
+      </c>
+      <c r="B990" s="4" t="s">
+        <v>2817</v>
+      </c>
+      <c r="C990" s="3" t="s">
+        <v>2814</v>
+      </c>
+    </row>
+    <row r="991" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A991" s="3" t="s">
+        <v>2815</v>
+      </c>
+      <c r="B991" s="4" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C991" s="3" t="s">
+        <v>2819</v>
+      </c>
+    </row>
+    <row r="992" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A992" s="3" t="s">
+        <v>2822</v>
+      </c>
+      <c r="B992" s="4" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C992" s="3" t="s">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A993" s="3" t="s">
+        <v>2827</v>
+      </c>
+      <c r="B993" s="4" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C993" s="3" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A994" s="3" t="s">
+        <v>2823</v>
+      </c>
+      <c r="B994" s="4" t="s">
+        <v>2826</v>
+      </c>
+      <c r="C994" s="3" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="995" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A995" s="3" t="s">
+        <v>2829</v>
+      </c>
+      <c r="B995" s="4" t="s">
+        <v>2825</v>
+      </c>
+      <c r="C995" s="3" t="s">
+        <v>1223</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849AF069-0AFF-4989-8D15-F548FF991162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD911FF-F0D8-47A4-A298-50DB8A5CE6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4830" yWindow="130" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2979" uniqueCount="2830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2988" uniqueCount="2839">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23768,6 +23768,38 @@
   </si>
   <si>
     <t>HousesRepairBaseNodesHard</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Param - Tag</t>
+  </si>
+  <si>
+    <t>Param - Team</t>
+  </si>
+  <si>
+    <t>Param - Trigger</t>
+  </si>
+  <si>
+    <t>SearhReference.TriggerParam.Tag</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SearhReference.TriggerParam.Team</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SearhReference.TriggerParam.Trigger</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数 - 标签</t>
+  </si>
+  <si>
+    <t>参数 - 小队</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数 - 触发</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -24171,7 +24203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D995"/>
+  <dimension ref="A1:D998"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -35118,6 +35150,39 @@
         <v>1223</v>
       </c>
     </row>
+    <row r="996" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A996" s="3" t="s">
+        <v>2833</v>
+      </c>
+      <c r="B996" s="4" t="s">
+        <v>2836</v>
+      </c>
+      <c r="C996" s="3" t="s">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="997" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A997" s="3" t="s">
+        <v>2834</v>
+      </c>
+      <c r="B997" s="4" t="s">
+        <v>2837</v>
+      </c>
+      <c r="C997" s="3" t="s">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="998" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A998" s="3" t="s">
+        <v>2835</v>
+      </c>
+      <c r="B998" s="4" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C998" s="3" t="s">
+        <v>2832</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD911FF-F0D8-47A4-A298-50DB8A5CE6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7692DDFA-9142-40B8-8CEE-3E964D8E4AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4830" yWindow="130" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2988" uniqueCount="2839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3000" uniqueCount="2851">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23800,6 +23800,47 @@
   </si>
   <si>
     <t>参数 - 触发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Place Free Circle</t>
+  </si>
+  <si>
+    <t>Place Line Segment</t>
+  </si>
+  <si>
+    <t>Place Arrow</t>
+  </si>
+  <si>
+    <t>Place Circle</t>
+  </si>
+  <si>
+    <t>MeasurementToolbox.PlaceCircle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnnotationObListAddLineSegment</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnnotationObListAddArrow</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnnotationObListAddCircle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置自由圆</t>
+  </si>
+  <si>
+    <t>放置线段</t>
+  </si>
+  <si>
+    <t>放置箭头</t>
+  </si>
+  <si>
+    <t>放置圆</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -24203,7 +24244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D998"/>
+  <dimension ref="A1:D1002"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -35183,6 +35224,50 @@
         <v>2832</v>
       </c>
     </row>
+    <row r="999" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A999" s="3" t="s">
+        <v>2843</v>
+      </c>
+      <c r="B999" s="4" t="s">
+        <v>2847</v>
+      </c>
+      <c r="C999" s="3" t="s">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1000" s="3" t="s">
+        <v>2844</v>
+      </c>
+      <c r="B1000" s="4" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1000" s="3" t="s">
+        <v>2840</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1001" s="3" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B1001" s="4" t="s">
+        <v>2849</v>
+      </c>
+      <c r="C1001" s="3" t="s">
+        <v>2841</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1002" s="3" t="s">
+        <v>2846</v>
+      </c>
+      <c r="B1002" s="4" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C1002" s="3" t="s">
+        <v>2842</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7692DDFA-9142-40B8-8CEE-3E964D8E4AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D15B135-4109-4A7E-97BF-EED3448B0DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4830" yWindow="130" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4850" yWindow="80" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3000" uniqueCount="2851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3003" uniqueCount="2854">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23842,6 +23842,16 @@
   <si>
     <t>放置圆</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DirectXInitializationFailed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Failed to initialize DirectX. Switching to DirectDraw rendering.</t>
+  </si>
+  <si>
+    <t>无法初始化DirectX，将切换至DirectDraw绘图。</t>
   </si>
 </sst>
 </file>
@@ -24244,7 +24254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1002"/>
+  <dimension ref="A1:D1003"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -35268,6 +35278,17 @@
         <v>2842</v>
       </c>
     </row>
+    <row r="1003" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1003" s="3" t="s">
+        <v>2851</v>
+      </c>
+      <c r="B1003" s="4" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C1003" s="3" t="s">
+        <v>2852</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA939036-2982-44DD-9ABE-6FBF23F96C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092BB862-CDAA-455B-A2E7-589EE623274B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4850" yWindow="80" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3006" uniqueCount="2857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="2860">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23650,13 +23650,6 @@
     <t>精确计算游戏对象间的深度关系（轻微影响性能）</t>
   </si>
   <si>
-    <t>使用 DirectX 11 (显卡) 绘图</t>
-  </si>
-  <si>
-    <t>Draw map using DirectX 11 (GPU)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Loading objects, please wait...</t>
   </si>
   <si>
@@ -23812,12 +23805,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Failed to initialize DirectX. Switching to DirectDraw rendering.</t>
-  </si>
-  <si>
-    <t>无法初始化DirectX，将切换至DirectDraw绘图。</t>
-  </si>
-  <si>
     <t>Enable dark mode (requires Auto-switch dark mode to be disabled)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -23846,6 +23833,28 @@
   <si>
     <t>启用高DPI感知时，使地图视图默认匹配系统缩放比例</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择渲染API (Y = OpenGL 3.3, N = Direct3D 11)</t>
+  </si>
+  <si>
+    <t>Options.OpenGLRendering</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set graphics API (Y = OpenGL 3.3, N = Direct3D 11)</t>
+  </si>
+  <si>
+    <t>Enable GPU-Accelerated Rendering (Recommended)</t>
+  </si>
+  <si>
+    <t>启用 GPU 加速绘图（推荐）</t>
+  </si>
+  <si>
+    <t>Failed to initialize rendering engine. Switching to DirectDraw (CPU) rendering.</t>
+  </si>
+  <si>
+    <t>无法初始化渲染引擎，将切换至DirectDraw (CPU)绘图。</t>
   </si>
 </sst>
 </file>
@@ -24248,7 +24257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1004"/>
+  <dimension ref="A1:D1005"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -32439,10 +32448,10 @@
         <v>754</v>
       </c>
       <c r="B746" s="4" t="s">
-        <v>2850</v>
+        <v>2846</v>
       </c>
       <c r="C746" s="3" t="s">
-        <v>2849</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.4">
@@ -35057,10 +35066,10 @@
         <v>2791</v>
       </c>
       <c r="B983" s="4" t="s">
-        <v>2801</v>
+        <v>2857</v>
       </c>
       <c r="C983" s="3" t="s">
-        <v>2802</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="984" spans="1:4" x14ac:dyDescent="0.4">
@@ -35098,65 +35107,65 @@
     </row>
     <row r="987" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A987" s="3" t="s">
-        <v>2804</v>
+        <v>2802</v>
       </c>
       <c r="B987" s="4" t="s">
-        <v>2807</v>
+        <v>2805</v>
       </c>
       <c r="C987" s="3" t="s">
-        <v>2803</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="988" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A988" s="3" t="s">
-        <v>2805</v>
+        <v>2803</v>
       </c>
       <c r="B988" s="4" t="s">
-        <v>2808</v>
+        <v>2806</v>
       </c>
       <c r="C988" s="3" t="s">
-        <v>2806</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="989" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A989" s="3" t="s">
-        <v>2811</v>
+        <v>2809</v>
       </c>
       <c r="B989" s="4" t="s">
-        <v>2812</v>
+        <v>2810</v>
       </c>
       <c r="C989" s="3" t="s">
-        <v>2809</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="990" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A990" s="3" t="s">
-        <v>2810</v>
+        <v>2808</v>
       </c>
       <c r="B990" s="4" t="s">
-        <v>2813</v>
+        <v>2811</v>
       </c>
       <c r="C990" s="3" t="s">
-        <v>2814</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="991" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A991" s="3" t="s">
-        <v>2817</v>
+        <v>2815</v>
       </c>
       <c r="B991" s="4" t="s">
-        <v>2816</v>
+        <v>2814</v>
       </c>
       <c r="C991" s="3" t="s">
-        <v>2815</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="992" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A992" s="3" t="s">
-        <v>2822</v>
+        <v>2820</v>
       </c>
       <c r="B992" s="4" t="s">
-        <v>2819</v>
+        <v>2817</v>
       </c>
       <c r="C992" s="3" t="s">
         <v>1218</v>
@@ -35164,21 +35173,21 @@
     </row>
     <row r="993" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A993" s="3" t="s">
-        <v>2818</v>
+        <v>2816</v>
       </c>
       <c r="B993" s="4" t="s">
+        <v>2819</v>
+      </c>
+      <c r="C993" s="3" t="s">
         <v>2821</v>
-      </c>
-      <c r="C993" s="3" t="s">
-        <v>2823</v>
       </c>
     </row>
     <row r="994" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A994" s="3" t="s">
-        <v>2824</v>
+        <v>2822</v>
       </c>
       <c r="B994" s="4" t="s">
-        <v>2820</v>
+        <v>2818</v>
       </c>
       <c r="C994" s="3" t="s">
         <v>1220</v>
@@ -35186,112 +35195,123 @@
     </row>
     <row r="995" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A995" s="3" t="s">
-        <v>2828</v>
+        <v>2826</v>
       </c>
       <c r="B995" s="4" t="s">
-        <v>2831</v>
+        <v>2829</v>
       </c>
       <c r="C995" s="3" t="s">
-        <v>2825</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="996" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A996" s="3" t="s">
-        <v>2829</v>
+        <v>2827</v>
       </c>
       <c r="B996" s="4" t="s">
-        <v>2832</v>
+        <v>2830</v>
       </c>
       <c r="C996" s="3" t="s">
-        <v>2826</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="997" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A997" s="3" t="s">
-        <v>2830</v>
+        <v>2828</v>
       </c>
       <c r="B997" s="4" t="s">
-        <v>2833</v>
+        <v>2831</v>
       </c>
       <c r="C997" s="3" t="s">
-        <v>2827</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="998" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A998" s="3" t="s">
-        <v>2838</v>
+        <v>2836</v>
       </c>
       <c r="B998" s="4" t="s">
-        <v>2842</v>
+        <v>2840</v>
       </c>
       <c r="C998" s="3" t="s">
-        <v>2834</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="999" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A999" s="3" t="s">
-        <v>2839</v>
+        <v>2837</v>
       </c>
       <c r="B999" s="4" t="s">
-        <v>2843</v>
+        <v>2841</v>
       </c>
       <c r="C999" s="3" t="s">
-        <v>2835</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="1000" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1000" s="3" t="s">
-        <v>2840</v>
+        <v>2838</v>
       </c>
       <c r="B1000" s="4" t="s">
-        <v>2844</v>
+        <v>2842</v>
       </c>
       <c r="C1000" s="3" t="s">
-        <v>2836</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="1001" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1001" s="3" t="s">
-        <v>2841</v>
+        <v>2839</v>
       </c>
       <c r="B1001" s="4" t="s">
-        <v>2845</v>
+        <v>2843</v>
       </c>
       <c r="C1001" s="3" t="s">
-        <v>2837</v>
-      </c>
-    </row>
-    <row r="1002" spans="1:3" x14ac:dyDescent="0.4">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A1002" s="3" t="s">
-        <v>2846</v>
+        <v>2844</v>
       </c>
       <c r="B1002" s="4" t="s">
-        <v>2848</v>
+        <v>2859</v>
       </c>
       <c r="C1002" s="3" t="s">
-        <v>2847</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1003" s="3" t="s">
+        <v>2847</v>
+      </c>
+      <c r="B1003" s="4" t="s">
         <v>2851</v>
       </c>
-      <c r="B1003" s="4" t="s">
-        <v>2855</v>
-      </c>
       <c r="C1003" s="3" t="s">
-        <v>2852</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="1004" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A1004" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="B1004" s="4" t="s">
+        <v>2852</v>
+      </c>
+      <c r="C1004" s="3" t="s">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1005" s="3" t="s">
+        <v>2854</v>
+      </c>
+      <c r="B1005" s="4" t="s">
         <v>2853</v>
       </c>
-      <c r="B1004" s="4" t="s">
-        <v>2856</v>
-      </c>
-      <c r="C1004" s="3" t="s">
-        <v>2854</v>
+      <c r="C1005" s="3" t="s">
+        <v>2855</v>
       </c>
     </row>
   </sheetData>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092BB862-CDAA-455B-A2E7-589EE623274B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCAA4D1-4CD1-4ED3-B2B4-B67B742BA791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4850" yWindow="80" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="2860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3012" uniqueCount="2863">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23855,6 +23855,16 @@
   </si>
   <si>
     <t>无法初始化渲染引擎，将切换至DirectDraw (CPU)绘图。</t>
+  </si>
+  <si>
+    <t>Options.ForceNeutralSpecialColor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在多人地图中，强制Neutral和Special所属方使用浅灰色</t>
+  </si>
+  <si>
+    <t>Force Neutral and Special houses to use the light gray color in skirmish</t>
   </si>
 </sst>
 </file>
@@ -24257,7 +24267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1005"/>
+  <dimension ref="A1:D1006"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -35314,6 +35324,17 @@
         <v>2855</v>
       </c>
     </row>
+    <row r="1006" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A1006" s="3" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B1006" s="4" t="s">
+        <v>2861</v>
+      </c>
+      <c r="C1006" s="3" t="s">
+        <v>2862</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCAA4D1-4CD1-4ED3-B2B4-B67B742BA791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090837AD-D8B6-4768-8C2C-EE460446507E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4850" yWindow="80" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3012" uniqueCount="2863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="2931">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -23865,6 +23865,210 @@
   </si>
   <si>
     <t>Force Neutral and Special houses to use the light gray color in skirmish</t>
+  </si>
+  <si>
+    <t>SpecialFlags.Title</t>
+  </si>
+  <si>
+    <t>Special Flags</t>
+  </si>
+  <si>
+    <t>SpecialFlags.TiberiumGrows</t>
+  </si>
+  <si>
+    <t>Tiberium grows</t>
+  </si>
+  <si>
+    <t>SpecialFlags.TiberiumSpreads</t>
+  </si>
+  <si>
+    <t>Tiberium spreads</t>
+  </si>
+  <si>
+    <t>SpecialFlags.TiberiumExplosive</t>
+  </si>
+  <si>
+    <t>Tiberium explosive</t>
+  </si>
+  <si>
+    <t>SpecialFlags.DestroyableBridges</t>
+  </si>
+  <si>
+    <t>Destroyable bridges</t>
+  </si>
+  <si>
+    <t>SpecialFlags.MCVDeploy</t>
+  </si>
+  <si>
+    <t>MCV deploy</t>
+  </si>
+  <si>
+    <t>SpecialFlags.InitialVeteran</t>
+  </si>
+  <si>
+    <t>Initial veteran (initial troops have veteran status)</t>
+  </si>
+  <si>
+    <t>SpecialFlags.FixedAlliance</t>
+  </si>
+  <si>
+    <t>Fixed alliance</t>
+  </si>
+  <si>
+    <t>SpecialFlags.HarvesterImmune</t>
+  </si>
+  <si>
+    <t>Harvester immune</t>
+  </si>
+  <si>
+    <t>SpecialFlags.FogOfWar</t>
+  </si>
+  <si>
+    <t>Fog of war</t>
+  </si>
+  <si>
+    <t>SpecialFlags.Inert</t>
+  </si>
+  <si>
+    <t>Inert</t>
+  </si>
+  <si>
+    <t>SpecialFlags.IonStorms</t>
+  </si>
+  <si>
+    <t>Ion storms</t>
+  </si>
+  <si>
+    <t>SpecialFlags.Meteorites</t>
+  </si>
+  <si>
+    <t>Meteorites</t>
+  </si>
+  <si>
+    <t>SpecialFlags.Visceroids</t>
+  </si>
+  <si>
+    <t>Visceroids</t>
+  </si>
+  <si>
+    <t>SpecialFlags.Note</t>
+  </si>
+  <si>
+    <t>Note: some of the settings are probably just ignored</t>
+  </si>
+  <si>
+    <t>BasicHomeCell</t>
+  </si>
+  <si>
+    <t>Home Cell:</t>
+  </si>
+  <si>
+    <t>BasicAltHomeCell</t>
+  </si>
+  <si>
+    <t>Alt. Home Cell:</t>
+  </si>
+  <si>
+    <t>BasicRepairBaseNodes</t>
+  </si>
+  <si>
+    <t>Repair Base Nodes (Phobos B45+)</t>
+  </si>
+  <si>
+    <t>BasicMCVRedeploys</t>
+  </si>
+  <si>
+    <t>MCV Redeploys (Phobos B34+)</t>
+  </si>
+  <si>
+    <t>BasicShowBriefing</t>
+  </si>
+  <si>
+    <t>Show Briefing (Phobos B39+):</t>
+  </si>
+  <si>
+    <t>BasicBriefingTheme</t>
+  </si>
+  <si>
+    <t>Briefing Theme (Phobos B39+):</t>
+  </si>
+  <si>
+    <t>BasicTitle</t>
+  </si>
+  <si>
+    <t>Basic settings</t>
+  </si>
+  <si>
+    <t>Singleplayer Map Settings</t>
+  </si>
+  <si>
+    <t>特定标识</t>
+  </si>
+  <si>
+    <t>矿石生长</t>
+  </si>
+  <si>
+    <t>矿石蔓延</t>
+  </si>
+  <si>
+    <t>矿石爆炸(无效)</t>
+  </si>
+  <si>
+    <t>可摧毁桥梁(不影响C4/伊文)</t>
+  </si>
+  <si>
+    <t>基地车部署(无效)</t>
+  </si>
+  <si>
+    <t>初始精英(遭遇战初始单位精英)</t>
+  </si>
+  <si>
+    <t>固定联盟</t>
+  </si>
+  <si>
+    <t>矿车无敌(无效)</t>
+  </si>
+  <si>
+    <t>战争迷雾(半透明)</t>
+  </si>
+  <si>
+    <t>惰性效果</t>
+  </si>
+  <si>
+    <t>离子风暴(无效)</t>
+  </si>
+  <si>
+    <t>陨石(无效)</t>
+  </si>
+  <si>
+    <t>器官兽(无效)</t>
+  </si>
+  <si>
+    <t>一些设置只在特定情况下生效。</t>
+  </si>
+  <si>
+    <t>起始位置:</t>
+  </si>
+  <si>
+    <t>支线起始位置:</t>
+  </si>
+  <si>
+    <t>修复基地节点 (Phobos B45+)</t>
+  </si>
+  <si>
+    <t>允许基地车重新部署 (Phobos B34+)</t>
+  </si>
+  <si>
+    <t>显示任务简报 (Phobos B39+)</t>
+  </si>
+  <si>
+    <t>简报背景音乐 (Phobos B39+):</t>
+  </si>
+  <si>
+    <t>基本设置</t>
+  </si>
+  <si>
+    <t>单人任务设置</t>
   </si>
 </sst>
 </file>
@@ -24267,7 +24471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1006"/>
+  <dimension ref="A1:D1029"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -35335,6 +35539,256 @@
         <v>2862</v>
       </c>
     </row>
+    <row r="1007" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1007" s="3" t="s">
+        <v>2863</v>
+      </c>
+      <c r="B1007" s="4" t="s">
+        <v>2908</v>
+      </c>
+      <c r="C1007" s="3" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1008" s="3" t="s">
+        <v>2865</v>
+      </c>
+      <c r="B1008" s="4" t="s">
+        <v>2909</v>
+      </c>
+      <c r="C1008" s="3" t="s">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1009" s="3" t="s">
+        <v>2867</v>
+      </c>
+      <c r="B1009" s="4" t="s">
+        <v>2910</v>
+      </c>
+      <c r="C1009" s="3" t="s">
+        <v>2868</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1010" s="3" t="s">
+        <v>2869</v>
+      </c>
+      <c r="B1010" s="4" t="s">
+        <v>2911</v>
+      </c>
+      <c r="C1010" s="3" t="s">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1011" s="3" t="s">
+        <v>2871</v>
+      </c>
+      <c r="B1011" s="4" t="s">
+        <v>2912</v>
+      </c>
+      <c r="C1011" s="3" t="s">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1012" s="3" t="s">
+        <v>2873</v>
+      </c>
+      <c r="B1012" s="4" t="s">
+        <v>2913</v>
+      </c>
+      <c r="C1012" s="3" t="s">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1013" s="3" t="s">
+        <v>2875</v>
+      </c>
+      <c r="B1013" s="4" t="s">
+        <v>2914</v>
+      </c>
+      <c r="C1013" s="3" t="s">
+        <v>2876</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1014" s="3" t="s">
+        <v>2877</v>
+      </c>
+      <c r="B1014" s="4" t="s">
+        <v>2915</v>
+      </c>
+      <c r="C1014" s="3" t="s">
+        <v>2878</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1015" s="3" t="s">
+        <v>2879</v>
+      </c>
+      <c r="B1015" s="4" t="s">
+        <v>2916</v>
+      </c>
+      <c r="C1015" s="3" t="s">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1016" s="3" t="s">
+        <v>2881</v>
+      </c>
+      <c r="B1016" s="4" t="s">
+        <v>2917</v>
+      </c>
+      <c r="C1016" s="3" t="s">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1017" s="3" t="s">
+        <v>2883</v>
+      </c>
+      <c r="B1017" s="4" t="s">
+        <v>2918</v>
+      </c>
+      <c r="C1017" s="3" t="s">
+        <v>2884</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1018" s="3" t="s">
+        <v>2885</v>
+      </c>
+      <c r="B1018" s="4" t="s">
+        <v>2919</v>
+      </c>
+      <c r="C1018" s="3" t="s">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1019" s="3" t="s">
+        <v>2887</v>
+      </c>
+      <c r="B1019" s="4" t="s">
+        <v>2920</v>
+      </c>
+      <c r="C1019" s="3" t="s">
+        <v>2888</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1020" s="3" t="s">
+        <v>2889</v>
+      </c>
+      <c r="B1020" s="4" t="s">
+        <v>2921</v>
+      </c>
+      <c r="C1020" s="3" t="s">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1021" s="3" t="s">
+        <v>2891</v>
+      </c>
+      <c r="B1021" s="4" t="s">
+        <v>2922</v>
+      </c>
+      <c r="C1021" s="3" t="s">
+        <v>2892</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1022" s="3" t="s">
+        <v>2893</v>
+      </c>
+      <c r="B1022" s="4" t="s">
+        <v>2923</v>
+      </c>
+      <c r="C1022" s="3" t="s">
+        <v>2894</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1023" s="3" t="s">
+        <v>2895</v>
+      </c>
+      <c r="B1023" s="4" t="s">
+        <v>2924</v>
+      </c>
+      <c r="C1023" s="3" t="s">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1024" s="3" t="s">
+        <v>2897</v>
+      </c>
+      <c r="B1024" s="4" t="s">
+        <v>2925</v>
+      </c>
+      <c r="C1024" s="3" t="s">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1025" s="3" t="s">
+        <v>2899</v>
+      </c>
+      <c r="B1025" s="4" t="s">
+        <v>2926</v>
+      </c>
+      <c r="C1025" s="3" t="s">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1026" s="3" t="s">
+        <v>2901</v>
+      </c>
+      <c r="B1026" s="4" t="s">
+        <v>2927</v>
+      </c>
+      <c r="C1026" s="3" t="s">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1027" s="3" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B1027" s="4" t="s">
+        <v>2928</v>
+      </c>
+      <c r="C1027" s="3" t="s">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1028" s="3" t="s">
+        <v>2905</v>
+      </c>
+      <c r="B1028" s="4" t="s">
+        <v>2929</v>
+      </c>
+      <c r="C1028" s="3" t="s">
+        <v>2906</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B1029" s="4" t="s">
+        <v>2930</v>
+      </c>
+      <c r="C1029" s="3" t="s">
+        <v>2907</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090837AD-D8B6-4768-8C2C-EE460446507E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72882206-FD5E-4991-B6B5-F38ECBBE5D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4850" yWindow="80" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="2931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3087" uniqueCount="2937">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24069,6 +24069,27 @@
   </si>
   <si>
     <t>单人任务设置</t>
+  </si>
+  <si>
+    <t>SingleplayerTitle</t>
+  </si>
+  <si>
+    <t>SearhReference.TagObject</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SearhReference.TagTag</t>
+  </si>
+  <si>
+    <t>Tag</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -24471,7 +24492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1029"/>
+  <dimension ref="A1:D1031"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -35782,11 +35803,36 @@
       </c>
     </row>
     <row r="1029" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1029" s="3" t="s">
+        <v>2931</v>
+      </c>
       <c r="B1029" s="4" t="s">
         <v>2930</v>
       </c>
       <c r="C1029" s="3" t="s">
         <v>2907</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1030" s="3" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B1030" s="4" t="s">
+        <v>2934</v>
+      </c>
+      <c r="C1030" s="3" t="s">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1031" s="3" t="s">
+        <v>2935</v>
+      </c>
+      <c r="B1031" s="4" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C1031" s="3" t="s">
+        <v>2936</v>
       </c>
     </row>
   </sheetData>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72882206-FD5E-4991-B6B5-F38ECBBE5D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE45B8C9-551D-4531-8B08-E523FC661A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4850" yWindow="80" windowWidth="24570" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4600" yWindow="550" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3087" uniqueCount="2937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="2940">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24090,6 +24090,15 @@
   <si>
     <t>Tag</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Make the arrangement of images in tileset browser more compact</t>
+  </si>
+  <si>
+    <t>Options.TileSetBrowserViewCompactArrange</t>
+  </si>
+  <si>
+    <t>紧凑排列地形浏览器的图像</t>
   </si>
 </sst>
 </file>
@@ -24492,7 +24501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1031"/>
+  <dimension ref="A1:D1032"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -35835,6 +35844,17 @@
         <v>2936</v>
       </c>
     </row>
+    <row r="1032" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A1032" s="3" t="s">
+        <v>2938</v>
+      </c>
+      <c r="B1032" s="4" t="s">
+        <v>2939</v>
+      </c>
+      <c r="C1032" s="3" t="s">
+        <v>2937</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE45B8C9-551D-4531-8B08-E523FC661A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095B1BC6-BA67-4814-B783-DDA7C4D930D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4600" yWindow="550" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="2940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3096" uniqueCount="2946">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24099,6 +24099,26 @@
   </si>
   <si>
     <t>紧凑排列地形浏览器的图像</t>
+  </si>
+  <si>
+    <t>SearhReference.AttachedTrigger</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attached Trigger</t>
+  </si>
+  <si>
+    <t>关联触发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SearchReferenceFollowActiveWindow</t>
+  </si>
+  <si>
+    <t>Follow active window</t>
+  </si>
+  <si>
+    <t>跟随活动窗口</t>
   </si>
 </sst>
 </file>
@@ -24501,7 +24521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1032"/>
+  <dimension ref="A1:D1034"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -35855,6 +35875,28 @@
         <v>2937</v>
       </c>
     </row>
+    <row r="1033" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1033" s="3" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B1033" s="4" t="s">
+        <v>2942</v>
+      </c>
+      <c r="C1033" s="3" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1034" s="3" t="s">
+        <v>2943</v>
+      </c>
+      <c r="B1034" s="4" t="s">
+        <v>2945</v>
+      </c>
+      <c r="C1034" s="3" t="s">
+        <v>2944</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095B1BC6-BA67-4814-B783-DDA7C4D930D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036CF52E-147E-49E3-A58C-94CF4C8631E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4600" yWindow="550" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3096" uniqueCount="2946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3099" uniqueCount="2949">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24119,6 +24119,16 @@
   </si>
   <si>
     <t>跟随活动窗口</t>
+  </si>
+  <si>
+    <t>Options.RecordBrushSizeHistory</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>记忆各操作的笔刷大小</t>
+  </si>
+  <si>
+    <t>Remember brush sizes for mouse commands</t>
   </si>
 </sst>
 </file>
@@ -24521,7 +24531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1034"/>
+  <dimension ref="A1:D1035"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -35897,6 +35907,17 @@
         <v>2944</v>
       </c>
     </row>
+    <row r="1035" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1035" s="3" t="s">
+        <v>2946</v>
+      </c>
+      <c r="B1035" s="4" t="s">
+        <v>2947</v>
+      </c>
+      <c r="C1035" s="3" t="s">
+        <v>2948</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036CF52E-147E-49E3-A58C-94CF4C8631E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8551E0D5-0D48-45F7-BF19-7E1C5DBF5343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4600" yWindow="550" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3099" uniqueCount="2949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3111" uniqueCount="2961">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24129,6 +24129,46 @@
   </si>
   <si>
     <t>Remember brush sizes for mouse commands</t>
+  </si>
+  <si>
+    <t>MoneyOnMap.MultiSelection.Riparius</t>
+  </si>
+  <si>
+    <t>MoneyOnMap.MultiSelection.Cruentus</t>
+  </si>
+  <si>
+    <t>MoneyOnMap.MultiSelection.Vinifera</t>
+  </si>
+  <si>
+    <t>MoneyOnMap.MultiSelection.Aboreus</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>, 金矿: %d</t>
+  </si>
+  <si>
+    <t>, 水晶: %d</t>
+  </si>
+  <si>
+    <t>, 矿石3: %d</t>
+  </si>
+  <si>
+    <t>, 矿石4: %d</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>, Ore: %d</t>
+  </si>
+  <si>
+    <t>, Gems: %d</t>
+  </si>
+  <si>
+    <t>, Ore 3: %d</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>, Ore 4: %d</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -24531,7 +24571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1035"/>
+  <dimension ref="A1:D1039"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -35918,6 +35958,50 @@
         <v>2948</v>
       </c>
     </row>
+    <row r="1036" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1036" s="3" t="s">
+        <v>2949</v>
+      </c>
+      <c r="B1036" s="4" t="s">
+        <v>2953</v>
+      </c>
+      <c r="C1036" s="3" t="s">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1037" s="3" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B1037" s="4" t="s">
+        <v>2954</v>
+      </c>
+      <c r="C1037" s="3" t="s">
+        <v>2958</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1038" s="3" t="s">
+        <v>2951</v>
+      </c>
+      <c r="B1038" s="4" t="s">
+        <v>2955</v>
+      </c>
+      <c r="C1038" s="3" t="s">
+        <v>2959</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1039" s="3" t="s">
+        <v>2952</v>
+      </c>
+      <c r="B1039" s="4" t="s">
+        <v>2956</v>
+      </c>
+      <c r="C1039" s="3" t="s">
+        <v>2960</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8551E0D5-0D48-45F7-BF19-7E1C5DBF5343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A5E0CB-3C6B-4C14-A699-AF8611AB6A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4600" yWindow="550" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3111" uniqueCount="2961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3114" uniqueCount="2964">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24169,6 +24169,16 @@
   <si>
     <t>, Ore 4: %d</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.MCP.Enable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enable MCP Server for LLMs</t>
+  </si>
+  <si>
+    <t>启用大语言模型的MCP服务器</t>
   </si>
 </sst>
 </file>
@@ -24571,7 +24581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1039"/>
+  <dimension ref="A1:D1040"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -36002,6 +36012,17 @@
         <v>2960</v>
       </c>
     </row>
+    <row r="1040" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1040" s="3" t="s">
+        <v>2961</v>
+      </c>
+      <c r="B1040" s="4" t="s">
+        <v>2963</v>
+      </c>
+      <c r="C1040" s="3" t="s">
+        <v>2962</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C20FC5-0993-4901-887D-BC8976C02360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A380B3C0-3BB4-4831-A2FD-5DAB15306D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4600" yWindow="550" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3114" uniqueCount="2964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3132" uniqueCount="2982">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24165,6 +24165,68 @@
   </si>
   <si>
     <t>TriggerNewShort</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicTheme</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景音乐:</t>
+  </si>
+  <si>
+    <t>BasicLoadingTheme</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加载界面背景音乐 (Ares 0.7+):</t>
+  </si>
+  <si>
+    <t>Theme:</t>
+  </si>
+  <si>
+    <t>Loading Theme (Ares 0.7+):</t>
+  </si>
+  <si>
+    <t>RandomTreeDisguiseDesc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set mirage disguise trees</t>
+  </si>
+  <si>
+    <t>RandomTreeDisguiseTitle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mirage disguise trees</t>
+  </si>
+  <si>
+    <t>选择幻影伪装的树木</t>
+  </si>
+  <si>
+    <t>幻影伪装树木</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomTreeTitle</t>
+  </si>
+  <si>
+    <t>RandomTreeDesc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请选择准备放置的树木</t>
+  </si>
+  <si>
+    <t>绘制随机树木</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Please select the trees that shall be placed</t>
+  </si>
+  <si>
+    <t>Random Tree Placing</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -24568,7 +24630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1040"/>
+  <dimension ref="A1:D1046"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -36010,6 +36072,72 @@
         <v>2959</v>
       </c>
     </row>
+    <row r="1041" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1041" s="3" t="s">
+        <v>2964</v>
+      </c>
+      <c r="B1041" s="4" t="s">
+        <v>2965</v>
+      </c>
+      <c r="C1041" s="3" t="s">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1042" s="3" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B1042" s="4" t="s">
+        <v>2967</v>
+      </c>
+      <c r="C1042" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1043" s="3" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1043" s="4" t="s">
+        <v>2974</v>
+      </c>
+      <c r="C1043" s="3" t="s">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1044" s="3" t="s">
+        <v>2972</v>
+      </c>
+      <c r="B1044" s="4" t="s">
+        <v>2975</v>
+      </c>
+      <c r="C1044" s="3" t="s">
+        <v>2973</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1045" s="3" t="s">
+        <v>2976</v>
+      </c>
+      <c r="B1045" s="4" t="s">
+        <v>2979</v>
+      </c>
+      <c r="C1045" s="3" t="s">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1046" s="3" t="s">
+        <v>2977</v>
+      </c>
+      <c r="B1046" s="4" t="s">
+        <v>2978</v>
+      </c>
+      <c r="C1046" s="3" t="s">
+        <v>2980</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A380B3C0-3BB4-4831-A2FD-5DAB15306D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA18F3C9-096B-458A-AF2B-3DA2EB1EB14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4600" yWindow="550" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3132" uniqueCount="2982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="2985">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24228,6 +24228,16 @@
   <si>
     <t>Random Tree Placing</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.AttachedTriggerIsSelfCheck</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Check whether attached trigger is itself</t>
+  </si>
+  <si>
+    <t>检查下级触发是否是自身</t>
   </si>
 </sst>
 </file>
@@ -24630,7 +24640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1046"/>
+  <dimension ref="A1:D1047"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -36138,6 +36148,17 @@
         <v>2980</v>
       </c>
     </row>
+    <row r="1047" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1047" s="3" t="s">
+        <v>2982</v>
+      </c>
+      <c r="B1047" s="4" t="s">
+        <v>2984</v>
+      </c>
+      <c r="C1047" s="3" t="s">
+        <v>2983</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA18F3C9-096B-458A-AF2B-3DA2EB1EB14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F555862-A8E0-4BEF-A41D-B5095E92DB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="2985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3147" uniqueCount="2997">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24238,6 +24238,46 @@
   </si>
   <si>
     <t>检查下级触发是否是自身</t>
+  </si>
+  <si>
+    <t>LuaHighRisk.Header</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The following high-risk operations were detected in the script:</t>
+  </si>
+  <si>
+    <t>LuaHighRisk.Footer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Are you sure you want to continue?</t>
+  </si>
+  <si>
+    <t>LuaHighRisk.Title</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>High-Risk Operation Confirmation</t>
+  </si>
+  <si>
+    <t>脚本中包含下列高危操作：</t>
+  </si>
+  <si>
+    <t>确认要执行吗？</t>
+  </si>
+  <si>
+    <t>高危操作确认</t>
+  </si>
+  <si>
+    <t>Options.DisableLuaConsoleSafetyCheck</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disable Lua console safety check</t>
+  </si>
+  <si>
+    <t>禁用Lua脚本安全检查</t>
   </si>
 </sst>
 </file>
@@ -24640,7 +24680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1047"/>
+  <dimension ref="A1:D1051"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -36159,6 +36199,50 @@
         <v>2983</v>
       </c>
     </row>
+    <row r="1048" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1048" s="3" t="s">
+        <v>2985</v>
+      </c>
+      <c r="B1048" s="4" t="s">
+        <v>2991</v>
+      </c>
+      <c r="C1048" s="3" t="s">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1049" s="3" t="s">
+        <v>2987</v>
+      </c>
+      <c r="B1049" s="4" t="s">
+        <v>2992</v>
+      </c>
+      <c r="C1049" s="3" t="s">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1050" s="3" t="s">
+        <v>2989</v>
+      </c>
+      <c r="B1050" s="4" t="s">
+        <v>2993</v>
+      </c>
+      <c r="C1050" s="3" t="s">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1051" s="3" t="s">
+        <v>2994</v>
+      </c>
+      <c r="B1051" s="4" t="s">
+        <v>2996</v>
+      </c>
+      <c r="C1051" s="3" t="s">
+        <v>2995</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F555862-A8E0-4BEF-A41D-B5095E92DB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760232C2-597E-4569-B7A5-C9107E39DBF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3147" uniqueCount="2997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3150" uniqueCount="3000">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24278,6 +24278,16 @@
   </si>
   <si>
     <t>禁用Lua脚本安全检查</t>
+  </si>
+  <si>
+    <t>Options.TileSetBrowserFloating</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将地形浏览器作为独立窗口显示</t>
+  </si>
+  <si>
+    <t>Tile browser as floating window</t>
   </si>
 </sst>
 </file>
@@ -24680,7 +24690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1051"/>
+  <dimension ref="A1:D1052"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -36243,6 +36253,17 @@
         <v>2995</v>
       </c>
     </row>
+    <row r="1052" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1052" s="3" t="s">
+        <v>2997</v>
+      </c>
+      <c r="B1052" s="4" t="s">
+        <v>2998</v>
+      </c>
+      <c r="C1052" s="3" t="s">
+        <v>2999</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760232C2-597E-4569-B7A5-C9107E39DBF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7A2D7E-4F79-4374-9AD7-98A9E9388006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3150" uniqueCount="3000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="3003">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24288,6 +24288,16 @@
   </si>
   <si>
     <t>Tile browser as floating window</t>
+  </si>
+  <si>
+    <t>Options.ViewObjectsFloating</t>
+  </si>
+  <si>
+    <t>Object browser as floating window</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将物品浏览器作为独立窗口显示</t>
   </si>
 </sst>
 </file>
@@ -24690,7 +24700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1052"/>
+  <dimension ref="A1:D1053"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -36264,6 +36274,17 @@
         <v>2999</v>
       </c>
     </row>
+    <row r="1053" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1053" s="3" t="s">
+        <v>3000</v>
+      </c>
+      <c r="B1053" s="4" t="s">
+        <v>3002</v>
+      </c>
+      <c r="C1053" s="3" t="s">
+        <v>3001</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7A2D7E-4F79-4374-9AD7-98A9E9388006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148763F4-196A-481F-881A-9A09FB568B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="3003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3165" uniqueCount="3015">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24298,6 +24298,45 @@
   </si>
   <si>
     <t>将物品浏览器作为独立窗口显示</t>
+  </si>
+  <si>
+    <t>TransparencyMenu.75</t>
+  </si>
+  <si>
+    <t>TransparencyMenu.50</t>
+  </si>
+  <si>
+    <t>TransparencyMenu.25</t>
+  </si>
+  <si>
+    <t>TransparencyMenu.100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻度透明(75%)</t>
+  </si>
+  <si>
+    <t>半透明(50%)</t>
+  </si>
+  <si>
+    <t>高度透明(25%)</t>
+  </si>
+  <si>
+    <t>不透明(100%)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>75% Opacity</t>
+  </si>
+  <si>
+    <t>50% Opacity</t>
+  </si>
+  <si>
+    <t>25% Opacity</t>
+  </si>
+  <si>
+    <t>Opaque (100%)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -24700,7 +24739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1053"/>
+  <dimension ref="A1:D1057"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -36285,6 +36324,50 @@
         <v>3001</v>
       </c>
     </row>
+    <row r="1054" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1054" s="3" t="s">
+        <v>3006</v>
+      </c>
+      <c r="B1054" s="4" t="s">
+        <v>3010</v>
+      </c>
+      <c r="C1054" s="3" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1055" s="3" t="s">
+        <v>3003</v>
+      </c>
+      <c r="B1055" s="4" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C1055" s="3" t="s">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1056" s="3" t="s">
+        <v>3004</v>
+      </c>
+      <c r="B1056" s="4" t="s">
+        <v>3008</v>
+      </c>
+      <c r="C1056" s="3" t="s">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1057" s="3" t="s">
+        <v>3005</v>
+      </c>
+      <c r="B1057" s="4" t="s">
+        <v>3009</v>
+      </c>
+      <c r="C1057" s="3" t="s">
+        <v>3013</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148763F4-196A-481F-881A-9A09FB568B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC64607-B989-4976-A10B-79D51F6CAE7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3165" uniqueCount="3015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3168" uniqueCount="3018">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24336,6 +24336,18 @@
   </si>
   <si>
     <t>Opaque (100%)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全透明(1%)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1% Opacity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TransparencyMenu.1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -24739,7 +24751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1057"/>
+  <dimension ref="A1:D1058"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -36368,6 +36380,17 @@
         <v>3013</v>
       </c>
     </row>
+    <row r="1058" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1058" s="3" t="s">
+        <v>3017</v>
+      </c>
+      <c r="B1058" s="4" t="s">
+        <v>3015</v>
+      </c>
+      <c r="C1058" s="3" t="s">
+        <v>3016</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654124E5-06C4-48C9-BFDF-EEE43CDCBD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67810AE-26E7-4EC5-8851-9A88A1B28213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="490" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24200,18 +24200,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Shift: Steep slope, Ctrl+Shift:  Ignore non-morphable tiles, A: Switch vertex mode, Up/Down: Raise/lower tile</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Ctrl: 抬升/降低同类地表（非顶点模式），Shift: 陡峭斜面，Ctrl+Shift: 无视不可抬升/降低地形，A：切换顶点模式</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Shift: 陡峭斜面，Ctrl+Shift: 无视不可抬升/降低地形，A：切换顶点模式，Up/Down：抬升或降低地表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>VertexModeOn</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -24237,6 +24229,14 @@
   </si>
   <si>
     <t>Zoom: %.02fx, middle-click to reset</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shift: 陡峭斜面，Ctrl+Shift: 无视不可抬升/降低地形，A：切换顶点模式，Up/Down/滚轮：抬升或降低地表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shift: Steep slope, Ctrl+Shift:  Ignore non-morphable tiles, A: Switch vertex mode, Up/Down/Mouse wheel: Raise/lower tile</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -25981,7 +25981,7 @@
         <v>116</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>3013</v>
@@ -25992,10 +25992,10 @@
         <v>117</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>3016</v>
+        <v>3022</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>3014</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.4">
@@ -32977,7 +32977,7 @@
         <v>2570</v>
       </c>
       <c r="C759" s="3" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.4">
@@ -36282,24 +36282,24 @@
     </row>
     <row r="1059" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1059" s="3" t="s">
+        <v>3015</v>
+      </c>
+      <c r="B1059" s="4" t="s">
+        <v>3016</v>
+      </c>
+      <c r="C1059" s="3" t="s">
         <v>3017</v>
-      </c>
-      <c r="B1059" s="4" t="s">
-        <v>3018</v>
-      </c>
-      <c r="C1059" s="3" t="s">
-        <v>3019</v>
       </c>
     </row>
     <row r="1060" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1060" s="3" t="s">
+        <v>3018</v>
+      </c>
+      <c r="B1060" s="4" t="s">
+        <v>3019</v>
+      </c>
+      <c r="C1060" s="3" t="s">
         <v>3020</v>
-      </c>
-      <c r="B1060" s="4" t="s">
-        <v>3021</v>
-      </c>
-      <c r="C1060" s="3" t="s">
-        <v>3022</v>
       </c>
     </row>
   </sheetData>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBCCEA2E-60F4-4C5E-8710-32289E6292A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEC31C2-FEAD-4818-8405-3C87E0CAF4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="490" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3168" uniqueCount="3017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="3020">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24049,6 +24049,15 @@
   </si>
   <si>
     <t>避让不可抬升地形</t>
+  </si>
+  <si>
+    <t>Options.ReloadIniWhenOpeningMap</t>
+  </si>
+  <si>
+    <t>Reload game INIs when opening map file</t>
+  </si>
+  <si>
+    <t>打开地图时重新加载游戏ini</t>
   </si>
 </sst>
 </file>
@@ -24451,7 +24460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1058"/>
+  <dimension ref="A1:D1059"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -36091,6 +36100,17 @@
         <v>3015</v>
       </c>
     </row>
+    <row r="1059" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1059" s="3" t="s">
+        <v>3017</v>
+      </c>
+      <c r="B1059" s="4" t="s">
+        <v>3019</v>
+      </c>
+      <c r="C1059" s="3" t="s">
+        <v>3018</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEC31C2-FEAD-4818-8405-3C87E0CAF4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9731764A-2BE7-4C1F-B37E-B5D422BD4393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="490" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="3020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3177" uniqueCount="3026">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24058,6 +24058,26 @@
   </si>
   <si>
     <t>打开地图时重新加载游戏ini</t>
+  </si>
+  <si>
+    <t>ReloadMapConfirmTitle</t>
+  </si>
+  <si>
+    <t>ReloadMapConfirmMessage</t>
+  </si>
+  <si>
+    <t>Reload Map Confirm</t>
+  </si>
+  <si>
+    <t>Are you sure you want to reload the map?</t>
+  </si>
+  <si>
+    <t>重载地图确认</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>确认要重新加载地图吗？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -24460,7 +24480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1059"/>
+  <dimension ref="A1:D1061"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -36111,6 +36131,28 @@
         <v>3018</v>
       </c>
     </row>
+    <row r="1060" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1060" s="3" t="s">
+        <v>3020</v>
+      </c>
+      <c r="B1060" s="4" t="s">
+        <v>3024</v>
+      </c>
+      <c r="C1060" s="3" t="s">
+        <v>3022</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1061" s="3" t="s">
+        <v>3021</v>
+      </c>
+      <c r="B1061" s="4" t="s">
+        <v>3025</v>
+      </c>
+      <c r="C1061" s="3" t="s">
+        <v>3023</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAF02AA-55C0-40BB-80C1-060BC4BB9283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53053490-3FF0-465F-B240-510F7DBF2BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5120" yWindow="2710" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1160" yWindow="1460" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3273" uniqueCount="3112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3291" uniqueCount="3130">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24316,6 +24316,67 @@
   <si>
     <t>生命值 (%)</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不使用本逻辑</t>
+  </si>
+  <si>
+    <t>设为不可重组</t>
+  </si>
+  <si>
+    <t>设为可重组</t>
+  </si>
+  <si>
+    <t>SetRecruitOnLiber.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetRecruitOnLiber.0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetRecruitOnLiber.-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解散重组:</t>
+  </si>
+  <si>
+    <t>TeamTypesTooltipSetRecruitOnLiber</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TeamTypesLabelSetRecruitOnLiber</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Phobos v0.5-alpha+) 在原版游戏中，当单位被加入到小队中时，其 RecruitableB 字段会被小队的设置 AreTeamMembersRecruitable 覆写。单位被小队释放时，该字段也不会被恢复。本设置允许小队在释放时重新设置该字段。默认为 [General]-&gt;SetRecruitableOnLiberate。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Don't use this logic</t>
+  </si>
+  <si>
+    <t>Marked as not recruitable</t>
+  </si>
+  <si>
+    <t>Marked as recruitable</t>
+  </si>
+  <si>
+    <t>Rec/Lib:</t>
+  </si>
+  <si>
+    <t>Phobos v0.5-alpha+) In vanilla, when a unit is added to a team, its RecruitableB flag is overwritten by the team's AreTeamMembersRecruitable setting. When the unit is liberated from the team, the flag is not restored. This setting allows a team to reset this flag when liberating its members. Default [General]-&gt;SetRecruitableOnLiberate.</t>
+  </si>
+  <si>
+    <t>LocalVariablesAltTooltip</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Phobos v0.5-alpha+) Using [Basic]-&gt;SkipMapSelect=yes in the map file allows you to bypass the restriction in mapselmd.ini-which requires that the player's faction in the current campaign must match the faction in the next new campaign.\nYou can use NextScenario and AltNextScenario to specify the map names required to enter a new campaign, thereby forcing the game to proceed to the next campaign.\nSetting a local variable named &lt;Alternate Next Scenario&gt; will also trigger AltNextScenario.</t>
+  </si>
+  <si>
+    <t>(Phobos v0.5-alpha+) 在地图文件中使用 [Basic]-&gt;SkipMapSelect=yes （跳过地图选择）可以绕过 mapselmd.ini中的限制——该限制要求当前战役中玩家所属的阵营必须与下一个新战役中的阵营一致。\n你可以使用 NextScenari（下一主线剧情）和 AltNextScenario （下一支线剧情）来指定进入新战役所需的地图名称强制游戏进入下一个战役。\n启用一个名为 &lt;Alternate Next Scenario&gt; 的局部变量也可以触发 AltNextScenario。</t>
   </si>
 </sst>
 </file>
@@ -24733,7 +24794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1093"/>
+  <dimension ref="A1:D1099"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -36758,6 +36819,72 @@
         <v>3109</v>
       </c>
     </row>
+    <row r="1094" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1094" s="3" t="s">
+        <v>3117</v>
+      </c>
+      <c r="B1094" s="4" t="s">
+        <v>3112</v>
+      </c>
+      <c r="C1094" s="3" t="s">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1095" s="3" t="s">
+        <v>3116</v>
+      </c>
+      <c r="B1095" s="4" t="s">
+        <v>3113</v>
+      </c>
+      <c r="C1095" s="3" t="s">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1096" s="3" t="s">
+        <v>3115</v>
+      </c>
+      <c r="B1096" s="4" t="s">
+        <v>3114</v>
+      </c>
+      <c r="C1096" s="3" t="s">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1097" s="3" t="s">
+        <v>3120</v>
+      </c>
+      <c r="B1097" s="4" t="s">
+        <v>3118</v>
+      </c>
+      <c r="C1097" s="3" t="s">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:3" ht="112" x14ac:dyDescent="0.4">
+      <c r="A1098" s="3" t="s">
+        <v>3119</v>
+      </c>
+      <c r="B1098" s="4" t="s">
+        <v>3121</v>
+      </c>
+      <c r="C1098" s="3" t="s">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:3" ht="152" x14ac:dyDescent="0.4">
+      <c r="A1099" s="3" t="s">
+        <v>3127</v>
+      </c>
+      <c r="B1099" s="4" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1099" s="3" t="s">
+        <v>3128</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53053490-3FF0-465F-B240-510F7DBF2BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1FAFCD-3D14-4A99-B6D3-029D35D01E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="1460" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3291" uniqueCount="3130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3327" uniqueCount="3165">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24377,6 +24377,126 @@
   </si>
   <si>
     <t>(Phobos v0.5-alpha+) 在地图文件中使用 [Basic]-&gt;SkipMapSelect=yes （跳过地图选择）可以绕过 mapselmd.ini中的限制——该限制要求当前战役中玩家所属的阵营必须与下一个新战役中的阵营一致。\n你可以使用 NextScenari（下一主线剧情）和 AltNextScenario （下一支线剧情）来指定进入新战役所需的地图名称强制游戏进入下一个战役。\n启用一个名为 &lt;Alternate Next Scenario&gt; 的局部变量也可以触发 AltNextScenario。</t>
+  </si>
+  <si>
+    <t>寻路距离</t>
+  </si>
+  <si>
+    <t>寻路测距</t>
+  </si>
+  <si>
+    <t>寻路类型:</t>
+  </si>
+  <si>
+    <t>MeasurementToolbox.MovementZone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.PathDistanceGroup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.PathDistance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.DestructibleOverlay</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.DestructibleUnits</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可摧毁\n单位</t>
+  </si>
+  <si>
+    <t>可摧毁\n覆盖物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.ClearPathDistance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除路径</t>
+  </si>
+  <si>
+    <t>MeasurementToolbox.PathType.NormalLand</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.PathType.NormalSea</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.PathType.NormalAmphibian</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陆地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>海面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>两栖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>火车</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.PathType.Train</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Path Distance</t>
+  </si>
+  <si>
+    <t>MovementZone:</t>
+  </si>
+  <si>
+    <t>Destructible\nOverlay</t>
+  </si>
+  <si>
+    <t>Destructible\nUnits</t>
+  </si>
+  <si>
+    <t>Clear Paths</t>
+  </si>
+  <si>
+    <t>Land</t>
+  </si>
+  <si>
+    <t>Sea</t>
+  </si>
+  <si>
+    <t>Amphibian</t>
+  </si>
+  <si>
+    <t>Train</t>
+  </si>
+  <si>
+    <t>DistanceRuler.PathDistance</t>
+  </si>
+  <si>
+    <t>DistanceRuler.PathUnreachable</t>
+  </si>
+  <si>
+    <t>寻路距离: %s</t>
+  </si>
+  <si>
+    <t>寻路距离: 无法到达</t>
+  </si>
+  <si>
+    <t>Path Distance: %s</t>
+  </si>
+  <si>
+    <t>Path Distance: Unreachable</t>
   </si>
 </sst>
 </file>
@@ -24794,7 +24914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1099"/>
+  <dimension ref="A1:D1111"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -36863,7 +36983,7 @@
         <v>3125</v>
       </c>
     </row>
-    <row r="1098" spans="1:3" ht="112" x14ac:dyDescent="0.4">
+    <row r="1098" spans="1:3" ht="114" x14ac:dyDescent="0.4">
       <c r="A1098" s="3" t="s">
         <v>3119</v>
       </c>
@@ -36883,6 +37003,138 @@
       </c>
       <c r="C1099" s="3" t="s">
         <v>3128</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1100" s="3" t="s">
+        <v>3135</v>
+      </c>
+      <c r="B1100" s="4" t="s">
+        <v>3130</v>
+      </c>
+      <c r="C1100" s="3" t="s">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1101" s="3" t="s">
+        <v>3134</v>
+      </c>
+      <c r="B1101" s="4" t="s">
+        <v>3131</v>
+      </c>
+      <c r="C1101" s="3" t="s">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1102" s="3" t="s">
+        <v>3133</v>
+      </c>
+      <c r="B1102" s="4" t="s">
+        <v>3132</v>
+      </c>
+      <c r="C1102" s="3" t="s">
+        <v>3151</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1103" s="3" t="s">
+        <v>3136</v>
+      </c>
+      <c r="B1103" s="4" t="s">
+        <v>3139</v>
+      </c>
+      <c r="C1103" s="3" t="s">
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1104" s="3" t="s">
+        <v>3137</v>
+      </c>
+      <c r="B1104" s="4" t="s">
+        <v>3138</v>
+      </c>
+      <c r="C1104" s="3" t="s">
+        <v>3153</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1105" s="3" t="s">
+        <v>3140</v>
+      </c>
+      <c r="B1105" s="4" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1105" s="3" t="s">
+        <v>3154</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A1106" s="3" t="s">
+        <v>3142</v>
+      </c>
+      <c r="B1106" s="4" t="s">
+        <v>3145</v>
+      </c>
+      <c r="C1106" s="3" t="s">
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A1107" s="3" t="s">
+        <v>3143</v>
+      </c>
+      <c r="B1107" s="4" t="s">
+        <v>3146</v>
+      </c>
+      <c r="C1107" s="3" t="s">
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A1108" s="3" t="s">
+        <v>3144</v>
+      </c>
+      <c r="B1108" s="4" t="s">
+        <v>3147</v>
+      </c>
+      <c r="C1108" s="3" t="s">
+        <v>3157</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1109" s="3" t="s">
+        <v>3149</v>
+      </c>
+      <c r="B1109" s="4" t="s">
+        <v>3148</v>
+      </c>
+      <c r="C1109" s="3" t="s">
+        <v>3158</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1110" s="3" t="s">
+        <v>3159</v>
+      </c>
+      <c r="B1110" s="4" t="s">
+        <v>3161</v>
+      </c>
+      <c r="C1110" s="3" t="s">
+        <v>3163</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1111" s="3" t="s">
+        <v>3160</v>
+      </c>
+      <c r="B1111" s="4" t="s">
+        <v>3162</v>
+      </c>
+      <c r="C1111" s="3" t="s">
+        <v>3164</v>
       </c>
     </row>
   </sheetData>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1FAFCD-3D14-4A99-B6D3-029D35D01E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9DD319-6313-4056-9D66-DFFD9FF4ADF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="1460" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13130" yWindow="580" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3327" uniqueCount="3165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3354" uniqueCount="3192">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24497,6 +24497,88 @@
   </si>
   <si>
     <t>Path Distance: Unreachable</t>
+  </si>
+  <si>
+    <t>Options.ConfirmDelete.SubEntries</t>
+  </si>
+  <si>
+    <t>删除触发/脚本等的子条目时需要确认</t>
+  </si>
+  <si>
+    <t>TriggerDelEventWarn</t>
+  </si>
+  <si>
+    <t>确认要删除此触发中选中的事件吗？</t>
+  </si>
+  <si>
+    <t>TriggerDelEventTitle</t>
+  </si>
+  <si>
+    <t>删除触发事件</t>
+  </si>
+  <si>
+    <t>TriggerDelActionWarn</t>
+  </si>
+  <si>
+    <t>确认要删除此触发中选中的行为吗？</t>
+  </si>
+  <si>
+    <t>TriggerDelActionTitle</t>
+  </si>
+  <si>
+    <t>删除触发行为</t>
+  </si>
+  <si>
+    <t>ScriptDelActionWarn</t>
+  </si>
+  <si>
+    <t>确认要删除此脚本中选中的行为吗？</t>
+  </si>
+  <si>
+    <t>ScriptDelActionTitle</t>
+  </si>
+  <si>
+    <t>删除脚本行为</t>
+  </si>
+  <si>
+    <t>TaskforceDelUnitWarn</t>
+  </si>
+  <si>
+    <t>确认要删除该特遣部队中选中的单位吗？</t>
+  </si>
+  <si>
+    <t>TaskforceDelUnitTitle</t>
+  </si>
+  <si>
+    <t>删除特遣部队单位</t>
+  </si>
+  <si>
+    <t>Are you sure to delete the selected event(s) from this trigger?</t>
+  </si>
+  <si>
+    <t>Delete Trigger Event</t>
+  </si>
+  <si>
+    <t>Are you sure to delete the selected action(s) from this trigger?</t>
+  </si>
+  <si>
+    <t>Delete Trigger Action</t>
+  </si>
+  <si>
+    <t>Are you sure to delete the selected action(s) from this script?</t>
+  </si>
+  <si>
+    <t>Delete Script Action</t>
+  </si>
+  <si>
+    <t>Are you sure to delete the selected unit from this task force?</t>
+  </si>
+  <si>
+    <t>Delete Task Force Unit</t>
+  </si>
+  <si>
+    <t>Ask for confirmation when deleting sub-entries of triggers/scripts, etc.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -24914,7 +24996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1111"/>
+  <dimension ref="A1:D1120"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -37137,6 +37219,105 @@
         <v>3164</v>
       </c>
     </row>
+    <row r="1112" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A1112" s="3" t="s">
+        <v>3165</v>
+      </c>
+      <c r="B1112" s="4" t="s">
+        <v>3166</v>
+      </c>
+      <c r="C1112" s="3" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1113" s="3" t="s">
+        <v>3167</v>
+      </c>
+      <c r="B1113" s="4" t="s">
+        <v>3168</v>
+      </c>
+      <c r="C1113" s="3" t="s">
+        <v>3183</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1114" s="3" t="s">
+        <v>3169</v>
+      </c>
+      <c r="B1114" s="4" t="s">
+        <v>3170</v>
+      </c>
+      <c r="C1114" s="3" t="s">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1115" s="3" t="s">
+        <v>3171</v>
+      </c>
+      <c r="B1115" s="4" t="s">
+        <v>3172</v>
+      </c>
+      <c r="C1115" s="3" t="s">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1116" s="3" t="s">
+        <v>3173</v>
+      </c>
+      <c r="B1116" s="4" t="s">
+        <v>3174</v>
+      </c>
+      <c r="C1116" s="3" t="s">
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1117" s="3" t="s">
+        <v>3175</v>
+      </c>
+      <c r="B1117" s="4" t="s">
+        <v>3176</v>
+      </c>
+      <c r="C1117" s="3" t="s">
+        <v>3187</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1118" s="3" t="s">
+        <v>3177</v>
+      </c>
+      <c r="B1118" s="4" t="s">
+        <v>3178</v>
+      </c>
+      <c r="C1118" s="3" t="s">
+        <v>3188</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1119" s="3" t="s">
+        <v>3179</v>
+      </c>
+      <c r="B1119" s="4" t="s">
+        <v>3180</v>
+      </c>
+      <c r="C1119" s="3" t="s">
+        <v>3189</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1120" s="3" t="s">
+        <v>3181</v>
+      </c>
+      <c r="B1120" s="4" t="s">
+        <v>3182</v>
+      </c>
+      <c r="C1120" s="3" t="s">
+        <v>3190</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9DD319-6313-4056-9D66-DFFD9FF4ADF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A23FD4-2FBF-4A21-8DAC-E1585B94044A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13130" yWindow="580" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3020" yWindow="760" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3354" uniqueCount="3192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3360" uniqueCount="3198">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24578,6 +24578,28 @@
   </si>
   <si>
     <t>Ask for confirmation when deleting sub-entries of triggers/scripts, etc.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BatchConnectOff</t>
+  </si>
+  <si>
+    <t>BatchConnectOn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BatchConnect: On, press 'A' to switch</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BatchConnect: Off, press 'A' to switch</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>批量连接：开，按A键切换</t>
+  </si>
+  <si>
+    <t>批量连接：关，按A键切换</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -24996,7 +25018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1120"/>
+  <dimension ref="A1:D1122"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -37318,6 +37340,28 @@
         <v>3190</v>
       </c>
     </row>
+    <row r="1121" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1121" s="3" t="s">
+        <v>3193</v>
+      </c>
+      <c r="B1121" s="4" t="s">
+        <v>3196</v>
+      </c>
+      <c r="C1121" s="3" t="s">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1122" s="3" t="s">
+        <v>3192</v>
+      </c>
+      <c r="B1122" s="4" t="s">
+        <v>3197</v>
+      </c>
+      <c r="C1122" s="3" t="s">
+        <v>3195</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A23FD4-2FBF-4A21-8DAC-E1585B94044A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03CA23D-C1C8-4BC1-AA3E-BEC972BC03EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3020" yWindow="760" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3360" uniqueCount="3198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3369" uniqueCount="3203">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24385,13 +24385,6 @@
     <t>寻路测距</t>
   </si>
   <si>
-    <t>寻路类型:</t>
-  </si>
-  <si>
-    <t>MeasurementToolbox.MovementZone</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>MeasurementToolbox.PathDistanceGroup</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -24400,21 +24393,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>MeasurementToolbox.DestructibleOverlay</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MeasurementToolbox.DestructibleUnits</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>可摧毁\n单位</t>
-  </si>
-  <si>
-    <t>可摧毁\n覆盖物</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>MeasurementToolbox.ClearPathDistance</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -24457,15 +24435,6 @@
     <t>Path Distance</t>
   </si>
   <si>
-    <t>MovementZone:</t>
-  </si>
-  <si>
-    <t>Destructible\nOverlay</t>
-  </si>
-  <si>
-    <t>Destructible\nUnits</t>
-  </si>
-  <si>
     <t>Clear Paths</t>
   </si>
   <si>
@@ -24600,6 +24569,56 @@
   </si>
   <si>
     <t>批量连接：关，按A键切换</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.SubjectToText</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>受阻碍：</t>
+  </si>
+  <si>
+    <t>覆盖物</t>
+  </si>
+  <si>
+    <t>MeasurementToolbox.SubjectToBuilding</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.SubjectToTree</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>树木</t>
+  </si>
+  <si>
+    <t>Subject to:</t>
+  </si>
+  <si>
+    <t>Overlay</t>
+  </si>
+  <si>
+    <t>Tree</t>
+  </si>
+  <si>
+    <t>MeasurementToolbox.SubjectToOverlay</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.PathObjectType.Vehicle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeasurementToolbox.PathObjectType.Infantry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>车辆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>步兵</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -25018,7 +25037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1122"/>
+  <dimension ref="A1:D1125"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -37111,255 +37130,288 @@
     </row>
     <row r="1100" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1100" s="3" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
       <c r="B1100" s="4" t="s">
         <v>3130</v>
       </c>
       <c r="C1100" s="3" t="s">
-        <v>3150</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="1101" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1101" s="3" t="s">
-        <v>3134</v>
+        <v>3132</v>
       </c>
       <c r="B1101" s="4" t="s">
         <v>3131</v>
       </c>
       <c r="C1101" s="3" t="s">
-        <v>3150</v>
-      </c>
-    </row>
-    <row r="1102" spans="1:3" x14ac:dyDescent="0.4">
+        <v>3144</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A1102" s="3" t="s">
-        <v>3133</v>
+        <v>3199</v>
       </c>
       <c r="B1102" s="4" t="s">
-        <v>3132</v>
+        <v>3201</v>
       </c>
       <c r="C1102" s="3" t="s">
-        <v>3151</v>
-      </c>
-    </row>
-    <row r="1103" spans="1:3" x14ac:dyDescent="0.4">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A1103" s="3" t="s">
-        <v>3136</v>
+        <v>3200</v>
       </c>
       <c r="B1103" s="4" t="s">
-        <v>3139</v>
+        <v>3202</v>
       </c>
       <c r="C1103" s="3" t="s">
-        <v>3152</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="1104" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1104" s="3" t="s">
-        <v>3137</v>
+        <v>3189</v>
       </c>
       <c r="B1104" s="4" t="s">
-        <v>3138</v>
+        <v>3190</v>
       </c>
       <c r="C1104" s="3" t="s">
-        <v>3153</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="1105" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1105" s="3" t="s">
+        <v>3198</v>
+      </c>
+      <c r="B1105" s="4" t="s">
+        <v>3191</v>
+      </c>
+      <c r="C1105" s="3" t="s">
+        <v>3196</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1106" s="3" t="s">
+        <v>3192</v>
+      </c>
+      <c r="B1106" s="4" t="s">
+        <v>3057</v>
+      </c>
+      <c r="C1106" s="3" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1107" s="3" t="s">
+        <v>3193</v>
+      </c>
+      <c r="B1107" s="4" t="s">
+        <v>3194</v>
+      </c>
+      <c r="C1107" s="3" t="s">
+        <v>3197</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1108" s="3" t="s">
+        <v>3134</v>
+      </c>
+      <c r="B1108" s="4" t="s">
+        <v>3135</v>
+      </c>
+      <c r="C1108" s="3" t="s">
+        <v>3145</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A1109" s="3" t="s">
+        <v>3136</v>
+      </c>
+      <c r="B1109" s="4" t="s">
+        <v>3139</v>
+      </c>
+      <c r="C1109" s="3" t="s">
+        <v>3146</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A1110" s="3" t="s">
+        <v>3137</v>
+      </c>
+      <c r="B1110" s="4" t="s">
         <v>3140</v>
       </c>
-      <c r="B1105" s="4" t="s">
+      <c r="C1110" s="3" t="s">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:3" ht="38" x14ac:dyDescent="0.4">
+      <c r="A1111" s="3" t="s">
+        <v>3138</v>
+      </c>
+      <c r="B1111" s="4" t="s">
         <v>3141</v>
       </c>
-      <c r="C1105" s="3" t="s">
-        <v>3154</v>
-      </c>
-    </row>
-    <row r="1106" spans="1:3" ht="38" x14ac:dyDescent="0.4">
-      <c r="A1106" s="3" t="s">
+      <c r="C1111" s="3" t="s">
+        <v>3148</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1112" s="3" t="s">
+        <v>3143</v>
+      </c>
+      <c r="B1112" s="4" t="s">
         <v>3142</v>
       </c>
-      <c r="B1106" s="4" t="s">
-        <v>3145</v>
-      </c>
-      <c r="C1106" s="3" t="s">
-        <v>3155</v>
-      </c>
-    </row>
-    <row r="1107" spans="1:3" ht="38" x14ac:dyDescent="0.4">
-      <c r="A1107" s="3" t="s">
-        <v>3143</v>
-      </c>
-      <c r="B1107" s="4" t="s">
-        <v>3146</v>
-      </c>
-      <c r="C1107" s="3" t="s">
-        <v>3156</v>
-      </c>
-    </row>
-    <row r="1108" spans="1:3" ht="38" x14ac:dyDescent="0.4">
-      <c r="A1108" s="3" t="s">
-        <v>3144</v>
-      </c>
-      <c r="B1108" s="4" t="s">
-        <v>3147</v>
-      </c>
-      <c r="C1108" s="3" t="s">
-        <v>3157</v>
-      </c>
-    </row>
-    <row r="1109" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1109" s="3" t="s">
+      <c r="C1112" s="3" t="s">
         <v>3149</v>
-      </c>
-      <c r="B1109" s="4" t="s">
-        <v>3148</v>
-      </c>
-      <c r="C1109" s="3" t="s">
-        <v>3158</v>
-      </c>
-    </row>
-    <row r="1110" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1110" s="3" t="s">
-        <v>3159</v>
-      </c>
-      <c r="B1110" s="4" t="s">
-        <v>3161</v>
-      </c>
-      <c r="C1110" s="3" t="s">
-        <v>3163</v>
-      </c>
-    </row>
-    <row r="1111" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1111" s="3" t="s">
-        <v>3160</v>
-      </c>
-      <c r="B1111" s="4" t="s">
-        <v>3162</v>
-      </c>
-      <c r="C1111" s="3" t="s">
-        <v>3164</v>
-      </c>
-    </row>
-    <row r="1112" spans="1:3" ht="38" x14ac:dyDescent="0.4">
-      <c r="A1112" s="3" t="s">
-        <v>3165</v>
-      </c>
-      <c r="B1112" s="4" t="s">
-        <v>3166</v>
-      </c>
-      <c r="C1112" s="3" t="s">
-        <v>3191</v>
       </c>
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1113" s="3" t="s">
-        <v>3167</v>
+        <v>3150</v>
       </c>
       <c r="B1113" s="4" t="s">
-        <v>3168</v>
+        <v>3152</v>
       </c>
       <c r="C1113" s="3" t="s">
-        <v>3183</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="1114" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1114" s="3" t="s">
-        <v>3169</v>
+        <v>3151</v>
       </c>
       <c r="B1114" s="4" t="s">
-        <v>3170</v>
+        <v>3153</v>
       </c>
       <c r="C1114" s="3" t="s">
-        <v>3184</v>
-      </c>
-    </row>
-    <row r="1115" spans="1:3" x14ac:dyDescent="0.4">
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:3" ht="38" x14ac:dyDescent="0.4">
       <c r="A1115" s="3" t="s">
-        <v>3171</v>
+        <v>3156</v>
       </c>
       <c r="B1115" s="4" t="s">
-        <v>3172</v>
+        <v>3157</v>
       </c>
       <c r="C1115" s="3" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
     </row>
     <row r="1116" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1116" s="3" t="s">
-        <v>3173</v>
+        <v>3158</v>
       </c>
       <c r="B1116" s="4" t="s">
+        <v>3159</v>
+      </c>
+      <c r="C1116" s="3" t="s">
         <v>3174</v>
-      </c>
-      <c r="C1116" s="3" t="s">
-        <v>3186</v>
       </c>
     </row>
     <row r="1117" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1117" s="3" t="s">
+        <v>3160</v>
+      </c>
+      <c r="B1117" s="4" t="s">
+        <v>3161</v>
+      </c>
+      <c r="C1117" s="3" t="s">
         <v>3175</v>
-      </c>
-      <c r="B1117" s="4" t="s">
-        <v>3176</v>
-      </c>
-      <c r="C1117" s="3" t="s">
-        <v>3187</v>
       </c>
     </row>
     <row r="1118" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1118" s="3" t="s">
-        <v>3177</v>
+        <v>3162</v>
       </c>
       <c r="B1118" s="4" t="s">
-        <v>3178</v>
+        <v>3163</v>
       </c>
       <c r="C1118" s="3" t="s">
-        <v>3188</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="1119" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1119" s="3" t="s">
-        <v>3179</v>
+        <v>3164</v>
       </c>
       <c r="B1119" s="4" t="s">
-        <v>3180</v>
+        <v>3165</v>
       </c>
       <c r="C1119" s="3" t="s">
-        <v>3189</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="1120" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1120" s="3" t="s">
-        <v>3181</v>
+        <v>3166</v>
       </c>
       <c r="B1120" s="4" t="s">
-        <v>3182</v>
+        <v>3167</v>
       </c>
       <c r="C1120" s="3" t="s">
-        <v>3190</v>
+        <v>3178</v>
       </c>
     </row>
     <row r="1121" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1121" s="3" t="s">
-        <v>3193</v>
+        <v>3168</v>
       </c>
       <c r="B1121" s="4" t="s">
-        <v>3196</v>
+        <v>3169</v>
       </c>
       <c r="C1121" s="3" t="s">
-        <v>3194</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="1122" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1122" s="3" t="s">
-        <v>3192</v>
+        <v>3170</v>
       </c>
       <c r="B1122" s="4" t="s">
-        <v>3197</v>
+        <v>3171</v>
       </c>
       <c r="C1122" s="3" t="s">
-        <v>3195</v>
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1123" s="3" t="s">
+        <v>3172</v>
+      </c>
+      <c r="B1123" s="4" t="s">
+        <v>3173</v>
+      </c>
+      <c r="C1123" s="3" t="s">
+        <v>3181</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1124" s="3" t="s">
+        <v>3184</v>
+      </c>
+      <c r="B1124" s="4" t="s">
+        <v>3187</v>
+      </c>
+      <c r="C1124" s="3" t="s">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1125" s="3" t="s">
+        <v>3183</v>
+      </c>
+      <c r="B1125" s="4" t="s">
+        <v>3188</v>
+      </c>
+      <c r="C1125" s="3" t="s">
+        <v>3186</v>
       </c>
     </row>
   </sheetData>

--- a/Supplementary/文档/FALanguage新增标签.xlsx
+++ b/Supplementary/文档/FALanguage新增标签.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YURI\源码\FA2spHDM\Supplementary\文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03CA23D-C1C8-4BC1-AA3E-BEC972BC03EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F51288-93EF-4103-B3F0-319E99CB1B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3020" yWindow="760" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8820" yWindow="2030" windowWidth="28900" windowHeight="17710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3369" uniqueCount="3203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3372" uniqueCount="3206">
   <si>
     <t>INIEditorTitle</t>
   </si>
@@ -24620,6 +24620,16 @@
   <si>
     <t>步兵</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Options.TileSetBrowserMultiLineTabs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地形浏览器标签页多行显示</t>
+  </si>
+  <si>
+    <t>Display tile browser tabs in multiple rows</t>
   </si>
 </sst>
 </file>
@@ -25037,7 +25047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1125"/>
+  <dimension ref="A1:D1126"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.25" style="3" customWidth="1"/>
@@ -37414,6 +37424,17 @@
         <v>3186</v>
       </c>
     </row>
+    <row r="1126" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1126" s="3" t="s">
+        <v>3203</v>
+      </c>
+      <c r="B1126" s="4" t="s">
+        <v>3204</v>
+      </c>
+      <c r="C1126" s="3" t="s">
+        <v>3205</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
